--- a/processed_ruby_restored_xlsx/sc013_１日目添い寝.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc013_１日目添い寝.ss.xlsx
@@ -547,8 +547,8 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>In the end I couldn't tell who wrote it, but somehow I
-have a feeling about everyone.</t>
+          <t>In the end I couldn't tell who wrote it, but somehow
+I have a feeling about everyone.</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -582,8 +582,8 @@
         <is>
           <t>If we're talking pure clinginess then Rurichiyo-chan
 fits too, and Nono-chan just arrived on this
-island—she might be anxious even if she hasn't said it
-out loud.</t>
+island—she might be anxious even if she hasn't said
+it out loud.</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -629,8 +629,8 @@
       <c r="B11" s="1" t="inlineStr">
         <is>
           <t>They probably couldn't say it there with the others
-around, but they were also questioned about who they'd
-sleep beside.</t>
+around, but they were also questioned about who
+they'd sleep beside.</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -814,8 +814,8 @@
       <c r="B23" s="1" t="inlineStr">
         <is>
           <t>She's the type who most innocently would have written
-it, and imagining that Miru-chan really did is just so
-cute.</t>
+it, and imagining that Miru-chan really did is just
+so cute.</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -830,9 +830,9 @@
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>Besides, she'd probably accept without hesitation, and
-it seems like we'd get to have a cuddly sleep beside
-her......</t>
+          <t>Besides, she'd probably accept without hesitation,
+and it seems like we'd get to have a cuddly sleep
+beside her......</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -972,8 +972,8 @@
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>The lights are out, and it looks like both of them are
-already asleep.</t>
+          <t>The lights are out, and it looks like both of them
+are already asleep.</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1282,7 +1282,8 @@
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>She probably felt the draft when I lifted the blanket.</t>
+          <t>She probably felt the draft when I lifted the
+blanket.</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1327,8 +1328,8 @@
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>...Once the futon warms up, her breathing goes back to
-normal.</t>
+          <t>...Once the futon warms up, her breathing goes back
+to normal.</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1463,9 +1464,9 @@
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>Even asleep, if she reacts just to the temperature she
-feels, then... what would happen if I touched her with
-my hand？</t>
+          <t>Even asleep, if she reacts just to the temperature
+she feels, then... what would happen if I touched her
+with my hand？</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -1481,8 +1482,8 @@
       <c r="B66" s="1" t="inlineStr">
         <is>
           <t>Usually Miru-chan comes over to me, but when she does
-that her mood comes first, so sensation probably takes
-a backseat.</t>
+that her mood comes first, so sensation probably
+takes a backseat.</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -1497,8 +1498,8 @@
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>But now, unconscious and defenseless, Miru-chan's true
-sensitivity should be completely exposed.</t>
+          <t>But now, unconscious and defenseless, Miru-chan's
+true sensitivity should be completely exposed.</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -1573,8 +1574,8 @@
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>I won't allow that expression to be distorted even for
-an instant...！</t>
+          <t>I won't allow that expression to be distorted even
+for an instant...！</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -2104,7 +2105,8 @@
       </c>
       <c r="B107" s="1" t="inlineStr">
         <is>
-          <t>When I left her alone, this time she started laughing.</t>
+          <t>When I left her alone, this time she started
+laughing.</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -2134,7 +2136,8 @@
       </c>
       <c r="B109" s="1" t="inlineStr">
         <is>
-          <t>Maybe she's dreaming about roughhousing with everyone？</t>
+          <t>Maybe she's dreaming about roughhousing with
+everyone？</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -2335,8 +2338,8 @@
       </c>
       <c r="B122" s="1" t="inlineStr">
         <is>
-          <t>...Miru-chan started sucking on the finger I’d pressed
-to her lips！</t>
+          <t>...Miru-chan started sucking on the finger I’d
+pressed to her lips！</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -2566,7 +2569,8 @@
       <c r="B137" s="1" t="inlineStr">
         <is>
           <t>Maybe because she was sucking in her sleep, she
-couldn’t breathe properly between breaths... probably.</t>
+couldn’t breathe properly between breaths...
+probably.</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -2596,8 +2600,8 @@
       </c>
       <c r="B139" s="1" t="inlineStr">
         <is>
-          <t>After all, today’s sex-ed should have been stimulating
-for Miru-chan too.</t>
+          <t>After all, today’s sex-ed should have been
+stimulating for Miru-chan too.</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -3375,9 +3379,9 @@
       </c>
       <c r="B190" s="1" t="inlineStr">
         <is>
-          <t>Because she was asleep, it was probably harder for her
-to exhale, but there was also the thing earlier where
-she latched onto my finger.</t>
+          <t>Because she was asleep, it was probably harder for
+her to exhale, but there was also the thing earlier
+where she latched onto my finger.</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -3636,8 +3640,8 @@
       </c>
       <c r="B207" s="1" t="inlineStr">
         <is>
-          <t>I tried to pull my tongue back during that moment, but
-I became unable to move.</t>
+          <t>I tried to pull my tongue back during that moment,
+but I became unable to move.</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -3667,8 +3671,8 @@
       </c>
       <c r="B209" s="1" t="inlineStr">
         <is>
-          <t>Our saliva, glinting, stretching into a string between
-her upper and lower lips…</t>
+          <t>Our saliva, glinting, stretching into a string
+between her upper and lower lips…</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -4446,8 +4450,8 @@
       </c>
       <c r="B260" s="1" t="inlineStr">
         <is>
-          <t>When I pulled my face away without thinking, Miru-chan
-smiled satisﬁedly.</t>
+          <t>When I pulled my face away without thinking,
+Miru-chan smiled satisﬁedly.</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -4478,7 +4482,8 @@
       </c>
       <c r="B262" s="1" t="inlineStr">
         <is>
-          <t>No, rather, I should say I was led to it by Miru-chan…</t>
+          <t>No, rather, I should say I was led to it by
+Miru-chan…</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -4493,7 +4498,8 @@
       </c>
       <c r="B263" s="1" t="inlineStr">
         <is>
-          <t>Against a sleeping Miru-chan, I'm completely helpless.</t>
+          <t>Against a sleeping Miru-chan, I'm completely
+helpless.</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -4554,8 +4560,9 @@
       </c>
       <c r="B267" s="1" t="inlineStr">
         <is>
-          <t>Earlier she was responding in her sleep to my teasing,
-but now it feels like she's drifted into a deep sleep.</t>
+          <t>Earlier she was responding in her sleep to my
+teasing, but now it feels like she's drifted into a
+deep sleep.</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -4679,8 +4686,8 @@
       </c>
       <c r="B275" s="1" t="inlineStr">
         <is>
-          <t>Contrary to her usual sassy attitude, she's actually a
-shy, somewhat socially awkward, and kind of lonely
+          <t>Contrary to her usual sassy attitude, she's actually
+a shy, somewhat socially awkward, and kind of lonely
 girl...</t>
         </is>
       </c>
@@ -5144,8 +5151,8 @@
       </c>
       <c r="B305" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan's sleeping face can be summed up in one word:
-cute.</t>
+          <t>Rin-chan's sleeping face can be summed up in one
+word: cute.</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -5191,8 +5198,8 @@
       <c r="B308" s="1" t="inlineStr">
         <is>
           <t>She’s usually cheeky and sharp-tongued, messing me
-about, but she can be shy and easily frightened, which
-is kind of cute.</t>
+about, but she can be shy and easily frightened,
+which is kind of cute.</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -5254,8 +5261,8 @@
       </c>
       <c r="B312" s="1" t="inlineStr">
         <is>
-          <t>I couldn't even go so far as to play a prank on her as
-payback...</t>
+          <t>I couldn't even go so far as to play a prank on her
+as payback...</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -5331,7 +5338,8 @@
       </c>
       <c r="B317" s="1" t="inlineStr">
         <is>
-          <t>It was as if she were embarrassed at catching my gaze.</t>
+          <t>It was as if she were embarrassed at catching my
+gaze.</t>
         </is>
       </c>
       <c r="C317" t="n">
@@ -5363,8 +5371,8 @@
       <c r="B319" s="1" t="inlineStr">
         <is>
           <t>...But Rin-chan has that kind of quick intuition that
-makes me think she might, and that's one of the things
-that teases me.</t>
+makes me think she might, and that's one of the
+things that teases me.</t>
         </is>
       </c>
       <c r="C319" t="n">
@@ -5471,8 +5479,8 @@
       </c>
       <c r="B326" s="1" t="inlineStr">
         <is>
-          <t>Right now, she probably wouldn't notice no matter what
-I did.</t>
+          <t>Right now, she probably wouldn't notice no matter
+what I did.</t>
         </is>
       </c>
       <c r="C326" t="n">
@@ -5657,8 +5665,8 @@
       </c>
       <c r="B338" s="1" t="inlineStr">
         <is>
-          <t>...It's such a trivial thing, but it weirdly turned me
-on.</t>
+          <t>...It's such a trivial thing, but it weirdly turned
+me on.</t>
         </is>
       </c>
       <c r="C338" t="n">
@@ -5688,8 +5696,8 @@
       </c>
       <c r="B340" s="1" t="inlineStr">
         <is>
-          <t>No, that's not it. These half-open lips are those of a
-girl waiting for a kiss...！</t>
+          <t>No, that's not it. These half-open lips are those of
+a girl waiting for a kiss...！</t>
         </is>
       </c>
       <c r="C340" t="n">
@@ -5827,7 +5835,8 @@
       </c>
       <c r="B349" s="1" t="inlineStr">
         <is>
-          <t>Uwaa... just thinking about it makes my heart race...！</t>
+          <t>Uwaa... just thinking about it makes my heart
+race...！</t>
         </is>
       </c>
       <c r="C349" t="n">
@@ -6619,8 +6628,8 @@
       </c>
       <c r="B401" s="1" t="inlineStr">
         <is>
-          <t>Normally, Rin-chan is quick with words when it counts,
-so it's scary when she doesn't speak.</t>
+          <t>Normally, Rin-chan is quick with words when it
+counts, so it's scary when she doesn't speak.</t>
         </is>
       </c>
       <c r="C401" t="n">
@@ -6846,8 +6855,8 @@
       </c>
       <c r="B416" s="1" t="inlineStr">
         <is>
-          <t>Her face is still red, but Rin-chan's usual expression
-is back.</t>
+          <t>Her face is still red, but Rin-chan's usual
+expression is back.</t>
         </is>
       </c>
       <c r="C416" t="n">
@@ -7607,8 +7616,8 @@
       </c>
       <c r="B466" s="1" t="inlineStr">
         <is>
-          <t>She wanted to see a hidden act somewhere away from the
-others.</t>
+          <t>She wanted to see a hidden act somewhere away from
+the others.</t>
         </is>
       </c>
       <c r="C466" t="n">
@@ -7775,9 +7784,9 @@
       </c>
       <c r="B477" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan, who didn't know what 'okazu' meant, frowned,
-thinking she'd been told something completely
-unrelated.</t>
+          <t>Rin-chan, who didn't know what 'okazu' meant,
+frowned, thinking she'd been told something
+completely unrelated.</t>
         </is>
       </c>
       <c r="C477" t="n">
@@ -8312,8 +8321,8 @@
       <c r="B512" s="1" t="inlineStr">
         <is>
           <t>The fact she handed me her panties probably meant yes
-to that sort of thing, but when push came to shove she
-might get so embarrassed she’d start to cry.</t>
+to that sort of thing, but when push came to shove
+she might get so embarrassed she’d start to cry.</t>
         </is>
       </c>
       <c r="C512" t="n">
@@ -8560,8 +8569,8 @@
       </c>
       <c r="B528" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan said in a slightly annoyed voice, hugging her
-knees with a faintly troubled expression.</t>
+          <t>Rin-chan said in a slightly annoyed voice, hugging
+her knees with a faintly troubled expression.</t>
         </is>
       </c>
       <c r="C528" t="n">
@@ -9086,8 +9095,8 @@
       </c>
       <c r="B562" s="1" t="inlineStr">
         <is>
-          <t>A warm, reassuring sense of being enveloped...or so to
-speak.</t>
+          <t>A warm, reassuring sense of being enveloped...or so
+to speak.</t>
         </is>
       </c>
       <c r="C562" t="n">
@@ -9102,9 +9111,9 @@
       </c>
       <c r="B563" s="1" t="inlineStr">
         <is>
-          <t>But the parent bird's feathers are unexpectedly stiff,
-and there's a sternness to them that pushes the chick
-to fly off sooner.</t>
+          <t>But the parent bird's feathers are unexpectedly
+stiff, and there's a sternness to them that pushes
+the chick to fly off sooner.</t>
         </is>
       </c>
       <c r="C563" t="n">
@@ -9427,8 +9436,8 @@
       </c>
       <c r="B584" s="1" t="inlineStr">
         <is>
-          <t>When I stopped and my mind started working, I realized
-I was doing something really embarrassing...</t>
+          <t>When I stopped and my mind started working, I
+realized I was doing something really embarrassing...</t>
         </is>
       </c>
       <c r="C584" t="n">
@@ -9565,8 +9574,8 @@
       </c>
       <c r="B593" s="1" t="inlineStr">
         <is>
-          <t>When I look straight ahead, Rin-chan's cute slit comes
-into view.</t>
+          <t>When I look straight ahead, Rin-chan's cute slit
+comes into view.</t>
         </is>
       </c>
       <c r="C593" t="n">
@@ -9672,8 +9681,8 @@
       </c>
       <c r="B600" s="1" t="inlineStr">
         <is>
-          <t>From the patterns observed so far, that’s a sign she’s
-embarrassed.</t>
+          <t>From the patterns observed so far, that’s a sign
+she’s embarrassed.</t>
         </is>
       </c>
       <c r="C600" t="n">
@@ -9918,7 +9927,8 @@
       <c r="B616" s="1" t="inlineStr">
         <is>
           <t>While she fidgeted, her butt would drop and that area
-would become harder to see, but that’s also an accent.</t>
+would become harder to see, but that’s also an
+accent.</t>
         </is>
       </c>
       <c r="C616" t="n">
@@ -10133,8 +10143,8 @@
       </c>
       <c r="B630" s="1" t="inlineStr">
         <is>
-          <t>「Ahh... the stuff coming out from the tip's getting on
-the panties...」</t>
+          <t>「Ahh... the stuff coming out from the tip's getting
+on the panties...」</t>
         </is>
       </c>
       <c r="C630" t="n">
@@ -10407,8 +10417,8 @@
       </c>
       <c r="B648" s="1" t="inlineStr">
         <is>
-          <t>I meant to respond sincerely, but Rin-chan widened her
-eyes like it was the first she'd heard of it.</t>
+          <t>I meant to respond sincerely, but Rin-chan widened
+her eyes like it was the first she'd heard of it.</t>
         </is>
       </c>
       <c r="C648" t="n">
@@ -10532,8 +10542,8 @@
       </c>
       <c r="B656" s="1" t="inlineStr">
         <is>
-          <t>Ah, this mix of shame and bewilderment is irresistible
-too！</t>
+          <t>Ah, this mix of shame and bewilderment is
+irresistible too！</t>
         </is>
       </c>
       <c r="C656" t="n">
@@ -10807,9 +10817,9 @@
       </c>
       <c r="B674" s="1" t="inlineStr">
         <is>
-          <t>She's a little desperate and still looks troubled, but
-the light in her eyes is slowly returning to the usual
-Rin-chan.</t>
+          <t>She's a little desperate and still looks troubled,
+but the light in her eyes is slowly returning to the
+usual Rin-chan.</t>
         </is>
       </c>
       <c r="C674" t="n">
@@ -10841,8 +10851,8 @@
       <c r="B676" s="1" t="inlineStr">
         <is>
           <t>Feeling that again, I turned my hips toward Rin-chan
-once more and began stroking myself toward ejaculation
-however I liked.</t>
+once more and began stroking myself toward
+ejaculation however I liked.</t>
         </is>
       </c>
       <c r="C676" t="n">
@@ -11069,8 +11079,8 @@
       </c>
       <c r="B691" s="1" t="inlineStr">
         <is>
-          <t>「Right... and once it gets used to it, gradually speed
-up.」</t>
+          <t>「Right... and once it gets used to it, gradually
+speed up.」</t>
         </is>
       </c>
       <c r="C691" t="n">
@@ -11223,8 +11233,8 @@
       </c>
       <c r="B701" s="1" t="inlineStr">
         <is>
-          <t>When I stroked my penis at high speed, Rin-chan opened
-her eyes and mouth wide.</t>
+          <t>When I stroked my penis at high speed, Rin-chan
+opened her eyes and mouth wide.</t>
         </is>
       </c>
       <c r="C701" t="n">
@@ -11561,8 +11571,8 @@
       </c>
       <c r="B723" s="1" t="inlineStr">
         <is>
-          <t>Sensing my strange presence, Rin-chan called out to me
-with concern.</t>
+          <t>Sensing my strange presence, Rin-chan called out to
+me with concern.</t>
         </is>
       </c>
       <c r="C723" t="n">
@@ -11836,8 +11846,8 @@
       </c>
       <c r="B741" s="1" t="inlineStr">
         <is>
-          <t>The spurting semen arced through the air, and Rin-chan
-let out a small cry.</t>
+          <t>The spurting semen arced through the air, and
+Rin-chan let out a small cry.</t>
         </is>
       </c>
       <c r="C741" t="n">
@@ -12005,8 +12015,8 @@
       </c>
       <c r="B752" s="1" t="inlineStr">
         <is>
-          <t>It's like embarrassment has reached its absolute limit
-here...</t>
+          <t>It's like embarrassment has reached its absolute
+limit here...</t>
         </is>
       </c>
       <c r="C752" t="n">
@@ -12021,8 +12031,8 @@
       </c>
       <c r="B753" s="1" t="inlineStr">
         <is>
-          <t>It's better than her emotions exploding into a scream,
-but with Rin-chan it's scary from here on.</t>
+          <t>It's better than her emotions exploding into a
+scream, but with Rin-chan it's scary from here on.</t>
         </is>
       </c>
       <c r="C753" t="n">
@@ -12038,7 +12048,8 @@
       <c r="B754" s="1" t="inlineStr">
         <is>
           <t>I braced myself to be scolded, and while Rin-chan
-stayed frozen I quickly put on my underwear and pants.</t>
+stayed frozen I quickly put on my underwear and
+pants.</t>
         </is>
       </c>
       <c r="C754" t="n">
@@ -12420,9 +12431,9 @@
       </c>
       <c r="B779" s="1" t="inlineStr">
         <is>
-          <t>Semen was still between her legs, but she was probably
-so angry she didn’t even care about something like
-that.</t>
+          <t>Semen was still between her legs, but she was
+probably so angry she didn’t even care about
+something like that.</t>
         </is>
       </c>
       <c r="C779" t="n">
@@ -12467,8 +12478,8 @@
       </c>
       <c r="B782" s="1" t="inlineStr">
         <is>
-          <t>「...But you said 'show me,' Rin, so... I guess I can't
-really blame you...」</t>
+          <t>「...But you said 'show me,' Rin, so... I guess I
+can't really blame you...」</t>
         </is>
       </c>
       <c r="C782" t="n">
@@ -12729,8 +12740,8 @@
       </c>
       <c r="B799" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan spoke in a soft voice, then turned to me with
-a face like she was about to cry.</t>
+          <t>Rin-chan spoke in a soft voice, then turned to me
+with a face like she was about to cry.</t>
         </is>
       </c>
       <c r="C799" t="n">
@@ -12979,8 +12990,8 @@
       </c>
       <c r="B815" s="1" t="inlineStr">
         <is>
-          <t>It was then I realized I was still gripping Rin-chan's
-panties.</t>
+          <t>It was then I realized I was still gripping
+Rin-chan's panties.</t>
         </is>
       </c>
       <c r="C815" t="n">
@@ -13090,8 +13101,8 @@
         <is>
           <t>Normally she ends up playing the sensible one, so she
 looks the most mature among everyone, but when she
-wants attention, Rurichiyo-chan is the least shy about
-it.</t>
+wants attention, Rurichiyo-chan is the least shy
+about it.</t>
         </is>
       </c>
       <c r="C822" t="n">
@@ -13121,8 +13132,9 @@
       </c>
       <c r="B824" s="1" t="inlineStr">
         <is>
-          <t>Sometimes she's the one being coddled, sometimes she's
-the one who spoils me, and it always soothes my heart.</t>
+          <t>Sometimes she's the one being coddled, sometimes
+she's the one who spoils me, and it always soothes my
+heart.</t>
         </is>
       </c>
       <c r="C824" t="n">
@@ -13169,8 +13181,8 @@
       <c r="B827" s="1" t="inlineStr">
         <is>
           <t>There's a closeness that comes from being uncle and
-niece, sure, but I feel something between us that goes
-beyond that relationship.</t>
+niece, sure, but I feel something between us that
+goes beyond that relationship.</t>
         </is>
       </c>
       <c r="C827" t="n">
@@ -13230,8 +13242,8 @@
       </c>
       <c r="B831" s="1" t="inlineStr">
         <is>
-          <t>Ah... this is Rurichiyo-chan and Nono-chan's room now,
-huh.</t>
+          <t>Ah... this is Rurichiyo-chan and Nono-chan's room
+now, huh.</t>
         </is>
       </c>
       <c r="C831" t="n">
@@ -13310,8 +13322,8 @@
       </c>
       <c r="B836" s="1" t="inlineStr">
         <is>
-          <t>I peered in from below, and luckily Rurichiyo-chan was
-in the lower bunk.</t>
+          <t>I peered in from below, and luckily Rurichiyo-chan
+was in the lower bunk.</t>
         </is>
       </c>
       <c r="C836" t="n">
@@ -13371,8 +13383,8 @@
       </c>
       <c r="B840" s="1" t="inlineStr">
         <is>
-          <t>Maybe she sensed me — Rurichiyo-chan opened her eyes a
-little and sat up with a groggy start.</t>
+          <t>Maybe she sensed me — Rurichiyo-chan opened her eyes
+a little and sat up with a groggy start.</t>
         </is>
       </c>
       <c r="C840" t="n">
@@ -13828,7 +13840,8 @@
       </c>
       <c r="B870" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan fell back onto the bed holding my head.</t>
+          <t>Rurichiyo-chan fell back onto the bed holding my
+head.</t>
         </is>
       </c>
       <c r="C870" t="n">
@@ -14015,8 +14028,8 @@
       </c>
       <c r="B882" s="1" t="inlineStr">
         <is>
-          <t>Being held like this, with my head trapped, is kind of
-wonderful, but I can’t do anything like this.</t>
+          <t>Being held like this, with my head trapped, is kind
+of wonderful, but I can’t do anything like this.</t>
         </is>
       </c>
       <c r="C882" t="n">
@@ -14570,7 +14583,8 @@
       </c>
       <c r="B918" s="1" t="inlineStr">
         <is>
-          <t>Is Rurichiyo-chan dreaming that she's soothing a baby？</t>
+          <t>Is Rurichiyo-chan dreaming that she's soothing a
+baby？</t>
         </is>
       </c>
       <c r="C918" t="n">
@@ -14862,7 +14876,8 @@
       </c>
       <c r="B937" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan starts unbuttoning her pajamas herself.</t>
+          <t>Rurichiyo-chan starts unbuttoning her pajamas
+herself.</t>
         </is>
       </c>
       <c r="C937" t="n">
@@ -14877,9 +14892,9 @@
       </c>
       <c r="B938" s="1" t="inlineStr">
         <is>
-          <t>I pretty much knew what kind of dream you were having,
-but to go this far — what a child so full of maternal
-instinct...！</t>
+          <t>I pretty much knew what kind of dream you were
+having, but to go this far — what a child so full of
+maternal instinct...！</t>
         </is>
       </c>
       <c r="C938" t="n">
@@ -15033,8 +15048,8 @@
       </c>
       <c r="B948" s="1" t="inlineStr">
         <is>
-          <t>At the very least, Rurichiyo-chan is dreaming a gentle
-dream with pure feelings.</t>
+          <t>At the very least, Rurichiyo-chan is dreaming a
+gentle dream with pure feelings.</t>
         </is>
       </c>
       <c r="C948" t="n">
@@ -15080,8 +15095,8 @@
       </c>
       <c r="B951" s="1" t="inlineStr">
         <is>
-          <t>Above all, even if it was just a dream, Rurichiyo-chan
-was determined to do it.</t>
+          <t>Above all, even if it was just a dream,
+Rurichiyo-chan was determined to do it.</t>
         </is>
       </c>
       <c r="C951" t="n">
@@ -16523,8 +16538,8 @@
       </c>
       <c r="B1045" s="1" t="inlineStr">
         <is>
-          <t>「Aah... nfa...！ Sucking my boobs so much... good girl,
-dechu~... nfufu！」</t>
+          <t>「Aah... nfa...！ Sucking my boobs so much... good
+girl, dechu~... nfufu！」</t>
         </is>
       </c>
       <c r="C1045" t="n">
@@ -16539,8 +16554,8 @@
       </c>
       <c r="B1046" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan’s dream is just of soothing a baby — an
-utterly innocent thing.</t>
+          <t>Rurichiyo-chan’s dream is just of soothing a baby —
+an utterly innocent thing.</t>
         </is>
       </c>
       <c r="C1046" t="n">
@@ -16555,8 +16570,8 @@
       </c>
       <c r="B1047" s="1" t="inlineStr">
         <is>
-          <t>And yet... bringing sexual desire into that feels like
-it would taint that purity.</t>
+          <t>And yet... bringing sexual desire into that feels
+like it would taint that purity.</t>
         </is>
       </c>
       <c r="C1047" t="n">
@@ -16804,7 +16819,8 @@
       </c>
       <c r="B1063" s="1" t="inlineStr">
         <is>
-          <t>Whoa... just thinking about it gets me so fired up...！</t>
+          <t>Whoa... just thinking about it gets me so fired
+up...！</t>
         </is>
       </c>
       <c r="C1063" t="n">
@@ -17065,8 +17081,8 @@
       </c>
       <c r="B1080" s="1" t="inlineStr">
         <is>
-          <t>…Reacting to Rurichiyo-chan's lustful voice, I too was
-overwhelmed.</t>
+          <t>…Reacting to Rurichiyo-chan's lustful voice, I too
+was overwhelmed.</t>
         </is>
       </c>
       <c r="C1080" t="n">
@@ -17959,9 +17975,9 @@
       <c r="B1138" s="1" t="inlineStr">
         <is>
           <t>I'm not doing anything wrong, so I could walk in
-confidently, but thinking about going to a girl's room
-this late at night brings along a certain kind of
-nervousness.</t>
+confidently, but thinking about going to a girl's
+room this late at night brings along a certain kind
+of nervousness.</t>
         </is>
       </c>
       <c r="C1138" t="n">
@@ -18009,8 +18025,8 @@
       </c>
       <c r="B1141" s="1" t="inlineStr">
         <is>
-          <t>No... but the purpose is strictly to just sleep beside
-her.</t>
+          <t>No... but the purpose is strictly to just sleep
+beside her.</t>
         </is>
       </c>
       <c r="C1141" t="n">
@@ -18240,8 +18256,8 @@
       </c>
       <c r="B1156" s="1" t="inlineStr">
         <is>
-          <t>A reasonable question, but kind of obvious on purpose,
-huh.</t>
+          <t>A reasonable question, but kind of obvious on
+purpose, huh.</t>
         </is>
       </c>
       <c r="C1156" t="n">
@@ -18486,7 +18502,8 @@
       </c>
       <c r="B1172" s="1" t="inlineStr">
         <is>
-          <t>...Alright, this calls for a straightforward approach.</t>
+          <t>...Alright, this calls for a straightforward
+approach.</t>
         </is>
       </c>
       <c r="C1172" t="n">
@@ -18730,8 +18747,8 @@
       </c>
       <c r="B1188" s="1" t="inlineStr">
         <is>
-          <t>It's painfully obvious, but maybe I shouldn't push her
-any further.</t>
+          <t>It's painfully obvious, but maybe I shouldn't push
+her any further.</t>
         </is>
       </c>
       <c r="C1188" t="n">
@@ -18746,8 +18763,8 @@
       </c>
       <c r="B1189" s="1" t="inlineStr">
         <is>
-          <t>I get it. If I go out of my way to flaunt that I know,
-she might end up hating me.</t>
+          <t>I get it. If I go out of my way to flaunt that I
+know, she might end up hating me.</t>
         </is>
       </c>
       <c r="C1189" t="n">
@@ -18962,8 +18979,8 @@
       <c r="B1203" s="1" t="inlineStr">
         <is>
           <t>「Um... could you sleep beside me... I mean, before
-going to sleep, do something like what Mom always used
-to do...」</t>
+going to sleep, do something like what Mom always
+used to do...」</t>
         </is>
       </c>
       <c r="C1203" t="n">
@@ -19070,7 +19087,8 @@
       </c>
       <c r="B1210" s="1" t="inlineStr">
         <is>
-          <t>When I answer honestly, Nono-chan nods as if relieved.</t>
+          <t>When I answer honestly, Nono-chan nods as if
+relieved.</t>
         </is>
       </c>
       <c r="C1210" t="n">
@@ -19524,8 +19542,8 @@
       </c>
       <c r="B1240" s="1" t="inlineStr">
         <is>
-          <t>By the way, my room used to be a closet, but it's also
-the highest room, so it has a great view.</t>
+          <t>By the way, my room used to be a closet, but it's
+also the highest room, so it has a great view.</t>
         </is>
       </c>
       <c r="C1240" t="n">
@@ -19650,8 +19668,8 @@
       </c>
       <c r="B1248" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan mumbled and stumbled over her words, failing
-to get her point across.</t>
+          <t>Nono-chan mumbled and stumbled over her words,
+failing to get her point across.</t>
         </is>
       </c>
       <c r="C1248" t="n">
@@ -19865,8 +19883,9 @@
       </c>
       <c r="B1262" s="1" t="inlineStr">
         <is>
-          <t>「Actually, once I fall asleep, I don't seem to wake up
-easily, so I might end up causing you some trouble...」</t>
+          <t>「Actually, once I fall asleep, I don't seem to wake
+up easily, so I might end up causing you some
+trouble...」</t>
         </is>
       </c>
       <c r="C1262" t="n">
@@ -20823,8 +20842,8 @@
       </c>
       <c r="B1325" s="1" t="inlineStr">
         <is>
-          <t>「B-but. If you do the same thing you always do for me,
-I think I can sleep！」</t>
+          <t>「B-but. If you do the same thing you always do for
+me, I think I can sleep！」</t>
         </is>
       </c>
       <c r="C1325" t="n">
@@ -20855,8 +20874,8 @@
       </c>
       <c r="B1327" s="1" t="inlineStr">
         <is>
-          <t>The situation was moving so fast my head couldn’t keep
-up in places… but I understood.</t>
+          <t>The situation was moving so fast my head couldn’t
+keep up in places… but I understood.</t>
         </is>
       </c>
       <c r="C1327" t="n">
@@ -20993,8 +21012,8 @@
       </c>
       <c r="B1336" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan was probably more worried about being unable
-to sleep than I had thought.</t>
+          <t>Nono-chan was probably more worried about being
+unable to sleep than I had thought.</t>
         </is>
       </c>
       <c r="C1336" t="n">
@@ -21669,8 +21688,8 @@
       <c r="B1380" s="1" t="inlineStr">
         <is>
           <t>And yet needing someone to sleep next to her would
-make her look like a little kid, and she wouldn't want
-everyone to know that.</t>
+make her look like a little kid, and she wouldn't
+want everyone to know that.</t>
         </is>
       </c>
       <c r="C1380" t="n">
@@ -22591,8 +22610,8 @@
       </c>
       <c r="B1440" s="1" t="inlineStr">
         <is>
-          <t>When I reached out to pick her up in a princess carry,
-I suddenly realized something.</t>
+          <t>When I reached out to pick her up in a princess
+carry, I suddenly realized something.</t>
         </is>
       </c>
       <c r="C1440" t="n">
@@ -22699,8 +22718,8 @@
       <c r="B1447" s="1" t="inlineStr">
         <is>
           <t>But given the situation—there's a girl asleep on the
-bed in my room... it would be strange not to be turned
-on.</t>
+bed in my room... it would be strange not to be
+turned on.</t>
         </is>
       </c>
       <c r="C1447" t="n">
@@ -22715,8 +22734,8 @@
       </c>
       <c r="B1448" s="1" t="inlineStr">
         <is>
-          <t>No, still, absentmindedly undoing the buttons can only
-be described as losing my mind.</t>
+          <t>No, still, absentmindedly undoing the buttons can
+only be described as losing my mind.</t>
         </is>
       </c>
       <c r="C1448" t="n">
@@ -22839,7 +22858,8 @@
       </c>
       <c r="B1456" s="1" t="inlineStr">
         <is>
-          <t>I snapped back to myself and shook my head in a panic.</t>
+          <t>I snapped back to myself and shook my head in a
+panic.</t>
         </is>
       </c>
       <c r="C1456" t="n">
@@ -23146,7 +23166,8 @@
       </c>
       <c r="B1476" s="1" t="inlineStr">
         <is>
-          <t>I wanted, at this point, to just strip her completely！</t>
+          <t>I wanted, at this point, to just strip her
+completely！</t>
         </is>
       </c>
       <c r="C1476" t="n">
@@ -23208,8 +23229,8 @@
       </c>
       <c r="B1480" s="1" t="inlineStr">
         <is>
-          <t>Even though it's my own hand, it feels like some other
-girl is stroking me.</t>
+          <t>Even though it's my own hand, it feels like some
+other girl is stroking me.</t>
         </is>
       </c>
       <c r="C1480" t="n">
@@ -23702,7 +23723,8 @@
       </c>
       <c r="B1512" s="1" t="inlineStr">
         <is>
-          <t>As expected, Nono-chan shows no sign of waking at all.</t>
+          <t>As expected, Nono-chan shows no sign of waking at
+all.</t>
         </is>
       </c>
       <c r="C1512" t="n">
@@ -23808,8 +23830,8 @@
       </c>
       <c r="B1519" s="1" t="inlineStr">
         <is>
-          <t>I wrap my palm in a slightly larger wad of tissues and
-wipe the semen off her cheek.</t>
+          <t>I wrap my palm in a slightly larger wad of tissues
+and wipe the semen off her cheek.</t>
         </is>
       </c>
       <c r="C1519" t="n">
@@ -24161,8 +24183,8 @@
       </c>
       <c r="B1542" s="1" t="inlineStr">
         <is>
-          <t>Maybe feeling something off at that spot, her sleeping
-breaths grow uneven.</t>
+          <t>Maybe feeling something off at that spot, her
+sleeping breaths grow uneven.</t>
         </is>
       </c>
       <c r="C1542" t="n">
@@ -24392,8 +24414,8 @@
       </c>
       <c r="B1557" s="1" t="inlineStr">
         <is>
-          <t>When the towel touched her chest, her sleeping breaths
-grew even more ragged.</t>
+          <t>When the towel touched her chest, her sleeping
+breaths grew even more ragged.</t>
         </is>
       </c>
       <c r="C1557" t="n">
@@ -24500,8 +24522,8 @@
       </c>
       <c r="B1564" s="1" t="inlineStr">
         <is>
-          <t>Sorry... this isn't the time to be enjoying myself, is
-it...</t>
+          <t>Sorry... this isn't the time to be enjoying myself,
+is it...</t>
         </is>
       </c>
       <c r="C1564" t="n">
@@ -24653,8 +24675,8 @@
       </c>
       <c r="B1574" s="1" t="inlineStr">
         <is>
-          <t>If I leave her alone, Nono-chan's breathing returns to
-normal, her breaths deepening.</t>
+          <t>If I leave her alone, Nono-chan's breathing returns
+to normal, her breaths deepening.</t>
         </is>
       </c>
       <c r="C1574" t="n">
@@ -24746,8 +24768,8 @@
       </c>
       <c r="B1580" s="1" t="inlineStr">
         <is>
-          <t>Come to think of it, even if she's a deep sleeper, she
-looks awfully quiet when she sleeps.</t>
+          <t>Come to think of it, even if she's a deep sleeper,
+she looks awfully quiet when she sleeps.</t>
         </is>
       </c>
       <c r="C1580" t="n">
@@ -24856,9 +24878,9 @@
       <c r="B1587" s="1" t="inlineStr">
         <is>
           <t>If the goal is for her to relax, it'd still be better
-if she slept here, but if that happens she'll probably
-feel awkward afterward, Nono-chan would try to be
-considerate.</t>
+if she slept here, but if that happens she'll
+probably feel awkward afterward, Nono-chan would try
+to be considerate.</t>
         </is>
       </c>
       <c r="C1587" t="n">

--- a/processed_ruby_restored_xlsx/sc013_１日目添い寝.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc013_１日目添い寝.ss.xlsx
@@ -515,8 +515,8 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>Thinking that as I lay down on the bed, I suddenly
-remembered that thing and sprang up.</t>
+          <t>Thinking that, I lay down on the bed, but suddenly
+remembered that and sprang up.</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -531,8 +531,8 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>That's right, during Sugoroku there was an order to
-sleep beside someone！</t>
+          <t>Oh right — during the Sugoroku game, there was an
+order to sleep next to someone!</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -547,8 +547,8 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>In the end I couldn't tell who wrote it, but somehow
-I have a feeling about everyone.</t>
+          <t>I couldn't figure out who had written it in the end,
+but somehow I had a hunch about everyone.</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -563,9 +563,9 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>The one who most simply seems like the type to write
-it is Miru-chan, but Rin-chan is also that kind of
-clingy, so I can't be sure.</t>
+          <t>Miru-chan is the person who most fits the image of
+someone who'd write it, but Rin-chan's the sort who's
+clingy like that too, so I can't say for sure.</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -598,7 +598,7 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>So, who is it？</t>
+          <t>Well, who could it be?</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -613,7 +613,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>I want to sleep beside all of them！</t>
+          <t>I want to sleep next to all of them!</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -628,9 +628,9 @@
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>They probably couldn't say it there with the others
-around, but they were also questioned about who
-they'd sleep beside.</t>
+          <t>I probably couldn't say it there with the other girls
+around, but I was also pressed about who I'd sleep
+next to.</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -660,8 +660,8 @@
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>Ugh... if only this body were four, I could sleep
-beside them all！</t>
+          <t>Ugh... if only I had four bodies, I could sleep next
+to all of them!</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -676,8 +676,8 @@
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>I'd like to go to each of them one by one, but that's
-just impossible.</t>
+          <t>I'd like to go around and do it for each one in turn,
+but that's just not possible.</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -708,7 +708,7 @@
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>The choice is entrusted to me...！</t>
+          <t>The choice is up to me...!</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -723,7 +723,7 @@
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>Who will I sleep beside...？</t>
+          <t>Who will I sleep next to...?</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -813,9 +813,9 @@
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>She's the type who most innocently would have written
-it, and imagining that Miru-chan really did is just
-so cute.</t>
+          <t>I don't know how to put it, but Miru-chan seems like
+the one who'd write it most innocently, and imagining
+that she actually did is so cute.</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -830,9 +830,9 @@
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>Besides, she'd probably accept without hesitation,
-and it seems like we'd get to have a cuddly sleep
-beside her......</t>
+          <t>Besides, Miru-chan would probably accept it without
+hesitation, and it seems like we could cuddle up and
+sleep together...</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -847,7 +847,7 @@
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>Alright, once I've decided, I'll act immediately！</t>
+          <t>Alright, now that I've decided, I'll act immediately!</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -878,8 +878,8 @@
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>My heart's pounding like I'm going for a nighttime
-visit...</t>
+          <t>I'm a little nervous—my heart's pounding like I'm
+going to sneak into her bed at night...</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -956,8 +956,8 @@
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan is in the same room, and Miru-chan is on the
-top bunk of the two-tier bed.</t>
+          <t>Rin-chan is also in the same room, and Miru-chan is
+on the top bunk.</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1004,8 +1004,8 @@
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>I hold my breath to muffle my presence, but climbing
-the bed ladder is the hard part.</t>
+          <t>I hold my breath and move silently, but climbing the
+ladder to the top bunk is the tricky part.</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1020,8 +1020,8 @@
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>After all, it's stuff made for girls, so as soon as I
-step on it it'll creak.</t>
+          <t>After all, it's made for girls, so if I climb onto it
+it'll immediately make a sound.</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>Slowly, slowly, one rung at a time...</t>
+          <t>Stealthily, one rung at a time...</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>Still, it lets out a squeak.</t>
+          <t>Even so, it creaks.</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>「suu-pii... suu-pii」</t>
+          <t>「snores... snores...」</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1127,8 +1127,8 @@
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>However, halfway up the ladder I can already hear
-healthy sleeping breaths.</t>
+          <t>But as I climbed the ladder, I could already hear her
+steady, healthy breathing.</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1143,8 +1143,8 @@
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>Even without seeing her face, I can tell she's
-completely out.</t>
+          <t>I can tell she's already fast asleep without even
+having to look at her sleeping face.</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>「suu-fuu... nnn... suu~」</t>
+          <t>"soft breaths... mmm... soft breaths..."</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -1236,8 +1236,8 @@
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>When I crawl into the same blanket, Miru-chan's
-breathing changes.</t>
+          <t>As I slip into the same futon, Miru-chan's breathing
+changes.</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>Could it be she sensed I was here？</t>
+          <t>Maybe she realized I'd come?</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>I think that, but Miru-chan is definitely asleep.</t>
+          <t>I thought so, but Miru-chan is definitely asleep.</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -1282,8 +1282,8 @@
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>She probably felt the draft when I lifted the
-blanket.</t>
+          <t>Miru-chan probably felt the night air when I lifted
+the futon.</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>「suuuu... fuuu... suu-pii」</t>
+          <t>「soft breaths... mmm... snores...」</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>...Once the futon warms up, her breathing goes back
+          <t>...Once the futon warmed up, her breathing returned
 to normal.</t>
         </is>
       </c>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>What a sensitive, honest body.</t>
+          <t>What a sensitive, responsive body.</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>「suu~pi~... suu~pi~」</t>
+          <t>「snores... snores...」</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>...So sensitive and so honest...</t>
+          <t>...Sensitive and responsive, huh...</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -1464,9 +1464,9 @@
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>Even asleep, if she reacts just to the temperature
-she feels, then... what would happen if I touched her
-with my hand？</t>
+          <t>Even if she's asleep, if she reacts only to perceived
+temperature... I wonder what would happen if I
+touched her with my hand?</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -1481,9 +1481,9 @@
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>Usually Miru-chan comes over to me, but when she does
-that her mood comes first, so sensation probably
-takes a backseat.</t>
+          <t>Usually Miru-chan is the one who comes to me, but in
+moments like that her mood comes first, so physical
+sensations probably take a backseat.</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -1498,8 +1498,8 @@
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>But now, unconscious and defenseless, Miru-chan's
-true sensitivity should be completely exposed.</t>
+          <t>But now, unguarded and unaware, Miru-chan's natural
+sensitivity should be laid bare.</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>C-Can I just touch you a little...？</t>
+          <t>J-Just a little... can I touch you?</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>「supi~... su~pi~」</t>
+          <t>「snores... snores...」</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>Ah... what a blissful sleeping face she has.</t>
+          <t>Ah... what a blissful sleeping face Miru-chan has.</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -1590,8 +1590,8 @@
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>But I'm not going to do anything violent or anything,
-I just want to play a little prank...</t>
+          <t>It's not like I'm going to be violent; I just want to
+play a little prank...</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>「Suu... nnn, nfu...！」</t>
+          <t>「Huu... mmm, nfu...！」</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>But... but... .</t>
+          <t>But... but...</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>「Nn！　Nnnh~！」</t>
+          <t>Nn! Nnnh~!</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="B86" s="1" t="inlineStr">
         <is>
-          <t>S-so cute... and so soft...！</t>
+          <t>S-So cute... and so soft...!</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="B88" s="1" t="inlineStr">
         <is>
-          <t>「Nn... sss... sss... hii~...」</t>
+          <t>「Mmm... shh... shh... hii~...」</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -1834,7 +1834,8 @@
       </c>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>When I let go, her soft sleeping breaths return.</t>
+          <t>When I let go, she goes back to breathing in her
+sleep.</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -1849,8 +1850,8 @@
       </c>
       <c r="B90" s="1" t="inlineStr">
         <is>
-          <t>Relieved by the way they looked, I let out a quiet
-chuckle to myself.</t>
+          <t>Relieved to see her like that, I chuckled quietly to
+myself.</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -1880,7 +1881,7 @@
       </c>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t>「...Eii.」</t>
+          <t>「...There!」</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -1895,7 +1896,7 @@
       </c>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t>Puni.</t>
+          <t>Squish.</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -1910,7 +1911,8 @@
       </c>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t>This time I tried pressing the tip of my nose.</t>
+          <t>This time I tried pressing the tip of Miru-chan's
+nose.</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -1940,7 +1942,7 @@
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>「Mmm！　Uuu…！」</t>
+          <t>「Mmm! Uuuu...!」</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -1985,7 +1987,7 @@
       </c>
       <c r="B99" s="1" t="inlineStr">
         <is>
-          <t>「...Eii!」</t>
+          <t>「...There!」</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -2000,7 +2002,7 @@
       </c>
       <c r="B100" s="1" t="inlineStr">
         <is>
-          <t>Puni.</t>
+          <t>Squish.</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -2015,7 +2017,7 @@
       </c>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>I tried pressing her cheek again.</t>
+          <t>I tried pressing Miru-chan's cheek again.</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -2060,7 +2062,7 @@
       </c>
       <c r="B104" s="1" t="inlineStr">
         <is>
-          <t>Oh… she growls when I press it….</t>
+          <t>Oh... she moans when I press her...</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -2090,7 +2092,7 @@
       </c>
       <c r="B106" s="1" t="inlineStr">
         <is>
-          <t>「Fuu… Suu… Fuhii…！」</t>
+          <t>「Mmm... shh... shh... hii~...」</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -2105,8 +2107,7 @@
       </c>
       <c r="B107" s="1" t="inlineStr">
         <is>
-          <t>When I left her alone, this time she started
-laughing.</t>
+          <t>When I left her be, she began laughing.</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -2121,7 +2122,7 @@
       </c>
       <c r="B108" s="1" t="inlineStr">
         <is>
-          <t>I wonder what kind of dream she's having？</t>
+          <t>I wonder what kind of dream Miru-chan is having?</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -2136,8 +2137,7 @@
       </c>
       <c r="B109" s="1" t="inlineStr">
         <is>
-          <t>Maybe she's dreaming about roughhousing with
-everyone？</t>
+          <t>I wonder if she's dreaming of playing with everyone?</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -2152,8 +2152,8 @@
       </c>
       <c r="B110" s="1" t="inlineStr">
         <is>
-          <t>...At the very least, I can tell that a little prank
-like this won't disturb Miru-chan's sleep.</t>
+          <t>...At the very least, I realized that a little prank
+like this wouldn't disturb Miru-chan's sleep.</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -2198,8 +2198,8 @@
       </c>
       <c r="B113" s="1" t="inlineStr">
         <is>
-          <t>...And now drool is starting to gather at the corner
-of her mouth.</t>
+          <t>...And drool was starting to drip from Miru-chan's
+mouth.</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="B114" s="1" t="inlineStr">
         <is>
-          <t>Oh well, this kid...！</t>
+          <t>Good grief, Miru-chan...!</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B117" s="1" t="inlineStr">
         <is>
-          <t>「Nn... ？ Nn, nnn~...」</t>
+          <t>「Nn…? Nn, nnn~…」</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -2275,9 +2275,10 @@
       </c>
       <c r="B118" s="1" t="inlineStr">
         <is>
-          <t>Unlike just pressing a little, tracing with my finger
-seems to give a different sensation, and she reacts
-with a puzzled sort of response.</t>
+          <t>Compared to the brief presses before, tracing my
+finger along Miru-chan's cheek apparently feels
+different to her, and she reacts with a slightly
+puzzled expression.</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -2323,7 +2324,7 @@
       </c>
       <c r="B121" s="1" t="inlineStr">
         <is>
-          <t>「Mmm... *smooch. smooch-smooch... smoo—*」</t>
+          <t>「Nn... chu. chu-chu... chuu~」</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -2354,8 +2355,8 @@
       </c>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>If you offer a finger and she ends up sucking on it,
-she’s like a little puppy.</t>
+          <t>If you offer a finger, Miru-chan will suck on it—just
+like a little puppy.</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -2370,7 +2371,7 @@
       </c>
       <c r="B124" s="1" t="inlineStr">
         <is>
-          <t>Ah... what an innocent reaction this is！</t>
+          <t>Ah... what an innocent reaction!</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -2400,7 +2401,7 @@
       </c>
       <c r="B126" s="1" t="inlineStr">
         <is>
-          <t>「*smooch, slurp, smooch-smooch, smoo~*」</t>
+          <t>「Chu, churu, chu-chu, chuu~...」</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -2415,8 +2416,8 @@
       </c>
       <c r="B127" s="1" t="inlineStr">
         <is>
-          <t>She was even sucking up the drool, making sounds like
-she was doing something she shouldn’t.</t>
+          <t>Miru-chan was even sucking up the drool too, making
+noises as if she were doing something naughty.</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -2446,7 +2447,8 @@
       </c>
       <c r="B129" s="1" t="inlineStr">
         <is>
-          <t>I smiled inwardly and stared at her intently.</t>
+          <t>I smiled to myself and watched her like that
+intently.</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -2491,8 +2493,8 @@
       </c>
       <c r="B132" s="1" t="inlineStr">
         <is>
-          <t>As if dreaming about sucking a tasty candy,
-Miru-chan’s drool wouldn’t stop.</t>
+          <t>Miru-chan's drool doesn't stop, as if she's dreaming
+about sucking on a delicious candy.</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -2507,8 +2509,8 @@
       </c>
       <c r="B133" s="1" t="inlineStr">
         <is>
-          <t>Because of that, the wet sounds took on more and more
-of a sticky quality.</t>
+          <t>Because of that, the sound of the liquid became
+increasingly thick and sticky.</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -2538,7 +2540,7 @@
       </c>
       <c r="B135" s="1" t="inlineStr">
         <is>
-          <t>「Nn！ Nnnu... chuku！ Chu, chu！ Nn！ Nfuh, nn...！」</t>
+          <t>「Nn! Nnnu... chuku! chu, chu! Nn! nfu, nn...!」</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -2568,9 +2570,8 @@
       </c>
       <c r="B137" s="1" t="inlineStr">
         <is>
-          <t>Maybe because she was sucking in her sleep, she
-couldn’t breathe properly between breaths...
-probably.</t>
+          <t>She might not be able to breathe properly because
+she's sucking while asleep... probably.</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -2585,7 +2586,7 @@
       </c>
       <c r="B138" s="1" t="inlineStr">
         <is>
-          <t>Or maybe her dream had switched to something else...？</t>
+          <t>Or maybe she's switched to a different dream...?</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -2647,7 +2648,7 @@
       </c>
       <c r="B142" s="1" t="inlineStr">
         <is>
-          <t>「Nn！ Nnnu... nfuh, nn... nnuuu...」</t>
+          <t>「Nn! Nnnu... nfu, nn... nnuuu...」</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -2662,8 +2663,9 @@
       </c>
       <c r="B143" s="1" t="inlineStr">
         <is>
-          <t>...Maybe it’s my imagination, but Miru-chan’s
-breathing sounded more sultry... I thought.</t>
+          <t>...Maybe it's just my imagination, but Miru-chan's
+breathing seems to have become more sultry... I
+think.</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -2708,7 +2710,7 @@
       </c>
       <c r="B146" s="1" t="inlineStr">
         <is>
-          <t>I thought that and gently withdrew my finger.</t>
+          <t>Thinking that, I gently pulled my finger out.</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -2738,7 +2740,7 @@
       </c>
       <c r="B148" s="1" t="inlineStr">
         <is>
-          <t>「Nn... pwah... ah, nnnu...」</t>
+          <t>「Nn... pwah... ah, Nnnu...」</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -2783,8 +2785,8 @@
       </c>
       <c r="B151" s="1" t="inlineStr">
         <is>
-          <t>When I pulled my finger away, Miru-chan’s sleeping
-breaths returned to normal.</t>
+          <t>When I withdrew my finger, Miru-chan's breathing
+returned to normal.</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -2799,7 +2801,7 @@
       </c>
       <c r="B152" s="1" t="inlineStr">
         <is>
-          <t>So maybe she really was having trouble.</t>
+          <t>I guess she really was having trouble breathing.</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -2829,7 +2831,7 @@
       </c>
       <c r="B154" s="1" t="inlineStr">
         <is>
-          <t>「Suu~... suu... nn, nn, nn...」</t>
+          <t>「suu~... suu... nn, nn, nn...」</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -2844,8 +2846,8 @@
       </c>
       <c r="B155" s="1" t="inlineStr">
         <is>
-          <t>Contrary to my feeling of having done something a
-little bad, Miru-chan’s breaths grew more heated.</t>
+          <t>Contrary to my thought that I'd done something a
+little wrong, Miru-chan's breathing grew more heated.</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -2860,7 +2862,7 @@
       </c>
       <c r="B156" s="1" t="inlineStr">
         <is>
-          <t>No！ That’s just my misunderstanding.</t>
+          <t>No — I'm mistaken.</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -2876,8 +2878,8 @@
       <c r="B157" s="1" t="inlineStr">
         <is>
           <t>Earlier, I thought Miru-chan's breathing sounded
-sultry... that lingering feeling's spawning these
-wicked thoughts！</t>
+sultry... that lingering feeling is what gives rise
+to these impure thoughts!</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -2907,7 +2909,7 @@
       </c>
       <c r="B159" s="1" t="inlineStr">
         <is>
-          <t>「nng… nnu… nn… nfu…」</t>
+          <t>「Nn… nnu… nn… nfu…」</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -2922,7 +2924,7 @@
       </c>
       <c r="B160" s="1" t="inlineStr">
         <is>
-          <t>…No, it's definitely kind of feverish after all.</t>
+          <t>…No—Miru-chan does seem a little feverish after all.</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -2982,7 +2984,7 @@
       </c>
       <c r="B164" s="1" t="inlineStr">
         <is>
-          <t>I realized my own body was all warm and tingly.</t>
+          <t>I realized my body felt warm all over.</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -3029,7 +3031,7 @@
       </c>
       <c r="B167" s="1" t="inlineStr">
         <is>
-          <t>A man's core…</t>
+          <t>The core of my manhood...</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -3059,7 +3061,7 @@
       </c>
       <c r="B169" s="1" t="inlineStr">
         <is>
-          <t>「faa, nnya… aaah…」</t>
+          <t>「Fah... nnh... aaah...」</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -3105,7 +3107,7 @@
       </c>
       <c r="B172" s="1" t="inlineStr">
         <is>
-          <t>「nii, hyan… dai… shukii…」</t>
+          <t>"Big brother... hyaa... I love you so much..."</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -3120,8 +3122,8 @@
       </c>
       <c r="B173" s="1" t="inlineStr">
         <is>
-          <t>…Staring quietly at Miru-chan's reactions, words I
-hadn't expected slipped out.</t>
+          <t>As I watched Miru-chan's reactions intently,
+unexpected words slipped out.</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -3166,7 +3168,7 @@
       </c>
       <c r="B176" s="1" t="inlineStr">
         <is>
-          <t>「fuhi！ fu… fufufu…！」</t>
+          <t>「Heh! Huh… heh heh heh…！」</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -3196,7 +3198,7 @@
       </c>
       <c r="B178" s="1" t="inlineStr">
         <is>
-          <t>She says she loves me while she's laughing.</t>
+          <t>Miru-chan is laughing while saying she loves me.</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -3241,7 +3243,7 @@
       </c>
       <c r="B181" s="1" t="inlineStr">
         <is>
-          <t>Suddenly swept up, I couldn't help but lean my face
+          <t>Carried away, I couldn't help but bring my face
 closer to Miru-chan.</t>
         </is>
       </c>
@@ -3257,8 +3259,8 @@
       </c>
       <c r="B182" s="1" t="inlineStr">
         <is>
-          <t>Her face was right in front of me… her lips closing
-in.</t>
+          <t>Miru-chan's face was right in front of me... her lips
+drew close.</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -3288,7 +3290,7 @@
       </c>
       <c r="B184" s="1" t="inlineStr">
         <is>
-          <t>「suu… suu… suu…」</t>
+          <t>「Suu... suu... suu...」</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -3303,8 +3305,8 @@
       </c>
       <c r="B185" s="1" t="inlineStr">
         <is>
-          <t>Even though it's only a few centimeters, I can feel
-her breathing so close.</t>
+          <t>Even though we're only a few centimeters apart... I
+can even feel her breathing right next to me.</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -3319,7 +3321,7 @@
       </c>
       <c r="B186" s="1" t="inlineStr">
         <is>
-          <t>Okay, just… kiss her.</t>
+          <t>Come on... just kiss her.</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -3349,7 +3351,7 @@
       </c>
       <c r="B188" s="1" t="inlineStr">
         <is>
-          <t>「n… nn… nfu~…」</t>
+          <t>「Mmm... mmm... mfu~...」</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -3379,9 +3381,9 @@
       </c>
       <c r="B190" s="1" t="inlineStr">
         <is>
-          <t>Because she was asleep, it was probably harder for
-her to exhale, but there was also the thing earlier
-where she latched onto my finger.</t>
+          <t>Because Miru-chan was asleep, it was probably harder
+for her to exhale, and there was also the matter of
+her having just sucked on my finger.</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -3397,7 +3399,8 @@
       <c r="B191" s="1" t="inlineStr">
         <is>
           <t>Right now our lips are touching, so it's like this,
-but if she stuck her tongue out, maybe…？</t>
+but if Miru-chan were to stick out her tongue...
+could it be...?</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -3427,7 +3430,7 @@
       </c>
       <c r="B193" s="1" t="inlineStr">
         <is>
-          <t>「Nn… ah… chu, chu chu… chu—」</t>
+          <t>「Mmm… ahn… smooch, smooch… smooch—」</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -3442,7 +3445,7 @@
       </c>
       <c r="B194" s="1" t="inlineStr">
         <is>
-          <t>U-ugh… she's, she's sucking on it…！</t>
+          <t>U-ugh… s-she's sucking on it…!</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -3473,7 +3476,7 @@
       </c>
       <c r="B196" s="1" t="inlineStr">
         <is>
-          <t>So soft… unbelievably soft.</t>
+          <t>S-so soft… incredibly soft.</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -3503,7 +3506,7 @@
       </c>
       <c r="B198" s="1" t="inlineStr">
         <is>
-          <t>「Chu, chu chu！ Chuu—…」</t>
+          <t>「Smooch, smooch! Smooch—…」</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -3533,7 +3536,7 @@
       </c>
       <c r="B200" s="1" t="inlineStr">
         <is>
-          <t>「...？!　...!」</t>
+          <t>…? …!</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -3548,7 +3551,7 @@
       </c>
       <c r="B201" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan kept suckling on my tongue and wouldn't let
+          <t>Miru-chan kept sucking on my tongue and wouldn't let
 go.</t>
         </is>
       </c>
@@ -3564,8 +3567,8 @@
       </c>
       <c r="B202" s="1" t="inlineStr">
         <is>
-          <t>Putting that aside, it's painful to keep my tongue
-stuck out like this.</t>
+          <t>Putting that aside, it's uncomfortable to keep my
+tongue sticking out.</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -3580,7 +3583,7 @@
       </c>
       <c r="B203" s="1" t="inlineStr">
         <is>
-          <t>I'm the one who feels like I'm about to suffocate…！</t>
+          <t>I'm the one who's about to have trouble breathing…!</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -3610,7 +3613,7 @@
       </c>
       <c r="B205" s="1" t="inlineStr">
         <is>
-          <t>「Chuk! Chu, churu! Nn! Chuu!」</t>
+          <t>「Smooch, smooch! Smooch~! Pwaaah!」</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -3640,8 +3643,8 @@
       </c>
       <c r="B207" s="1" t="inlineStr">
         <is>
-          <t>I tried to pull my tongue back during that moment,
-but I became unable to move.</t>
+          <t>At that moment I tried to pull my tongue back, but I
+couldn't move.</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -3656,7 +3659,7 @@
       </c>
       <c r="B208" s="1" t="inlineStr">
         <is>
-          <t>I'd seen it…</t>
+          <t>I couldn't help seeing it…</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -3671,8 +3674,8 @@
       </c>
       <c r="B209" s="1" t="inlineStr">
         <is>
-          <t>Our saliva, glinting, stretching into a string
-between her upper and lower lips…</t>
+          <t>Miru-chan's and my saliva glinted, stretching into a
+thread between our lips…</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -3702,8 +3705,8 @@
       </c>
       <c r="B211" s="1" t="inlineStr">
         <is>
-          <t>My hardening penis from getting turned on is
-unbearable！</t>
+          <t>My penis getting hard from being so horny is
+unbearable!</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -3733,7 +3736,7 @@
       </c>
       <c r="B213" s="1" t="inlineStr">
         <is>
-          <t>「Chuk！ Chu, churu！ Nn！ Chuu！」</t>
+          <t>"Smooch! S-sluurp! Nn! Smoooch!"</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -3763,7 +3766,7 @@
       </c>
       <c r="B215" s="1" t="inlineStr">
         <is>
-          <t>「Uah… ah…！」</t>
+          <t>「Uwa… ah…！」</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -3794,7 +3797,8 @@
       </c>
       <c r="B217" s="1" t="inlineStr">
         <is>
-          <t>My penis hurts but breathing is painful too….</t>
+          <t>My penis is uncomfortable, but I'm having trouble
+breathing too...</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -3824,7 +3828,7 @@
       </c>
       <c r="B219" s="1" t="inlineStr">
         <is>
-          <t>「Nn… nnuu… nmunmunmu…」</t>
+          <t>「Mmm... mmm... mmm-mm-mm...」</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -3869,7 +3873,7 @@
       </c>
       <c r="B222" s="1" t="inlineStr">
         <is>
-          <t>So, she started nibbling and licking my tongue.</t>
+          <t>Then she started nibbling at my tongue.</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -3884,8 +3888,8 @@
       </c>
       <c r="B223" s="1" t="inlineStr">
         <is>
-          <t>Aaah... the feeling of those soft lips, their strong
-springiness, was nibbling at my tongue...！</t>
+          <t>Aaaah... her soft lips, so incredibly springy, were
+nibbling my tongue...!</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -3900,7 +3904,7 @@
       </c>
       <c r="B224" s="1" t="inlineStr">
         <is>
-          <t>I-I can't... hold on anymore！</t>
+          <t>I-I can't take this anymore!</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -3930,7 +3934,7 @@
       </c>
       <c r="B226" s="1" t="inlineStr">
         <is>
-          <t>「U-uhh... uhaah！」</t>
+          <t>U-uu... uhaah!</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -3945,8 +3949,7 @@
       </c>
       <c r="B227" s="1" t="inlineStr">
         <is>
-          <t>I let out a big breath and shoved my hand into my
-pants.</t>
+          <t>I exhaled deeply and shoved my hand into my pants.</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -3991,7 +3994,8 @@
       </c>
       <c r="B230" s="1" t="inlineStr">
         <is>
-          <t>「Hamu, nngh... chu, chuchu, chuu！」</t>
+          <t>「Mmm... nngh... nibble, smooch, smooch-smooch,
+smooch!」</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -4021,7 +4025,7 @@
       </c>
       <c r="B232" s="1" t="inlineStr">
         <is>
-          <t>「Uah... ah, chu, chu！」</t>
+          <t>「Uah... ah, smooch, smooch！」</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -4052,8 +4056,9 @@
       </c>
       <c r="B234" s="1" t="inlineStr">
         <is>
-          <t>Taking advantage of that, I matched my tongue
-movements to hers and started using my tongue too.</t>
+          <t>Seizing the opportunity, I matched my tongue
+movements to Miru-chan's and began using mine as
+well.</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -4099,7 +4104,7 @@
       </c>
       <c r="B237" s="1" t="inlineStr">
         <is>
-          <t>「Chu, chuchu！ Hehe, nnn... chu！」</t>
+          <t>「Smooch, smooch! Hehe, mmm... smooch!」</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -4129,7 +4134,7 @@
       </c>
       <c r="B239" s="1" t="inlineStr">
         <is>
-          <t>「Chu, ha... ah！」</t>
+          <t>「Smooch, ha... ah!」</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -4160,8 +4165,8 @@
       </c>
       <c r="B241" s="1" t="inlineStr">
         <is>
-          <t>My already rock-hard penis sent crazy sensations
-through me with just a single stroke.</t>
+          <t>My already rock-hard penis gave me intense sensations
+even from just a single stroke.</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -4207,7 +4212,7 @@
       </c>
       <c r="B244" s="1" t="inlineStr">
         <is>
-          <t>「Nnngh... chu, chu！ Chuchu！ Juu！」</t>
+          <t>「Mmm... smooch, smooch! Smooch-smooch! dju!」</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -4222,10 +4227,10 @@
       </c>
       <c r="B245" s="1" t="inlineStr">
         <is>
-          <t>The sounds of our tongues and mucous membranes
-touching, mixed with drool dripping from the corners
-of our mouths, made everything feel even more
-lascivious.</t>
+          <t>The sound of our tongues' mucous membranes touching,
+intertwined with drool dripping from the corners of
+our mouths, turned it into something even more
+erotic.</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -4300,7 +4305,8 @@
       </c>
       <c r="B250" s="1" t="inlineStr">
         <is>
-          <t>「Chuchu！ Chuk！ Chu！ Jupu... chuchuu~！」</t>
+          <t>「Smooch-smooch! Schk! Smooch! Slurp...
+smooch-smooch~!」</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -4330,7 +4336,7 @@
       </c>
       <c r="B252" s="1" t="inlineStr">
         <is>
-          <t>「Fuhah...！」</t>
+          <t>「Haaah...!」</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -4360,7 +4366,7 @@
       </c>
       <c r="B254" s="1" t="inlineStr">
         <is>
-          <t>Prrt！　Prr-prrt！　Pruuu~！</t>
+          <t>Spurt! Spurt-spurt! Spuuuuurt!</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -4390,7 +4396,7 @@
       </c>
       <c r="B256" s="1" t="inlineStr">
         <is>
-          <t>「Hohe… ah… he…」</t>
+          <t>「Hoh... ah... heh...」</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -4405,7 +4411,7 @@
       </c>
       <c r="B257" s="1" t="inlineStr">
         <is>
-          <t>I- I came while kissing Miru-chan…</t>
+          <t>I- I came while smooching Miru-chan…</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -4435,7 +4441,7 @@
       </c>
       <c r="B259" s="1" t="inlineStr">
         <is>
-          <t>「Ah… pft, nn-ya, nnn~…」</t>
+          <t>「Ah... pft, nya, nnn~...」</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -4450,8 +4456,8 @@
       </c>
       <c r="B260" s="1" t="inlineStr">
         <is>
-          <t>When I pulled my face away without thinking,
-Miru-chan smiled satisﬁedly.</t>
+          <t>When I instinctively pulled my face away, Miru-chan
+smiled contentedly.</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -4466,8 +4472,8 @@
       </c>
       <c r="B261" s="1" t="inlineStr">
         <is>
-          <t>Her tongue had been tormenting me so much that I came
-without even properly stroking myself.</t>
+          <t>Miru-chan's tongue had been tormenting me so much
+that I came without even properly stroking myself.</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -4529,7 +4535,7 @@
       </c>
       <c r="B265" s="1" t="inlineStr">
         <is>
-          <t>「Suu~… suu~… suu~…」</t>
+          <t>「Soft, steady breathing…」</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -4544,7 +4550,7 @@
       </c>
       <c r="B266" s="1" t="inlineStr">
         <is>
-          <t>Watching her closely after pulling my face away,
+          <t>When I pulled my face away and watched her,
 Miru-chan's breathing grew deeper.</t>
         </is>
       </c>
@@ -4560,9 +4566,9 @@
       </c>
       <c r="B267" s="1" t="inlineStr">
         <is>
-          <t>Earlier she was responding in her sleep to my
-teasing, but now it feels like she's drifted into a
-deep sleep.</t>
+          <t>Until just a moment ago Miru-chan was responding to
+my teasing even while asleep, but now it feels like
+she's fallen into a deep sleep.</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -4577,8 +4583,8 @@
       </c>
       <c r="B268" s="1" t="inlineStr">
         <is>
-          <t>I guess it’s probably been so long that she probably
-isn’t even dreaming anymore.</t>
+          <t>By now, Miru-chan is probably not even dreaming
+anymore.</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -4609,7 +4615,7 @@
       </c>
       <c r="B270" s="1" t="inlineStr">
         <is>
-          <t>I thought so, and I lifted my hips.</t>
+          <t>Thinking that, I pushed myself up.</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -4624,7 +4630,7 @@
       </c>
       <c r="B271" s="1" t="inlineStr">
         <is>
-          <t>Ugh... semen is dripping inside my pants and it feels
+          <t>Ugh... semen's dripping into my pants; it's
 disgusting.</t>
         </is>
       </c>
@@ -4640,8 +4646,8 @@
       </c>
       <c r="B272" s="1" t="inlineStr">
         <is>
-          <t>I thought it was just a little prank, but she totally
-got me back...</t>
+          <t>I thought it was just a little prank, but Miru-chan
+totally got me back...</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -4656,7 +4662,7 @@
       </c>
       <c r="B273" s="1" t="inlineStr">
         <is>
-          <t>You really can't beat a girl at that.</t>
+          <t>Ugh... I can't win against girls.</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -4671,7 +4677,7 @@
       </c>
       <c r="B274" s="1" t="inlineStr">
         <is>
-          <t>...Yeah, I'm going to go see Rin-chan.</t>
+          <t>...Yeah. I'll go to Rin-chan's place.</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -4686,9 +4692,9 @@
       </c>
       <c r="B275" s="1" t="inlineStr">
         <is>
-          <t>Contrary to her usual sassy attitude, she's actually
-a shy, somewhat socially awkward, and kind of lonely
-girl...</t>
+          <t>Contrary to her usual sassy attitude, Miru-chan is
+actually bashful, shy around strangers, and easily
+gets lonely...</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -4718,8 +4724,8 @@
       </c>
       <c r="B277" s="1" t="inlineStr">
         <is>
-          <t>I'm so looking forward to how she'll react when I
-sleep next to her.</t>
+          <t>Besides, I'm dying to see how Rin-chan will react
+when I lie down next to her.</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -4734,8 +4740,8 @@
       </c>
       <c r="B278" s="1" t="inlineStr">
         <is>
-          <t>I'm sure she'll be all flustered in a way she usually
-isn't.</t>
+          <t>Rin-chan will probably end up all flustered, unlike
+usual.</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -4796,8 +4802,9 @@
       </c>
       <c r="B282" s="1" t="inlineStr">
         <is>
-          <t>I figured if I went to sleep beside Rin-chan she'd go
-all red and look so cute.</t>
+          <t>I couldn't help thinking that if I went to lie down
+next to Rin-chan, she'd flush bright red and be so
+cute.</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -4812,7 +4819,7 @@
       </c>
       <c r="B283" s="1" t="inlineStr">
         <is>
-          <t>Maybe she'd act all clingy to me…</t>
+          <t>Maybe she'd start acting clingy...</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -4858,8 +4865,8 @@
       </c>
       <c r="B286" s="1" t="inlineStr">
         <is>
-          <t>Then that girl-specific, sweet, milky scent hit my
-nose.</t>
+          <t>Then a cloyingly sweet, milky scent typical of girls
+wafted to my nose.</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -4904,8 +4911,8 @@
       </c>
       <c r="B289" s="1" t="inlineStr">
         <is>
-          <t>But the room light is off and there's no sign that
-Rin-chan is awake.</t>
+          <t>But the light in the room is off, and there's no sign
+that Rin-chan is awake.</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -4920,9 +4927,9 @@
       </c>
       <c r="B290" s="1" t="inlineStr">
         <is>
-          <t>Hmm… I might not get the snuggling reaction I
-pictured, but anyway I'll just take a look at her
-sleeping face.</t>
+          <t>Hmm… I might not get the reaction I pictured from
+lying next to her, but I'll at least take a look at
+Rin-chan's sleeping face.</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -4952,7 +4959,7 @@
       </c>
       <c r="B292" s="1" t="inlineStr">
         <is>
-          <t>「Suu…… suu……」</t>
+          <t>「suu…… suu……」</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -4967,7 +4974,7 @@
       </c>
       <c r="B293" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan was quietly breathing in the futon.</t>
+          <t>Rin-chan lay in her futon, breathing softly.</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -4982,7 +4989,7 @@
       </c>
       <c r="B294" s="1" t="inlineStr">
         <is>
-          <t>Ah… she's already fallen asleep, huh….</t>
+          <t>Ah… Rin-chan's already fallen asleep, huh…</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -5013,7 +5020,8 @@
       </c>
       <c r="B296" s="1" t="inlineStr">
         <is>
-          <t>At least I'll just look at her sleeping face.</t>
+          <t>At least I'll take a look at Rin-chan's sleeping
+face.</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -5028,7 +5036,7 @@
       </c>
       <c r="B297" s="1" t="inlineStr">
         <is>
-          <t>I rested my face by the side of the bed and stared at
+          <t>I leaned over the side of Rin-chan's bed and gazed at
 her sleeping face.</t>
         </is>
       </c>
@@ -5089,9 +5097,10 @@
       </c>
       <c r="B301" s="1" t="inlineStr">
         <is>
-          <t>When she's awake she has that sharp-eyed, sassy vibe,
-but right now she has an age-appropriate innocent
-expression.</t>
+          <t>When Rin-chan is awake she tends to have slanted eyes
+and gives off a cheeky, impertinent air, but right
+now her expression is an innocent, age-appropriate
+one.</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -5121,7 +5130,7 @@
       </c>
       <c r="B303" s="1" t="inlineStr">
         <is>
-          <t>「Suu………n, nnn… suu…」</t>
+          <t>「suu………n, nnn… suu…」</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -5136,7 +5145,7 @@
       </c>
       <c r="B304" s="1" t="inlineStr">
         <is>
-          <t>Even the way she grunts now and then is innocent.</t>
+          <t>Even Rin-chan's occasional murmurs sound innocent.</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -5167,7 +5176,7 @@
       </c>
       <c r="B306" s="1" t="inlineStr">
         <is>
-          <t>I want to keep staring at it forever….</t>
+          <t>I could stare at her forever...</t>
         </is>
       </c>
       <c r="C306" t="n">
@@ -5182,7 +5191,7 @@
       </c>
       <c r="B307" s="1" t="inlineStr">
         <is>
-          <t>But it’s not like I hate Rin-chan as she usually is.</t>
+          <t>But it's not that I dislike the usual Rin-chan.</t>
         </is>
       </c>
       <c r="C307" t="n">
@@ -5197,9 +5206,9 @@
       </c>
       <c r="B308" s="1" t="inlineStr">
         <is>
-          <t>She’s usually cheeky and sharp-tongued, messing me
-about, but she can be shy and easily frightened,
-which is kind of cute.</t>
+          <t>Rin-chan is usually cheeky and sharp-tongued, toying
+with me, but she also has cute sides—like being shy
+or easily frightened.</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -5214,7 +5223,7 @@
       </c>
       <c r="B309" s="1" t="inlineStr">
         <is>
-          <t>That gap grips my heart tight and won't let go.</t>
+          <t>That contrast grips my heart and won't let go.</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -5244,9 +5253,9 @@
       </c>
       <c r="B311" s="1" t="inlineStr">
         <is>
-          <t>Seeing such an innocent sleeping face, which I could
-never imagine from her usual self, what else could I
-do but dote on her？</t>
+          <t>Seeing Rin-chan's innocent sleeping face — something
+I could never have imagined from her usual self —
+what else could I do but dote on her?</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -5261,8 +5270,8 @@
       </c>
       <c r="B312" s="1" t="inlineStr">
         <is>
-          <t>I couldn't even go so far as to play a prank on her
-as payback...</t>
+          <t>I couldn't even play a prank on Rin-chan in return
+like I usually would.</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -5307,7 +5316,7 @@
       </c>
       <c r="B315" s="1" t="inlineStr">
         <is>
-          <t>「Suu... suu... suu...！」</t>
+          <t>「(inhale... inhale... inhale...!)」</t>
         </is>
       </c>
       <c r="C315" t="n">
@@ -5322,8 +5331,8 @@
       </c>
       <c r="B316" s="1" t="inlineStr">
         <is>
-          <t>As I kept watching, Rin-chan let out a hot little
-sigh.</t>
+          <t>As I continued to gaze at her, Rin-chan let out a
+warm sigh.</t>
         </is>
       </c>
       <c r="C316" t="n">
@@ -5338,8 +5347,8 @@
       </c>
       <c r="B317" s="1" t="inlineStr">
         <is>
-          <t>It was as if she were embarrassed at catching my
-gaze.</t>
+          <t>It was as if Rin-chan had noticed my gaze and was
+embarrassed.</t>
         </is>
       </c>
       <c r="C317" t="n">
@@ -5370,9 +5379,8 @@
       </c>
       <c r="B319" s="1" t="inlineStr">
         <is>
-          <t>...But Rin-chan has that kind of quick intuition that
-makes me think she might, and that's one of the
-things that teases me.</t>
+          <t>...but Rin-chan is perceptive enough to make me think
+so, and that's another reason she toys with me.</t>
         </is>
       </c>
       <c r="C319" t="n">
@@ -5433,7 +5441,7 @@
       </c>
       <c r="B323" s="1" t="inlineStr">
         <is>
-          <t>「Nnnu... suu... suu...」</t>
+          <t>「(mmm... inhale... inhale...)」</t>
         </is>
       </c>
       <c r="C323" t="n">
@@ -5448,8 +5456,8 @@
       </c>
       <c r="B324" s="1" t="inlineStr">
         <is>
-          <t>It only reacted for the moment I poked it with a
-squish, but her deep breathing didn't change.</t>
+          <t>Rin-chan's cheek only gave a tiny reaction when I
+poked it, but her deep breathing didn't change.</t>
         </is>
       </c>
       <c r="C324" t="n">
@@ -5525,8 +5533,8 @@
       </c>
       <c r="B329" s="1" t="inlineStr">
         <is>
-          <t>I was only supposed to admire her, but would it be so
-bad if I played a little prank？</t>
+          <t>I was only supposed to dote on her, but would it be
+okay if I tried pulling a little prank?</t>
         </is>
       </c>
       <c r="C329" t="n">
@@ -5541,8 +5549,9 @@
       </c>
       <c r="B330" s="1" t="inlineStr">
         <is>
-          <t>I can't violate that innocent sleeping face, and I
-don't intend to do anything that would wake her up...</t>
+          <t>I can't bring myself to disturb that innocent
+sleeping face, and I don't intend to play any prank
+that would wake her up...</t>
         </is>
       </c>
       <c r="C330" t="n">
@@ -5557,7 +5566,7 @@
       </c>
       <c r="B331" s="1" t="inlineStr">
         <is>
-          <t>Yeah, just a little... just a tiny, light touch...</t>
+          <t>Yes... just a little... just a light touch...</t>
         </is>
       </c>
       <c r="C331" t="n">
@@ -5618,7 +5627,7 @@
       </c>
       <c r="B335" s="1" t="inlineStr">
         <is>
-          <t>「Suu…………n, pu」</t>
+          <t>「(inhale... mmm, pfft)」</t>
         </is>
       </c>
       <c r="C335" t="n">
@@ -5634,7 +5643,7 @@
       <c r="B336" s="1" t="inlineStr">
         <is>
           <t>When my finger touched her lips, Rin-chan's mouth
-popped open from the bounce.</t>
+popped open reflexively.</t>
         </is>
       </c>
       <c r="C336" t="n">
@@ -5665,8 +5674,8 @@
       </c>
       <c r="B338" s="1" t="inlineStr">
         <is>
-          <t>...It's such a trivial thing, but it weirdly turned
-me on.</t>
+          <t>...It's such a trivial thing, but it makes me
+strangely aroused.</t>
         </is>
       </c>
       <c r="C338" t="n">
@@ -5696,8 +5705,8 @@
       </c>
       <c r="B340" s="1" t="inlineStr">
         <is>
-          <t>No, that's not it. These half-open lips are those of
-a girl waiting for a kiss...！</t>
+          <t>No, that's not it. These half-parted lips belong to a
+girl waiting for a kiss...!</t>
         </is>
       </c>
       <c r="C340" t="n">
@@ -5727,7 +5736,7 @@
       </c>
       <c r="B342" s="1" t="inlineStr">
         <is>
-          <t>「Suu~………… suu~……」</t>
+          <t>「(inhale... inhale...)」</t>
         </is>
       </c>
       <c r="C342" t="n">
@@ -5758,8 +5767,8 @@
       </c>
       <c r="B344" s="1" t="inlineStr">
         <is>
-          <t>...And since I can't stop thinking about kissing her,
-even that sounds provocative to me.</t>
+          <t>Now that I'm aware of the idea of a kiss, even that
+strikes me as provocative.</t>
         </is>
       </c>
       <c r="C344" t="n">
@@ -5851,7 +5860,7 @@
       </c>
       <c r="B350" s="1" t="inlineStr">
         <is>
-          <t>Yeah, just a little, just a tiny bit...</t>
+          <t>Yes... just a little, just a tiny bit...</t>
         </is>
       </c>
       <c r="C350" t="n">
@@ -5912,7 +5921,7 @@
       </c>
       <c r="B354" s="1" t="inlineStr">
         <is>
-          <t>That's how it is now.</t>
+          <t>That's how it is for now.</t>
         </is>
       </c>
       <c r="C354" t="n">
@@ -5927,7 +5936,7 @@
       </c>
       <c r="B355" s="1" t="inlineStr">
         <is>
-          <t>About to kiss Rin-chan... right？</t>
+          <t>Was I about to kiss Rin-chan...?</t>
         </is>
       </c>
       <c r="C355" t="n">
@@ -5972,7 +5981,7 @@
       </c>
       <c r="B358" s="1" t="inlineStr">
         <is>
-          <t>「suu... suu... fuh」</t>
+          <t>「(inhale... inhale... huff)」</t>
         </is>
       </c>
       <c r="C358" t="n">
@@ -6003,7 +6012,7 @@
       </c>
       <c r="B360" s="1" t="inlineStr">
         <is>
-          <t>O-okay... just a little...</t>
+          <t>A-alright... just a little...</t>
         </is>
       </c>
       <c r="C360" t="n">
@@ -6018,8 +6027,8 @@
       </c>
       <c r="B361" s="1" t="inlineStr">
         <is>
-          <t>I focused on keeping my heartbeat down and moved my
-face closer to Rin-chan's...</t>
+          <t>I consciously suppressed my racing heart and brought
+my face closer to Rin-chan's...</t>
         </is>
       </c>
       <c r="C361" t="n">
@@ -6049,7 +6058,7 @@
       </c>
       <c r="B363" s="1" t="inlineStr">
         <is>
-          <t>「suu... ah, nn...？」</t>
+          <t>「(inhale... nng...?)」</t>
         </is>
       </c>
       <c r="C363" t="n">
@@ -6064,7 +6073,7 @@
       </c>
       <c r="B364" s="1" t="inlineStr">
         <is>
-          <t>When our lips touched, her exhale changed.</t>
+          <t>When our lips met, her breath changed.</t>
         </is>
       </c>
       <c r="C364" t="n">
@@ -6079,8 +6088,9 @@
       </c>
       <c r="B365" s="1" t="inlineStr">
         <is>
-          <t>I thought that was natural, but I felt like there was
-some deliberate note to it...</t>
+          <t>I thought that was only natural, but I couldn't shake
+the feeling there was something intentional about
+it...</t>
         </is>
       </c>
       <c r="C365" t="n">
@@ -6155,7 +6165,7 @@
       </c>
       <c r="B370" s="1" t="inlineStr">
         <is>
-          <t>………………You woke up！？</t>
+          <t>………………She woke up!?</t>
         </is>
       </c>
       <c r="C370" t="n">
@@ -6277,7 +6287,7 @@
       </c>
       <c r="B378" s="1" t="inlineStr">
         <is>
-          <t>「W-what were you doing...？」</t>
+          <t>「W-what were you doing...?」</t>
         </is>
       </c>
       <c r="C378" t="n">
@@ -6430,8 +6440,8 @@
       </c>
       <c r="B388" s="1" t="inlineStr">
         <is>
-          <t>In situations like this, nothing looks lamer than an
-excuse that tries to defend yourself.</t>
+          <t>In a situation like this, nothing is more pathetic
+than a self-justifying excuse.</t>
         </is>
       </c>
       <c r="C388" t="n">
@@ -6613,7 +6623,7 @@
       </c>
       <c r="B400" s="1" t="inlineStr">
         <is>
-          <t>......Silence flowed.</t>
+          <t>......Silence fell.</t>
         </is>
       </c>
       <c r="C400" t="n">
@@ -6659,7 +6669,7 @@
       </c>
       <c r="B403" s="1" t="inlineStr">
         <is>
-          <t>「Um... are you angry？」</t>
+          <t>Um... are you angry?</t>
         </is>
       </c>
       <c r="C403" t="n">
@@ -6689,7 +6699,7 @@
       </c>
       <c r="B405" s="1" t="inlineStr">
         <is>
-          <t>「I'm not angry」</t>
+          <t>I'm not angry</t>
         </is>
       </c>
       <c r="C405" t="n">
@@ -6704,8 +6714,8 @@
       </c>
       <c r="B406" s="1" t="inlineStr">
         <is>
-          <t>While keeping my head lowered and watching, I was
-answered immediately in a curt tone.</t>
+          <t>Keeping my head bowed, I watched her; she replied
+immediately in a firm tone.</t>
         </is>
       </c>
       <c r="C406" t="n">
@@ -6750,7 +6760,8 @@
       </c>
       <c r="B409" s="1" t="inlineStr">
         <is>
-          <t>「...I guess it can't be helped... Niini is pervy.」</t>
+          <t>「...I guess it can't be helped... You're such a
+pervert, Niini.」</t>
         </is>
       </c>
       <c r="C409" t="n">
@@ -6795,7 +6806,7 @@
       </c>
       <c r="B412" s="1" t="inlineStr">
         <is>
-          <t>...Or so I thought, but I was easily forgiven？</t>
+          <t>...Or so I thought—was I forgiven that easily?</t>
         </is>
       </c>
       <c r="C412" t="n">
@@ -6840,7 +6851,7 @@
       </c>
       <c r="B415" s="1" t="inlineStr">
         <is>
-          <t>...She lifts her face while apologizing.</t>
+          <t>I raised my head while apologizing.</t>
         </is>
       </c>
       <c r="C415" t="n">
@@ -6886,7 +6897,7 @@
       </c>
       <c r="B418" s="1" t="inlineStr">
         <is>
-          <t>「But it's a punishment game...right？」</t>
+          <t>"But it's a punishment game, you know?"</t>
         </is>
       </c>
       <c r="C418" t="n">
@@ -6946,7 +6957,7 @@
       </c>
       <c r="B422" s="1" t="inlineStr">
         <is>
-          <t>If I'm forgiven, I'll accept a little penalty.</t>
+          <t>If I'm forgiven, I'll accept any small penalty.</t>
         </is>
       </c>
       <c r="C422" t="n">
@@ -6961,7 +6972,7 @@
       </c>
       <c r="B423" s="1" t="inlineStr">
         <is>
-          <t>I wait for her decision with that mindset...</t>
+          <t>I wait for her decision in that state of mind...</t>
         </is>
       </c>
       <c r="C423" t="n">
@@ -6991,7 +7002,7 @@
       </c>
       <c r="B425" s="1" t="inlineStr">
         <is>
-          <t>「Then, the punishment game」</t>
+          <t>「Alright then—punishment game.」</t>
         </is>
       </c>
       <c r="C425" t="n">
@@ -7021,7 +7032,7 @@
       </c>
       <c r="B427" s="1" t="inlineStr">
         <is>
-          <t>「Again, shasee, show me.」</t>
+          <t>"Again—show me you cum."</t>
         </is>
       </c>
       <c r="C427" t="n">
@@ -7128,7 +7139,7 @@
       </c>
       <c r="B434" s="1" t="inlineStr">
         <is>
-          <t>「W-why, shasee...？」</t>
+          <t>「W-why...would I cum?」</t>
         </is>
       </c>
       <c r="C434" t="n">
@@ -7158,7 +7169,8 @@
       </c>
       <c r="B436" s="1" t="inlineStr">
         <is>
-          <t>「B-because Rin... lost to MiruMiru and Nono-chan...」</t>
+          <t>「B-because Rin... can't beat MiruMiru or
+Nono-chan...」</t>
         </is>
       </c>
       <c r="C436" t="n">
@@ -7203,7 +7215,8 @@
       </c>
       <c r="B439" s="1" t="inlineStr">
         <is>
-          <t>Ah...is the bath sex-ed lesson still lingering...?</t>
+          <t>Ah... Is the sex education from the bath still
+lingering...?</t>
         </is>
       </c>
       <c r="C439" t="n">
@@ -7326,8 +7339,8 @@
       </c>
       <c r="B447" s="1" t="inlineStr">
         <is>
-          <t>「...So when you say you want to see me ejaculate, do
-you mean you'll do it with your hand, Rin-chan？」</t>
+          <t>「...So when you say you want to see me cum, do you
+mean you'll do it by hand, Rin-chan?」</t>
         </is>
       </c>
       <c r="C447" t="n">
@@ -7357,7 +7370,7 @@
       </c>
       <c r="B449" s="1" t="inlineStr">
         <is>
-          <t>「No. I won't do that, okay？」</t>
+          <t>No, I won't.</t>
         </is>
       </c>
       <c r="C449" t="n">
@@ -7418,7 +7431,7 @@
       <c r="B453" s="1" t="inlineStr">
         <is>
           <t>「If you think you lost, doesn't that mean you want to
-challenge me again？」</t>
+try again?」</t>
         </is>
       </c>
       <c r="C453" t="n">
@@ -7448,7 +7461,7 @@
       </c>
       <c r="B455" s="1" t="inlineStr">
         <is>
-          <t>「N-no... that's embarrassing...」</t>
+          <t>I-it's embarrassing...</t>
         </is>
       </c>
       <c r="C455" t="n">
@@ -7463,7 +7476,7 @@
       </c>
       <c r="B456" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan said, turning her flushed face away.</t>
+          <t>Rin-chan said, turning away with a flushed face.</t>
         </is>
       </c>
       <c r="C456" t="n">
@@ -7493,7 +7506,7 @@
       </c>
       <c r="B458" s="1" t="inlineStr">
         <is>
-          <t>「Also, I can't do it as well as MiruMiru...」</t>
+          <t>「Besides, I'm not as good at it as MiruMiru...」</t>
         </is>
       </c>
       <c r="C458" t="n">
@@ -7553,8 +7566,8 @@
       </c>
       <c r="B462" s="1" t="inlineStr">
         <is>
-          <t>「Ugh... shut up. Niini should just quietly take the
-punishment.」</t>
+          <t>"Ugh... shut up. Niini should just obediently accept
+the punishment."</t>
         </is>
       </c>
       <c r="C462" t="n">
@@ -7569,8 +7582,8 @@
       </c>
       <c r="B463" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan said sharply but quietly, still looking
-annoyed.</t>
+          <t>Rin-chan, still wearing an annoyed expression,
+quietly admonished me.</t>
         </is>
       </c>
       <c r="C463" t="n">
@@ -7601,7 +7614,7 @@
       </c>
       <c r="B465" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan wanted something special.</t>
+          <t>Rin-chan wants to feel special.</t>
         </is>
       </c>
       <c r="C465" t="n">
@@ -7616,8 +7629,8 @@
       </c>
       <c r="B466" s="1" t="inlineStr">
         <is>
-          <t>She wanted to see a hidden act somewhere away from
-the others.</t>
+          <t>Rin-chan wants to see a private act in a place where
+no one else is around.</t>
         </is>
       </c>
       <c r="C466" t="n">
@@ -7632,8 +7645,9 @@
       </c>
       <c r="B467" s="1" t="inlineStr">
         <is>
-          <t>And since it didn't go well in the bath, she probably
-wanted to make up that disadvantage.</t>
+          <t>Besides, since Rin-chan didn't do it well in the
+bath, she probably also wants to make up for that
+disadvantage.</t>
         </is>
       </c>
       <c r="C467" t="n">
@@ -7663,7 +7677,7 @@
       </c>
       <c r="B469" s="1" t="inlineStr">
         <is>
-          <t>「...Then it's special, okay？」</t>
+          <t>「…Then it's special, okay?」</t>
         </is>
       </c>
       <c r="C469" t="n">
@@ -7693,7 +7707,7 @@
       </c>
       <c r="B471" s="1" t="inlineStr">
         <is>
-          <t>「Uh...okay！」</t>
+          <t>「Y-yeah!」</t>
         </is>
       </c>
       <c r="C471" t="n">
@@ -7739,7 +7753,7 @@
       </c>
       <c r="B474" s="1" t="inlineStr">
         <is>
-          <t>「Ah... but I kind of want something to go with it...」</t>
+          <t>Ah... but I kind of want something to get me going...</t>
         </is>
       </c>
       <c r="C474" t="n">
@@ -7769,7 +7783,7 @@
       </c>
       <c r="B476" s="1" t="inlineStr">
         <is>
-          <t>「...Rice？」</t>
+          <t>...Rice?</t>
         </is>
       </c>
       <c r="C476" t="n">
@@ -7784,8 +7798,8 @@
       </c>
       <c r="B477" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan, who didn't know what 'okazu' meant,
-frowned, thinking she'd been told something
+          <t>Rin-chan, not knowing what he meant by 'something to
+get him going,' frowned, thinking he'd said something
 completely unrelated.</t>
         </is>
       </c>
@@ -7862,8 +7876,8 @@
       </c>
       <c r="B482" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan let out a sigh and wrapped the towel blanket
-around her stomach.</t>
+          <t>Rin-chan let out a sigh and wrapped the towel around
+her stomach.</t>
         </is>
       </c>
       <c r="C482" t="n">
@@ -7878,7 +7892,8 @@
       </c>
       <c r="B483" s="1" t="inlineStr">
         <is>
-          <t>Then she was rustling around with something.</t>
+          <t>Then Rin-chan rustled around, fiddling with
+something.</t>
         </is>
       </c>
       <c r="C483" t="n">
@@ -7954,7 +7969,7 @@
       </c>
       <c r="B488" s="1" t="inlineStr">
         <is>
-          <t>「Here... you can have this.」</t>
+          <t>「Here... take this.」</t>
         </is>
       </c>
       <c r="C488" t="n">
@@ -8060,7 +8075,7 @@
       </c>
       <c r="B495" s="1" t="inlineStr">
         <is>
-          <t>「Even the manga Niini has often shows panties.」</t>
+          <t>Even the manga Niini owns often features panties.</t>
         </is>
       </c>
       <c r="C495" t="n">
@@ -8105,8 +8120,8 @@
       </c>
       <c r="B498" s="1" t="inlineStr">
         <is>
-          <t>Having way too many things come to mind, all I can do
-is nod obediently.</t>
+          <t>With far too many possibilities running through my
+head, I could do nothing but nod obediently.</t>
         </is>
       </c>
       <c r="C498" t="n">
@@ -8121,8 +8136,8 @@
       </c>
       <c r="B499" s="1" t="inlineStr">
         <is>
-          <t>...Or rather, she went into my room and read my manga
-without me knowing...？</t>
+          <t>...Or rather, Rin-chan went into my room and was
+reading my manga and stuff without me knowing...?</t>
         </is>
       </c>
       <c r="C499" t="n">
@@ -8167,7 +8182,7 @@
       </c>
       <c r="B502" s="1" t="inlineStr">
         <is>
-          <t>「B-But, can I use these panties？」</t>
+          <t>「B-But... can I use these panties?」</t>
         </is>
       </c>
       <c r="C502" t="n">
@@ -8272,7 +8287,7 @@
       </c>
       <c r="B509" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan kept rushing me like crazy.</t>
+          <t>Rin-chan was relentlessly urging me.</t>
         </is>
       </c>
       <c r="C509" t="n">
@@ -8287,9 +8302,10 @@
       </c>
       <c r="B510" s="1" t="inlineStr">
         <is>
-          <t>She was probably curious and embarrassed and feeling
-all sorts of things, but she didn’t seem to be
-thinking ahead about what would happen afterward.</t>
+          <t>Rin-chan was probably curious and embarrassed and
+feeling all sorts of complicated emotions, but she
+didn’t seem to be thinking ahead to what would happen
+afterward.</t>
         </is>
       </c>
       <c r="C510" t="n">
@@ -8304,8 +8320,8 @@
       </c>
       <c r="B511" s="1" t="inlineStr">
         <is>
-          <t>...What should I do？ Is it okay to sniff it, lick it,
-or put it on my face...？</t>
+          <t>...What should I do? Is it okay if I sniff it, lick
+it, or drape it over my face...?</t>
         </is>
       </c>
       <c r="C511" t="n">
@@ -8399,7 +8415,7 @@
       </c>
       <c r="B517" s="1" t="inlineStr">
         <is>
-          <t>「...Pff！」</t>
+          <t>「...Pfft!」</t>
         </is>
       </c>
       <c r="C517" t="n">
@@ -8430,9 +8446,9 @@
       </c>
       <c r="B519" s="1" t="inlineStr">
         <is>
-          <t>My gaze went under the towel blanket... and
-unbelievably, the area where Rin-chan’s thighs meet
-her body was completely exposed...</t>
+          <t>My gaze went under the towel blanket... and,
+unbelievably, the bases of both of Rin-chan's thighs
+were completely exposed...</t>
         </is>
       </c>
       <c r="C519" t="n">
@@ -8462,7 +8478,7 @@
       </c>
       <c r="B521" s="1" t="inlineStr">
         <is>
-          <t>「...Nn？」</t>
+          <t>「...Nn?」</t>
         </is>
       </c>
       <c r="C521" t="n">
@@ -8492,7 +8508,8 @@
       </c>
       <c r="B523" s="1" t="inlineStr">
         <is>
-          <t>It seemed she hadn’t realized her current posture.</t>
+          <t>Apparently Rin-chan hadn’t noticed the way she was
+sitting.</t>
         </is>
       </c>
       <c r="C523" t="n">
@@ -8507,8 +8524,8 @@
       </c>
       <c r="B524" s="1" t="inlineStr">
         <is>
-          <t>I’d seen her naked earlier in the bath, but never had
-that spot been so openly on display like this.</t>
+          <t>I’d seen Rin-chan naked in the bath earlier, but I’d
+never seen that area completely exposed like this.</t>
         </is>
       </c>
       <c r="C524" t="n">
@@ -8523,8 +8540,8 @@
       </c>
       <c r="B525" s="1" t="inlineStr">
         <is>
-          <t>...A plump little mound, with an innocent, single
-crease...！</t>
+          <t>...A plump, fleshy mound with a single
+innocent-looking crease...!</t>
         </is>
       </c>
       <c r="C525" t="n">
@@ -8554,7 +8571,7 @@
       </c>
       <c r="B527" s="1" t="inlineStr">
         <is>
-          <t>「Niini...！ What are you doing...？」</t>
+          <t>「Niini...! What are you doing...?」</t>
         </is>
       </c>
       <c r="C527" t="n">
@@ -8569,8 +8586,9 @@
       </c>
       <c r="B528" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan said in a slightly annoyed voice, hugging
-her knees with a faintly troubled expression.</t>
+          <t>Rin-chan spoke in a slightly annoyed tone, but she
+was hugging her knees with a somewhat troubled
+expression.</t>
         </is>
       </c>
       <c r="C528" t="n">
@@ -8648,8 +8666,8 @@
       </c>
       <c r="B533" s="1" t="inlineStr">
         <is>
-          <t>I kneeled in front of Rin-chan and pulled down my
-pants along with the panties.</t>
+          <t>I knelt in front of Rin-chan and pulled down her
+pants and panties.</t>
         </is>
       </c>
       <c r="C533" t="n">
@@ -8679,7 +8697,7 @@
       </c>
       <c r="B535" s="1" t="inlineStr">
         <is>
-          <t>「...!？!」</t>
+          <t>「...!?」</t>
         </is>
       </c>
       <c r="C535" t="n">
@@ -8694,7 +8712,7 @@
       </c>
       <c r="B536" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan widened her eyes and sucked in a breath.</t>
+          <t>Rin-chan widened her eyes and gasped.</t>
         </is>
       </c>
       <c r="C536" t="n">
@@ -8724,7 +8742,7 @@
       </c>
       <c r="B538" s="1" t="inlineStr">
         <is>
-          <t>「...They're already...so big...？」</t>
+          <t>「...It's already so big...?」</t>
         </is>
       </c>
       <c r="C538" t="n">
@@ -8784,9 +8802,9 @@
       </c>
       <c r="B542" s="1" t="inlineStr">
         <is>
-          <t>Just thinking that I had to masturbate in front of
-Rin-chan turned me on, and being handed her panties
-made it impossible for me to calm down.</t>
+          <t>I was already aroused just at the thought of having
+to masturbate in front of Rin-chan, and being handed
+her panties made it impossible for me to calm down.</t>
         </is>
       </c>
       <c r="C542" t="n">
@@ -8816,7 +8834,7 @@
       </c>
       <c r="B544" s="1" t="inlineStr">
         <is>
-          <t>「...They get like that from Rin's panties...」</t>
+          <t>「...It gets like that from Rin-chan's panties...」</t>
         </is>
       </c>
       <c r="C544" t="n">
@@ -8831,8 +8849,7 @@
       </c>
       <c r="B545" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan muttered while hiding her mouth with her
-knees.</t>
+          <t>Rin-chan murmured, hiding her mouth behind her knees.</t>
         </is>
       </c>
       <c r="C545" t="n">
@@ -8847,7 +8864,7 @@
       </c>
       <c r="B546" s="1" t="inlineStr">
         <is>
-          <t>She was probably trying to hide her shame.</t>
+          <t>She was probably trying to hide her embarrassment.</t>
         </is>
       </c>
       <c r="C546" t="n">
@@ -8862,8 +8879,8 @@
       </c>
       <c r="B547" s="1" t="inlineStr">
         <is>
-          <t>But naturally she curled her body, lifting her butt,
-which made that area even easier to see！</t>
+          <t>But she instinctively curled up, which raised her
+butt and made that area even easier to see!</t>
         </is>
       </c>
       <c r="C547" t="n">
@@ -8923,7 +8940,7 @@
       </c>
       <c r="B551" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan said with the same pouty tone as always.</t>
+          <t>Rin-chan snapped in her usual sulky tone.</t>
         </is>
       </c>
       <c r="C551" t="n">
@@ -8938,8 +8955,8 @@
       </c>
       <c r="B552" s="1" t="inlineStr">
         <is>
-          <t>Her embarrassment and the coldness she used to hide
-it...</t>
+          <t>Her embarrassment and the aloofness she put on to
+hide it...</t>
         </is>
       </c>
       <c r="C552" t="n">
@@ -8985,7 +9002,7 @@
       </c>
       <c r="B555" s="1" t="inlineStr">
         <is>
-          <t>「Ah...no, okay, I'm, I'm going...」</t>
+          <t>「Ah... no — okay, I-I'm going...」</t>
         </is>
       </c>
       <c r="C555" t="n">
@@ -9000,8 +9017,8 @@
       </c>
       <c r="B556" s="1" t="inlineStr">
         <is>
-          <t>I steeled myself, stayed on my knees, pushed my hips
-out, and put Rin-chan's panties over my penis.</t>
+          <t>I steeled myself, remained kneeling, thrust my hips
+forward, and placed Rin-chan's panties over my penis.</t>
         </is>
       </c>
       <c r="C556" t="n">
@@ -9062,9 +9079,9 @@
       </c>
       <c r="B560" s="1" t="inlineStr">
         <is>
-          <t>The soft fabric totally different from my own
-underwear. And the warmth of Rin-chan who had just
-been wearing them.</t>
+          <t>A soft fabric completely different from my own
+underwear — and the warmth left by Rin-chan, who had
+been wearing them until just now.</t>
         </is>
       </c>
       <c r="C560" t="n">
@@ -9079,8 +9096,8 @@
       </c>
       <c r="B561" s="1" t="inlineStr">
         <is>
-          <t>Yes, it was like a chick being wrapped in a parent
-bird's feathers.</t>
+          <t>It was as if a chick were being enveloped in its
+parent's feathers.</t>
         </is>
       </c>
       <c r="C561" t="n">
@@ -9144,7 +9161,7 @@
       </c>
       <c r="B565" s="1" t="inlineStr">
         <is>
-          <t>In that instant, I absentmindedly stroked my penis.</t>
+          <t>At that moment, I was mindlessly stroking my penis.</t>
         </is>
       </c>
       <c r="C565" t="n">
@@ -9174,7 +9191,7 @@
       </c>
       <c r="B567" s="1" t="inlineStr">
         <is>
-          <t>「Ah... so that's how you use it...？」</t>
+          <t>Ah... so that's how you use it...？</t>
         </is>
       </c>
       <c r="C567" t="n">
@@ -9250,7 +9267,7 @@
       </c>
       <c r="B572" s="1" t="inlineStr">
         <is>
-          <t>「...In manga, they’d sniff them...」</t>
+          <t>「...In manga, they'd go 'sniff sniff'...」</t>
         </is>
       </c>
       <c r="C572" t="n">
@@ -9295,9 +9312,8 @@
       </c>
       <c r="B575" s="1" t="inlineStr">
         <is>
-          <t>When it came down to it I thought I'd be so
-embarrassed I'd end up crying, but was kunkun okay
-with it？</t>
+          <t>I thought I'd be so embarrassed I'd end up crying
+when it came down to it, but sniffing was okay, huh?</t>
         </is>
       </c>
       <c r="C575" t="n">
@@ -9327,7 +9343,7 @@
       </c>
       <c r="B577" s="1" t="inlineStr">
         <is>
-          <t>「...So, can I sniff you？」</t>
+          <t>"...So, can I sniff it?"</t>
         </is>
       </c>
       <c r="C577" t="n">
@@ -9372,8 +9388,8 @@
       </c>
       <c r="B580" s="1" t="inlineStr">
         <is>
-          <t>When I tried baiting her, Rin-chan trembled and
-refused.</t>
+          <t>When I tried to tease her, Rin-chan's shoulders
+trembled as she refused.</t>
         </is>
       </c>
       <c r="C580" t="n">
@@ -9388,9 +9404,9 @@
       </c>
       <c r="B581" s="1" t="inlineStr">
         <is>
-          <t>True to her stubborn, cheeky self she handed over her
-panties, but she really hadn't thought about what
-would happen afterward, had she?</t>
+          <t>True to her stubborn, cheeky nature, Rin-chan handed
+me her panties, but as expected she hadn't thought
+about what would happen afterward.</t>
         </is>
       </c>
       <c r="C581" t="n">
@@ -9405,7 +9421,8 @@
       </c>
       <c r="B582" s="1" t="inlineStr">
         <is>
-          <t>…Good—I'm glad they didn't go sniffing and licking.</t>
+          <t>…Good — I'm glad Rin-chan didn't start sniffing and
+licking.</t>
         </is>
       </c>
       <c r="C582" t="n">
@@ -9420,8 +9437,8 @@
       </c>
       <c r="B583" s="1" t="inlineStr">
         <is>
-          <t>Putting that aside, it hurts that the hand that was
-moved by the panties stopped.</t>
+          <t>Putting that aside, it's annoying that my
+hand—stirred by the panties—came to a stop.</t>
         </is>
       </c>
       <c r="C583" t="n">
@@ -9436,8 +9453,9 @@
       </c>
       <c r="B584" s="1" t="inlineStr">
         <is>
-          <t>When I stopped and my mind started working, I
-realized I was doing something really embarrassing...</t>
+          <t>When I stopped my hand and my mind started working, I
+realized I was doing something incredibly
+embarrassing...</t>
         </is>
       </c>
       <c r="C584" t="n">
@@ -9512,8 +9530,8 @@
       </c>
       <c r="B589" s="1" t="inlineStr">
         <is>
-          <t>I stayed completely still, and was quietly urged on
-with few words.</t>
+          <t>I couldn't move at all; she urged me on with terse
+words.</t>
         </is>
       </c>
       <c r="C589" t="n">
@@ -9558,8 +9576,8 @@
       </c>
       <c r="B592" s="1" t="inlineStr">
         <is>
-          <t>I immediately start thinking up excuses, but before
-that I realize I’d forgotten something important.</t>
+          <t>I instinctively start thinking up excuses, but I'd
+already forgotten something important.</t>
         </is>
       </c>
       <c r="C592" t="n">
@@ -9574,8 +9592,8 @@
       </c>
       <c r="B593" s="1" t="inlineStr">
         <is>
-          <t>When I look straight ahead, Rin-chan's cute slit
-comes into view.</t>
+          <t>When I looked straight at her, I caught sight of
+Rin-chan's cute little slit.</t>
         </is>
       </c>
       <c r="C593" t="n">
@@ -9590,7 +9608,7 @@
       </c>
       <c r="B594" s="1" t="inlineStr">
         <is>
-          <t>And of course that makes my penis tense up...！</t>
+          <t>And of course, my penis hardens...!</t>
         </is>
       </c>
       <c r="C594" t="n">
@@ -9665,7 +9683,7 @@
       </c>
       <c r="B599" s="1" t="inlineStr">
         <is>
-          <t>As I declared that and began stroking my penis,
+          <t>When I said that and began stroking my penis,
 Rin-chan nodded and curled her body up.</t>
         </is>
       </c>
@@ -9697,8 +9715,8 @@
       </c>
       <c r="B601" s="1" t="inlineStr">
         <is>
-          <t>And because she curls up, her butt sticks up, making
-that area easier to see — which doesn’t change.</t>
+          <t>Also, when she curls up her hips lift, making that
+area easier to see — that doesn't change.</t>
         </is>
       </c>
       <c r="C601" t="n">
@@ -9743,7 +9761,7 @@
       </c>
       <c r="B604" s="1" t="inlineStr">
         <is>
-          <t>「…!　……!」</t>
+          <t>「…! ……」</t>
         </is>
       </c>
       <c r="C604" t="n">
@@ -9773,7 +9791,7 @@
       </c>
       <c r="B606" s="1" t="inlineStr">
         <is>
-          <t>「Ah… u, fuu…!」</t>
+          <t>「Ah... uh... haa...」</t>
         </is>
       </c>
       <c r="C606" t="n">
@@ -9788,8 +9806,8 @@
       </c>
       <c r="B607" s="1" t="inlineStr">
         <is>
-          <t>Watching me stroke my penis in front of her, Rin-chan
-let out a muffled breath.</t>
+          <t>Rin-chan, watching me stroke my penis in front of
+her, let out a muffled sigh.</t>
         </is>
       </c>
       <c r="C607" t="n">
@@ -9804,7 +9822,8 @@
       </c>
       <c r="B608" s="1" t="inlineStr">
         <is>
-          <t>…Surely, just watching is embarrassing for her.</t>
+          <t>…Rin-chan is probably embarrassed just from being
+watched.</t>
         </is>
       </c>
       <c r="C608" t="n">
@@ -9819,8 +9838,8 @@
       </c>
       <c r="B609" s="1" t="inlineStr">
         <is>
-          <t>As proof, she fidgeted her feet and her gaze kept
-flitting away.</t>
+          <t>As further proof, she wriggled her feet and her gaze
+tended to wander.</t>
         </is>
       </c>
       <c r="C609" t="n">
@@ -9880,7 +9899,7 @@
       </c>
       <c r="B613" s="1" t="inlineStr">
         <is>
-          <t>「N…no…！」</t>
+          <t>「N-no…！」</t>
         </is>
       </c>
       <c r="C613" t="n">
@@ -9895,8 +9914,8 @@
       </c>
       <c r="B614" s="1" t="inlineStr">
         <is>
-          <t>If I called out to her so deliberately, Rin-chan
-reflexively refused.</t>
+          <t>If I were to call out to her so deliberately,
+Rin-chan would reflexively refuse.</t>
         </is>
       </c>
       <c r="C614" t="n">
@@ -9926,9 +9945,9 @@
       </c>
       <c r="B616" s="1" t="inlineStr">
         <is>
-          <t>While she fidgeted, her butt would drop and that area
-would become harder to see, but that’s also an
-accent.</t>
+          <t>As she kept fidgeting, her hips would sink and that
+area would become harder to see, but that, too, was
+part of the appeal.</t>
         </is>
       </c>
       <c r="C616" t="n">
@@ -9943,8 +9962,8 @@
       </c>
       <c r="B617" s="1" t="inlineStr">
         <is>
-          <t>It’s more exciting than having it exposed the whole
-time…！</t>
+          <t>This is more arousing than if it were visible the
+whole time…!</t>
         </is>
       </c>
       <c r="C617" t="n">
@@ -9974,8 +9993,8 @@
       </c>
       <c r="B619" s="1" t="inlineStr">
         <is>
-          <t>「Look, your panties feel so good my penis is
-twitching, Rin-chan.」</t>
+          <t>Look, Rin-chan — your panties feel so good that my
+penis is twitching, you know?</t>
         </is>
       </c>
       <c r="C619" t="n">
@@ -10005,7 +10024,7 @@
       </c>
       <c r="B621" s="1" t="inlineStr">
         <is>
-          <t>「…! …u, uuuu…!」</t>
+          <t>「…! …uuhhh…!」</t>
         </is>
       </c>
       <c r="C621" t="n">
@@ -10020,8 +10039,8 @@
       </c>
       <c r="B622" s="1" t="inlineStr">
         <is>
-          <t>When I provoked her like that, Rin-chan went beet-red
-and let out a thin groan.</t>
+          <t>When I deliberately called out to her, Rin-chan
+flushed bright red and let out a faint moan.</t>
         </is>
       </c>
       <c r="C622" t="n">
@@ -10036,8 +10055,8 @@
       </c>
       <c r="B623" s="1" t="inlineStr">
         <is>
-          <t>She then curled up again, and as a result that area
-became easier to see.</t>
+          <t>She curled up again, which made it easier to see down
+there.</t>
         </is>
       </c>
       <c r="C623" t="n">
@@ -10067,7 +10086,7 @@
       </c>
       <c r="B625" s="1" t="inlineStr">
         <is>
-          <t>「Ah, ah… it feels good… your panties, Rin-chan.」</t>
+          <t>「Ah, ah… your panties feel so good, Rin-chan.」</t>
         </is>
       </c>
       <c r="C625" t="n">
@@ -10097,7 +10116,7 @@
       </c>
       <c r="B627" s="1" t="inlineStr">
         <is>
-          <t>「Id…idiot…！」</t>
+          <t>「Y-you idiot...!」</t>
         </is>
       </c>
       <c r="C627" t="n">
@@ -10112,8 +10131,8 @@
       </c>
       <c r="B628" s="1" t="inlineStr">
         <is>
-          <t>Even her embarrassed face is something special...
-honestly, I can't get enough.</t>
+          <t>Even her embarrassed face is delightfully charming...
+honestly, it's irresistible.</t>
         </is>
       </c>
       <c r="C628" t="n">
@@ -10143,8 +10162,8 @@
       </c>
       <c r="B630" s="1" t="inlineStr">
         <is>
-          <t>「Ahh... the stuff coming out from the tip's getting
-on the panties...」</t>
+          <t>「Ah... the fluid coming out of the tip is getting on
+my panties...」</t>
         </is>
       </c>
       <c r="C630" t="n">
@@ -10174,7 +10193,7 @@
       </c>
       <c r="B632" s="1" t="inlineStr">
         <is>
-          <t>「Ugh... ahh, huu...」</t>
+          <t>「Ugh... uuh...」</t>
         </is>
       </c>
       <c r="C632" t="n">
@@ -10250,7 +10269,7 @@
       </c>
       <c r="B637" s="1" t="inlineStr">
         <is>
-          <t>「...！ Because Niini's being mean...」</t>
+          <t>「...! B-because Niini is being mean...」</t>
         </is>
       </c>
       <c r="C637" t="n">
@@ -10342,7 +10361,7 @@
       </c>
       <c r="B643" s="1" t="inlineStr">
         <is>
-          <t>「Nn...？」</t>
+          <t>「Mmm…？」</t>
         </is>
       </c>
       <c r="C643" t="n">
@@ -10372,7 +10391,7 @@
       </c>
       <c r="B645" s="1" t="inlineStr">
         <is>
-          <t>「Would you rather I just quietly stroke my penis？」</t>
+          <t>「Would you rather I just quietly stroke my penis?」</t>
         </is>
       </c>
       <c r="C645" t="n">
@@ -10433,8 +10452,8 @@
       </c>
       <c r="B649" s="1" t="inlineStr">
         <is>
-          <t>It seems her embarrassment is winning out and her
-head's a mess.</t>
+          <t>It seems her embarrassment is getting the better of
+her; she's all flustered.</t>
         </is>
       </c>
       <c r="C649" t="n">
@@ -10464,8 +10483,8 @@
       </c>
       <c r="B651" s="1" t="inlineStr">
         <is>
-          <t>「Ahaha... You're the one who said it was a punishment
-game, remember？」</t>
+          <t>「Ahaha... Rin-chan, you're the one who said it was a
+punishment game, remember？」</t>
         </is>
       </c>
       <c r="C651" t="n">
@@ -10603,7 +10622,7 @@
       </c>
       <c r="B660" s="1" t="inlineStr">
         <is>
-          <t>「Ka...cute...？」</t>
+          <t>「C-cute...?」</t>
         </is>
       </c>
       <c r="C660" t="n">
@@ -10618,9 +10637,9 @@
       </c>
       <c r="B661" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan, flustered by the words that slipped out of
-my mouth, widened her eyes, hugged her knees, and
-wiggled her legs even more.</t>
+          <t>Startled by the words that had slipped out of my
+mouth, Rin-chan widened her eyes, drew her knees to
+her chest, and fidgeted her legs even more.</t>
         </is>
       </c>
       <c r="C661" t="n">
@@ -10650,7 +10669,7 @@
       </c>
       <c r="B663" s="1" t="inlineStr">
         <is>
-          <t>「Niini, you idiot...！」</t>
+          <t>「N-Niini, you idiot...!」</t>
         </is>
       </c>
       <c r="C663" t="n">
@@ -10696,7 +10715,7 @@
       </c>
       <c r="B666" s="1" t="inlineStr">
         <is>
-          <t>「...Alright, then I'll keep up the penalty game.」</t>
+          <t>「...Alright, then I'll continue the punishment game.」</t>
         </is>
       </c>
       <c r="C666" t="n">
@@ -10756,7 +10775,7 @@
       </c>
       <c r="B670" s="1" t="inlineStr">
         <is>
-          <t>「Yeah... I'll watch...！」</t>
+          <t>「Okay... I'll be watching...！」</t>
         </is>
       </c>
       <c r="C670" t="n">
@@ -10771,8 +10790,8 @@
       </c>
       <c r="B671" s="1" t="inlineStr">
         <is>
-          <t>I deliberately put myself down a bit, and Rin-chan,
-pulled along, regained her fighting spirit.</t>
+          <t>I deliberately put myself down, and Rin-chan, caught
+up in it, regained her spirits.</t>
         </is>
       </c>
       <c r="C671" t="n">
@@ -10802,7 +10821,7 @@
       </c>
       <c r="B673" s="1" t="inlineStr">
         <is>
-          <t>「I'll watch, so... do your shasee, okay？」</t>
+          <t>"I'll be watching, so... cum for me, okay?"</t>
         </is>
       </c>
       <c r="C673" t="n">
@@ -10817,9 +10836,9 @@
       </c>
       <c r="B674" s="1" t="inlineStr">
         <is>
-          <t>She's a little desperate and still looks troubled,
-but the light in her eyes is slowly returning to the
-usual Rin-chan.</t>
+          <t>She's still looking a bit desperate and troubled, but
+the light in her eyes is gradually returning to her
+usual Rin-chan self.</t>
         </is>
       </c>
       <c r="C674" t="n">
@@ -10834,8 +10853,8 @@
       </c>
       <c r="B675" s="1" t="inlineStr">
         <is>
-          <t>I like it when Rin-chan gets shy and quiet, but after
-all, I want her to stay a little bratty.</t>
+          <t>I like it when Rin-chan gets shy and quiet, but I
+still want her to be a little sassy.</t>
         </is>
       </c>
       <c r="C675" t="n">
@@ -10850,9 +10869,9 @@
       </c>
       <c r="B676" s="1" t="inlineStr">
         <is>
-          <t>Feeling that again, I turned my hips toward Rin-chan
-once more and began stroking myself toward
-ejaculation however I liked.</t>
+          <t>Again feeling that way, I turned my hips back toward
+Rin-chan and began pumping myself toward ejaculation
+as I pleased.</t>
         </is>
       </c>
       <c r="C676" t="n">
@@ -10882,7 +10901,7 @@
       </c>
       <c r="B678" s="1" t="inlineStr">
         <is>
-          <t>「Ugh... huh...」</t>
+          <t>「Ugh... huff...」</t>
         </is>
       </c>
       <c r="C678" t="n">
@@ -10912,7 +10931,7 @@
       </c>
       <c r="B680" s="1" t="inlineStr">
         <is>
-          <t>「...Niini, you look like you're feeling good...」</t>
+          <t>「...Niini, you look like you're enjoying it...」</t>
         </is>
       </c>
       <c r="C680" t="n">
@@ -10957,8 +10976,8 @@
       </c>
       <c r="B683" s="1" t="inlineStr">
         <is>
-          <t>...Even though I'm stroking myself, being under
-Rin-chan's gaze makes the sensitivity different.</t>
+          <t>...Even though I'm stroking myself, it feels
+different when Rin-chan is watching me.</t>
         </is>
       </c>
       <c r="C683" t="n">
@@ -10988,7 +11007,7 @@
       </c>
       <c r="B685" s="1" t="inlineStr">
         <is>
-          <t>「Is that so... it feels good, huh？」</t>
+          <t>「Is that so...? Does it feel good?」</t>
         </is>
       </c>
       <c r="C685" t="n">
@@ -11018,8 +11037,8 @@
       </c>
       <c r="B687" s="1" t="inlineStr">
         <is>
-          <t>「Yeah... at first, slow like this... but rub a little
-harder...」</t>
+          <t>「Like this... at first, slowly like this... but rub a
+little more firmly...」</t>
         </is>
       </c>
       <c r="C687" t="n">
@@ -11079,8 +11098,8 @@
       </c>
       <c r="B691" s="1" t="inlineStr">
         <is>
-          <t>「Right... and once it gets used to it, gradually
-speed up.」</t>
+          <t>"Yeah... and then, once you get the hang of it,
+gradually pick up the pace."</t>
         </is>
       </c>
       <c r="C691" t="n">
@@ -11110,7 +11129,7 @@
       </c>
       <c r="B693" s="1" t="inlineStr">
         <is>
-          <t>「I... I see...」</t>
+          <t>「Oh... I see...」</t>
         </is>
       </c>
       <c r="C693" t="n">
@@ -11125,8 +11144,8 @@
       </c>
       <c r="B694" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan, getting back into her usual groove, started
-going along with my demonstration.</t>
+          <t>Rin-chan, regaining her usual groove, started to
+follow my lead.</t>
         </is>
       </c>
       <c r="C694" t="n">
@@ -11141,9 +11160,9 @@
       </c>
       <c r="B695" s="1" t="inlineStr">
         <is>
-          <t>But it wasn't that her shame or embarrassment had
-disappeared; she was still wiggling her legs while
-sitting with her knees up.</t>
+          <t>But her shyness and embarrassment hadn't disappeared;
+she was still fidgeting with her legs while sitting
+with her knees drawn up.</t>
         </is>
       </c>
       <c r="C695" t="n">
@@ -11158,7 +11177,7 @@
       </c>
       <c r="B696" s="1" t="inlineStr">
         <is>
-          <t>I can do it... With this momentum I can...!</t>
+          <t>I can come... With this rhythm, I can come...!</t>
         </is>
       </c>
       <c r="C696" t="n">
@@ -11188,7 +11207,7 @@
       </c>
       <c r="B698" s="1" t="inlineStr">
         <is>
-          <t>「And when you get into the rhythm, faster...！」</t>
+          <t>"And once you get the hang of it, go faster...!"</t>
         </is>
       </c>
       <c r="C698" t="n">
@@ -11218,7 +11237,7 @@
       </c>
       <c r="B700" s="1" t="inlineStr">
         <is>
-          <t>「Muuuh...！ I-It's fast...」</t>
+          <t>“Mmm...! I-It's fast...”</t>
         </is>
       </c>
       <c r="C700" t="n">
@@ -11233,7 +11252,7 @@
       </c>
       <c r="B701" s="1" t="inlineStr">
         <is>
-          <t>When I stroked my penis at high speed, Rin-chan
+          <t>When I began stroking my penis rapidly, Rin-chan
 opened her eyes and mouth wide.</t>
         </is>
       </c>
@@ -11249,7 +11268,8 @@
       </c>
       <c r="B702" s="1" t="inlineStr">
         <is>
-          <t>But it was still too early for her to be surprised.</t>
+          <t>But it was still too early for Rin-chan to be
+surprised.</t>
         </is>
       </c>
       <c r="C702" t="n">
@@ -11296,8 +11316,7 @@
       </c>
       <c r="B705" s="1" t="inlineStr">
         <is>
-          <t>「Uah... I'm... I'm going to come... I'm going to
-come...」</t>
+          <t>「Ah... I'm... I'm coming... I'm coming...!」</t>
         </is>
       </c>
       <c r="C705" t="n">
@@ -11327,7 +11346,7 @@
       </c>
       <c r="B707" s="1" t="inlineStr">
         <is>
-          <t>「Ugh... yeah...」</t>
+          <t>「Mmm... yeah...」</t>
         </is>
       </c>
       <c r="C707" t="n">
@@ -11357,7 +11376,7 @@
       </c>
       <c r="B709" s="1" t="inlineStr">
         <is>
-          <t>「Make sure you watch...！」</t>
+          <t>「Keep watching me, okay...!」</t>
         </is>
       </c>
       <c r="C709" t="n">
@@ -11418,9 +11437,9 @@
       </c>
       <c r="B713" s="1" t="inlineStr">
         <is>
-          <t>To ejaculate while being watched by Rin-chan... it's
-late to feel this way, but just thinking about it
-makes my heart race.</t>
+          <t>Ejaculating while Rin-chan watches... I know it's
+kind of late to be thinking that, but just thinking
+about it makes my heart race.</t>
         </is>
       </c>
       <c r="C713" t="n">
@@ -11435,8 +11454,8 @@
       </c>
       <c r="B714" s="1" t="inlineStr">
         <is>
-          <t>At the same time, Rin-chan, nervous too, was watching
-over my ejaculation...</t>
+          <t>At the same time, Rin-chan, her heart racing, was
+watching me ejaculate...</t>
         </is>
       </c>
       <c r="C714" t="n">
@@ -11466,7 +11485,7 @@
       </c>
       <c r="B716" s="1" t="inlineStr">
         <is>
-          <t>「...Kuh...！」</t>
+          <t>「…Ugh…！」</t>
         </is>
       </c>
       <c r="C716" t="n">
@@ -11481,7 +11500,7 @@
       </c>
       <c r="B717" s="1" t="inlineStr">
         <is>
-          <t>...My penis trembled and shook.</t>
+          <t>...My penis trembled.</t>
         </is>
       </c>
       <c r="C717" t="n">
@@ -11496,7 +11515,7 @@
       </c>
       <c r="B718" s="1" t="inlineStr">
         <is>
-          <t>It's finally... coming！</t>
+          <t>Here it comes!</t>
         </is>
       </c>
       <c r="C718" t="n">
@@ -11602,7 +11621,7 @@
       </c>
       <c r="B725" s="1" t="inlineStr">
         <is>
-          <t>「...！？」</t>
+          <t>"...!?"</t>
         </is>
       </c>
       <c r="C725" t="n">
@@ -11617,7 +11636,7 @@
       </c>
       <c r="B726" s="1" t="inlineStr">
         <is>
-          <t>When I responded to that call with my gaze... in that
+          <t>When I looked in response to that call... in that
 instant, I saw it.</t>
         </is>
       </c>
@@ -11633,8 +11652,8 @@
       </c>
       <c r="B727" s="1" t="inlineStr">
         <is>
-          <t>The base of Rin-chan's legs squirming, the plump soft
-flesh twitching...！</t>
+          <t>The base of Rin-chan's thighs, where her plump, soft
+flesh gave a little twitch...!</t>
         </is>
       </c>
       <c r="C727" t="n">
@@ -11664,7 +11683,7 @@
       </c>
       <c r="B729" s="1" t="inlineStr">
         <is>
-          <t>「Ah...! ...fu, n...」</t>
+          <t>「Ah... fuhn...」</t>
         </is>
       </c>
       <c r="C729" t="n">
@@ -11709,8 +11728,7 @@
       </c>
       <c r="B732" s="1" t="inlineStr">
         <is>
-          <t>That certainty was the trigger, and my ejaculation
-began！</t>
+          <t>That certainty triggered my ejaculation!</t>
         </is>
       </c>
       <c r="C732" t="n">
@@ -11725,7 +11743,7 @@
       </c>
       <c r="B733" s="1" t="inlineStr">
         <is>
-          <t>Biyururu!　Byubyu,　byuuuu!</t>
+          <t>Bigu! Byururu! Byubyu, byuuuu!</t>
         </is>
       </c>
       <c r="C733" t="n">
@@ -11785,8 +11803,8 @@
       </c>
       <c r="B737" s="1" t="inlineStr">
         <is>
-          <t>I grabbed the panties and brought them to Suzuguchi,
-but it was already too late.</t>
+          <t>I tried to bring the panties I'd been clutching to
+Suzuguchi, but it was already too late.</t>
         </is>
       </c>
       <c r="C737" t="n">
@@ -11801,7 +11819,7 @@
       </c>
       <c r="B738" s="1" t="inlineStr">
         <is>
-          <t>Byubyubyuu~！　Byuku！　Byuku！</t>
+          <t>Byubyu byuu~! Byuku! Byuku!</t>
         </is>
       </c>
       <c r="C738" t="n">
@@ -11831,7 +11849,7 @@
       </c>
       <c r="B740" s="1" t="inlineStr">
         <is>
-          <t>「Hyah...! Fua...!？」</t>
+          <t>「Eek...! Ah...!?」</t>
         </is>
       </c>
       <c r="C740" t="n">
@@ -11862,8 +11880,8 @@
       </c>
       <c r="B742" s="1" t="inlineStr">
         <is>
-          <t>Because the semen landed on Rin-chan’s legs, and at
-the base of them...</t>
+          <t>Because the semen had landed on Rin-chan's legs — at
+the base of her thighs...</t>
         </is>
       </c>
       <c r="C742" t="n">
@@ -11893,7 +11911,7 @@
       </c>
       <c r="B744" s="1" t="inlineStr">
         <is>
-          <t>「Nn...？ Fah... ah... aah...！？」</t>
+          <t>「Nn...? Hah... ah... aaah...!?」</t>
         </is>
       </c>
       <c r="C744" t="n">
@@ -11908,8 +11926,9 @@
       </c>
       <c r="B745" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan, who had mucus between her legs, twisted her
-face in puzzlement as if she were only now noticing.</t>
+          <t>Rin-chan, who had semen land between her legs,
+twisted her face in puzzlement, as if only now
+noticing.</t>
         </is>
       </c>
       <c r="C745" t="n">
@@ -11924,7 +11943,7 @@
       </c>
       <c r="B746" s="1" t="inlineStr">
         <is>
-          <t>That until just a moment ago, that place had been
+          <t>Until just a moment ago, down there had been
 completely exposed...</t>
         </is>
       </c>
@@ -11970,7 +11989,7 @@
       </c>
       <c r="B749" s="1" t="inlineStr">
         <is>
-          <t>Rin</t>
+          <t>Rin-chan</t>
         </is>
       </c>
       <c r="C749" t="n">
@@ -11985,7 +12004,7 @@
       </c>
       <c r="B750" s="1" t="inlineStr">
         <is>
-          <t>「Ah... ah... hyaa...」</t>
+          <t>「Ah... aaah... eek...」</t>
         </is>
       </c>
       <c r="C750" t="n">
@@ -12000,7 +12019,8 @@
       </c>
       <c r="B751" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan blushed more than ever and froze like that.</t>
+          <t>Rin-chan blushed like never before and froze in
+place.</t>
         </is>
       </c>
       <c r="C751" t="n">
@@ -12015,8 +12035,7 @@
       </c>
       <c r="B752" s="1" t="inlineStr">
         <is>
-          <t>It's like embarrassment has reached its absolute
-limit here...</t>
+          <t>It felt like her embarrassment had reached its peak.</t>
         </is>
       </c>
       <c r="C752" t="n">
@@ -12031,8 +12050,8 @@
       </c>
       <c r="B753" s="1" t="inlineStr">
         <is>
-          <t>It's better than her emotions exploding into a
-scream, but with Rin-chan it's scary from here on.</t>
+          <t>It's better than her bursting into a scream, but for
+Rin-chan the scary part is just beginning.</t>
         </is>
       </c>
       <c r="C753" t="n">
@@ -12048,8 +12067,8 @@
       <c r="B754" s="1" t="inlineStr">
         <is>
           <t>I braced myself to be scolded, and while Rin-chan
-stayed frozen I quickly put on my underwear and
-pants.</t>
+remained frozen, I put my underwear and pants back on
+for the time being.</t>
         </is>
       </c>
       <c r="C754" t="n">
@@ -12080,8 +12099,8 @@
       <c r="B756" s="1" t="inlineStr">
         <is>
           <t>In the meantime, Rin-chan had at least somewhat
-recovered from the shock, straightened up while
-covering between her legs with her hand.</t>
+recovered from the shock; she covered the area
+between her legs with her hand and composed herself.</t>
         </is>
       </c>
       <c r="C756" t="n">
@@ -12111,7 +12130,7 @@
       </c>
       <c r="B758" s="1" t="inlineStr">
         <is>
-          <t>「Ni-, Niini, Niiiii~~~」</t>
+          <t>「Ni, nini, Niinii~~~」</t>
         </is>
       </c>
       <c r="C758" t="n">
@@ -12216,9 +12235,9 @@
       </c>
       <c r="B765" s="1" t="inlineStr">
         <is>
-          <t>Like when you kissed me while I was asleep, I answer
-honestly because I can't make excuses in this
-situation.</t>
+          <t>As with when you kissed me while I was asleep, this
+is a situation where I can't make any excuses, so I
+answer honestly.</t>
         </is>
       </c>
       <c r="C765" t="n">
@@ -12295,7 +12314,7 @@
       </c>
       <c r="B770" s="1" t="inlineStr">
         <is>
-          <t>「Ah... that is...」</t>
+          <t>「Ah... well...」</t>
         </is>
       </c>
       <c r="C770" t="n">
@@ -12310,8 +12329,9 @@
       </c>
       <c r="B771" s="1" t="inlineStr">
         <is>
-          <t>I couldn't say I had been using Rin-chan's
-between-her-legs as sexual material, so I faltered.</t>
+          <t>I couldn't bring myself to say I'd been using
+Rin-chan's crotch as material to masturbate to, so I
+hesitated.</t>
         </is>
       </c>
       <c r="C771" t="n">
@@ -12341,7 +12361,7 @@
       </c>
       <c r="B773" s="1" t="inlineStr">
         <is>
-          <t>「...Anyway, shall I wipe between your legs？」</t>
+          <t>「...Anyway, shall I wipe you down there?」</t>
         </is>
       </c>
       <c r="C773" t="n">
@@ -12371,7 +12391,7 @@
       </c>
       <c r="B775" s="1" t="inlineStr">
         <is>
-          <t>「Don't dodge it.」</t>
+          <t>Don't try to dodge it.</t>
         </is>
       </c>
       <c r="C775" t="n">
@@ -12401,7 +12421,7 @@
       </c>
       <c r="B777" s="1" t="inlineStr">
         <is>
-          <t>「Yes, sorry...」</t>
+          <t>「Yes, I'm sorry...」</t>
         </is>
       </c>
       <c r="C777" t="n">
@@ -12416,7 +12436,7 @@
       </c>
       <c r="B778" s="1" t="inlineStr">
         <is>
-          <t>Being sharply snapped back at, I shrank.</t>
+          <t>She snapped at me, and I shrank back.</t>
         </is>
       </c>
       <c r="C778" t="n">
@@ -12431,9 +12451,8 @@
       </c>
       <c r="B779" s="1" t="inlineStr">
         <is>
-          <t>Semen was still between her legs, but she was
-probably so angry she didn’t even care about
-something like that.</t>
+          <t>She still had semen between her legs, but she was
+probably too angry to care about such a thing.</t>
         </is>
       </c>
       <c r="C779" t="n">
@@ -12448,7 +12467,7 @@
       </c>
       <c r="B780" s="1" t="inlineStr">
         <is>
-          <t>...What should I do about this follow...?</t>
+          <t>...How should I handle this...?</t>
         </is>
       </c>
       <c r="C780" t="n">
@@ -12478,8 +12497,8 @@
       </c>
       <c r="B782" s="1" t="inlineStr">
         <is>
-          <t>「...But you said 'show me,' Rin, so... I guess I
-can't really blame you...」</t>
+          <t>"...But you were the one who said 'show me' earlier,
+Rin... so... I guess it can't be helped..."</t>
         </is>
       </c>
       <c r="C782" t="n">
@@ -12494,8 +12513,8 @@
       </c>
       <c r="B783" s="1" t="inlineStr">
         <is>
-          <t>I hung my head, feeling utterly at a loss, when a
-gentle voice slipped out.</t>
+          <t>I hung my head, utterly at a loss, when gentle words
+slipped out.</t>
         </is>
       </c>
       <c r="C783" t="n">
@@ -12510,8 +12529,8 @@
       </c>
       <c r="B784" s="1" t="inlineStr">
         <is>
-          <t>Startled, I looked up, and Rin-chan was squirming
-while pressing her between-her-legs with both hands.</t>
+          <t>Startled, I looked up to see Rin-chan squirming while
+pressing the area between her legs with both hands.</t>
         </is>
       </c>
       <c r="C784" t="n">
@@ -12541,7 +12560,7 @@
       </c>
       <c r="B786" s="1" t="inlineStr">
         <is>
-          <t>「Ah... Rin, chan...？」</t>
+          <t>「Ah... Rin-chan...?」</t>
         </is>
       </c>
       <c r="C786" t="n">
@@ -12601,8 +12620,8 @@
       </c>
       <c r="B790" s="1" t="inlineStr">
         <is>
-          <t>She looked angry, but maybe she was just really
-embarrassed...？</t>
+          <t>She seemed angry, but maybe she was actually just
+really embarrassed...?</t>
         </is>
       </c>
       <c r="C790" t="n">
@@ -12617,9 +12636,9 @@
       </c>
       <c r="B791" s="1" t="inlineStr">
         <is>
-          <t>And she even saw the ejaculation up close, and semen
-landed directly between her legs… could it be that
-she’s awakened to something？</t>
+          <t>I even saw the ejaculation up close, and semen landed
+directly between her legs... Could it be that I've
+awakened to something?</t>
         </is>
       </c>
       <c r="C791" t="n">
@@ -12816,8 +12835,7 @@
       </c>
       <c r="B804" s="1" t="inlineStr">
         <is>
-          <t>...I was pushed out of the room like I was being
-thrown away.</t>
+          <t>...I left the room as if I'd been pushed out.</t>
         </is>
       </c>
       <c r="C804" t="n">
@@ -12863,8 +12881,8 @@
       </c>
       <c r="B807" s="1" t="inlineStr">
         <is>
-          <t>In the bath she was the most embarrassed, but she
-wanted to watch me cum.</t>
+          <t>Rin-chan was the most embarrassed in the bath, yet
+she wanted to watch me cum.</t>
         </is>
       </c>
       <c r="C807" t="n">
@@ -12879,8 +12897,8 @@
       </c>
       <c r="B808" s="1" t="inlineStr">
         <is>
-          <t>That cheeky, bratty look she gave me when she handed
-over her panties...</t>
+          <t>That cheeky, sassy look Rin-chan had when she handed
+me her panties...</t>
         </is>
       </c>
       <c r="C808" t="n">
@@ -12911,9 +12929,9 @@
       </c>
       <c r="B810" s="1" t="inlineStr">
         <is>
-          <t>Just when I thought she'd be angry, she'd forgive me
-easily, and yet she'd suddenly tell me sharply to get
-out...</t>
+          <t>Just when I thought Rin-chan would be angry, she
+would forgive me easily, and yet she'd also tell me
+sharply to get out...</t>
         </is>
       </c>
       <c r="C810" t="n">
@@ -12928,8 +12946,8 @@
       </c>
       <c r="B811" s="1" t="inlineStr">
         <is>
-          <t>She's a sensitive girl, so I can't understand all of
-Rin-chan's feelings.</t>
+          <t>Rin-chan is a sensitive girl, so I can't understand
+all of her feelings.</t>
         </is>
       </c>
       <c r="C811" t="n">
@@ -12960,7 +12978,7 @@
       </c>
       <c r="B813" s="1" t="inlineStr">
         <is>
-          <t>I'll watch over her growth.</t>
+          <t>I'll watch over her as she grows.</t>
         </is>
       </c>
       <c r="C813" t="n">
@@ -13006,7 +13024,7 @@
       </c>
       <c r="B816" s="1" t="inlineStr">
         <is>
-          <t>I had actually meant to catch my semen with those
+          <t>I had actually meant to catch my cum in these
 panties.</t>
         </is>
       </c>
@@ -13022,8 +13040,8 @@
       </c>
       <c r="B817" s="1" t="inlineStr">
         <is>
-          <t>I thought I could just wash them, but I came
-unexpectedly and couldn't stop it.</t>
+          <t>I thought washing them would be enough, but I
+couldn't hold back and ejaculated.</t>
         </is>
       </c>
       <c r="C817" t="n">
@@ -13069,7 +13087,7 @@
       </c>
       <c r="B820" s="1" t="inlineStr">
         <is>
-          <t>I think that as I head back to her room.</t>
+          <t>Thinking that, I returned to my room.</t>
         </is>
       </c>
       <c r="C820" t="n">
@@ -13132,9 +13150,8 @@
       </c>
       <c r="B824" s="1" t="inlineStr">
         <is>
-          <t>Sometimes she's the one being coddled, sometimes
-she's the one who spoils me, and it always soothes my
-heart.</t>
+          <t>Sometimes she clings to me, and sometimes she spoils
+me — either way, she soothes my heart.</t>
         </is>
       </c>
       <c r="C824" t="n">
@@ -13149,7 +13166,7 @@
       </c>
       <c r="B825" s="1" t="inlineStr">
         <is>
-          <t>Yeah, I'm going to cuddle up with Rurichiyo-chan！</t>
+          <t>Yeah, I'll sleep next to Rurichiyo-chan!</t>
         </is>
       </c>
       <c r="C825" t="n">
@@ -13197,7 +13214,7 @@
       </c>
       <c r="B828" s="1" t="inlineStr">
         <is>
-          <t>Not that I know exactly what it is.</t>
+          <t>That said, I don't really know what it is.</t>
         </is>
       </c>
       <c r="C828" t="n">
@@ -13227,7 +13244,7 @@
       </c>
       <c r="B830" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan's room had the lights off.</t>
+          <t>The lights were off in Rurichiyo-chan's room.</t>
         </is>
       </c>
       <c r="C830" t="n">
@@ -13242,7 +13259,7 @@
       </c>
       <c r="B831" s="1" t="inlineStr">
         <is>
-          <t>Ah... this is Rurichiyo-chan and Nono-chan's room
+          <t>Ah... so it's Rurichiyo-chan and Nono-chan's room
 now, huh.</t>
         </is>
       </c>
@@ -13258,8 +13275,8 @@
       </c>
       <c r="B832" s="1" t="inlineStr">
         <is>
-          <t>...I quiet my mind and listen, but neither of them
-seems to be awake.</t>
+          <t>...I quiet my mind and sharpen my senses, but there
+is no sign that either of them is awake.</t>
         </is>
       </c>
       <c r="C832" t="n">
@@ -13274,8 +13291,8 @@
       </c>
       <c r="B833" s="1" t="inlineStr">
         <is>
-          <t>Guess they fell asleep... I took too long thinking
-about it, so I can't blame them.</t>
+          <t>Guess they fell asleep... I spent quite a while
+worrying about it, so it can't be helped.</t>
         </is>
       </c>
       <c r="C833" t="n">
@@ -13306,8 +13323,8 @@
       </c>
       <c r="B835" s="1" t="inlineStr">
         <is>
-          <t>But it's a bunk bed, and I still didn't know which
-bunk Rurichiyo-chan slept in.</t>
+          <t>But it was a bunk bed, and I still didn't know which
+bunk Rurichiyo-chan was sleeping on.</t>
         </is>
       </c>
       <c r="C835" t="n">
@@ -13353,7 +13370,7 @@
       </c>
       <c r="B838" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C838" t="n">
@@ -13429,7 +13446,7 @@
       </c>
       <c r="B843" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C843" t="n">
@@ -13444,7 +13461,7 @@
       </c>
       <c r="B844" s="1" t="inlineStr">
         <is>
-          <t>「...nng？」</t>
+          <t>「...Mmm？」</t>
         </is>
       </c>
       <c r="C844" t="n">
@@ -13459,7 +13476,7 @@
       </c>
       <c r="B845" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan tilted her sleepy head to the side.</t>
+          <t>Rurichiyo-chan cocked her head sleepily.</t>
         </is>
       </c>
       <c r="C845" t="n">
@@ -13489,7 +13506,7 @@
       </c>
       <c r="B847" s="1" t="inlineStr">
         <is>
-          <t>「Rurichiyo-chan...？ Are you awake？ Or still asleep？」</t>
+          <t>「Rurichiyo-chan...? Are you awake? Or asleep?」</t>
         </is>
       </c>
       <c r="C847" t="n">
@@ -13504,7 +13521,7 @@
       </c>
       <c r="B848" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C848" t="n">
@@ -13519,7 +13536,7 @@
       </c>
       <c r="B849" s="1" t="inlineStr">
         <is>
-          <t>「Mmm~...？」</t>
+          <t>「Mmm...？」</t>
         </is>
       </c>
       <c r="C849" t="n">
@@ -13550,7 +13567,7 @@
       </c>
       <c r="B851" s="1" t="inlineStr">
         <is>
-          <t>She’s completely half-asleep...</t>
+          <t>She's completely half-asleep...</t>
         </is>
       </c>
       <c r="C851" t="n">
@@ -13580,7 +13597,7 @@
       </c>
       <c r="B853" s="1" t="inlineStr">
         <is>
-          <t>「Can't be helped... Rurichiyo-chan is...！」</t>
+          <t>Good grief... Rurichiyo-chan...</t>
         </is>
       </c>
       <c r="C853" t="n">
@@ -13595,8 +13612,8 @@
       </c>
       <c r="B854" s="1" t="inlineStr">
         <is>
-          <t>I climbed onto the bed with a suppressed, sinister
-chuckle, intending to make Rurichiyo-chan lie down.</t>
+          <t>I climbed onto the bed with a sly chuckle, intending
+to lay Rurichiyo-chan down.</t>
         </is>
       </c>
       <c r="C854" t="n">
@@ -13657,8 +13674,8 @@
       </c>
       <c r="B858" s="1" t="inlineStr">
         <is>
-          <t>Alright, let’s support her shoulders and hips and lay
-her down.</t>
+          <t>Alright, I'll support Rurichiyo-chan's shoulders and
+waist and lay her down.</t>
         </is>
       </c>
       <c r="C858" t="n">
@@ -13673,7 +13690,7 @@
       </c>
       <c r="B859" s="1" t="inlineStr">
         <is>
-          <t>Like laying the princess onto the bed, solemnly...</t>
+          <t>Solemnly... as if laying a princess down on a bed.</t>
         </is>
       </c>
       <c r="C859" t="n">
@@ -13703,7 +13720,7 @@
       </c>
       <c r="B861" s="1" t="inlineStr">
         <is>
-          <t>「Nn... n-fufu...！」</t>
+          <t>「Mmm... hee hee...！」</t>
         </is>
       </c>
       <c r="C861" t="n">
@@ -13733,7 +13750,7 @@
       </c>
       <c r="B863" s="1" t="inlineStr">
         <is>
-          <t>It's nice that you're cheerful even when you're
+          <t>It's good that she's in a good mood even when she's
 half-asleep.</t>
         </is>
       </c>
@@ -13794,8 +13811,9 @@
       </c>
       <c r="B867" s="1" t="inlineStr">
         <is>
-          <t>No sooner had I thought that than the hand that had
-been swimming through the air reached for my head.</t>
+          <t>No sooner had I thought that than Rurichiyo-chan's
+hand, which had been waving in the air, reached
+toward my head.</t>
         </is>
       </c>
       <c r="C867" t="n">
@@ -13840,8 +13858,8 @@
       </c>
       <c r="B870" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan fell back onto the bed holding my
-head.</t>
+          <t>Rurichiyo-chan collapsed onto the bed, still cradling
+my head.</t>
         </is>
       </c>
       <c r="C870" t="n">
@@ -13871,7 +13889,7 @@
       </c>
       <c r="B872" s="1" t="inlineStr">
         <is>
-          <t>「...！？」</t>
+          <t>「Ah...！？」</t>
         </is>
       </c>
       <c r="C872" t="n">
@@ -13886,8 +13904,8 @@
       </c>
       <c r="B873" s="1" t="inlineStr">
         <is>
-          <t>It was moving with more force than I expected, so I
-didn't resist and let myself fall with her.</t>
+          <t>Rurichiyo-chan had more momentum than I expected, so
+I deliberately didn't resist and fell with her.</t>
         </is>
       </c>
       <c r="C873" t="n">
@@ -13980,7 +13998,7 @@
       </c>
       <c r="B879" s="1" t="inlineStr">
         <is>
-          <t>「Nngh！　Nfu~...！」</t>
+          <t>「Mmm! Nfu~...!」</t>
         </is>
       </c>
       <c r="C879" t="n">
@@ -13995,9 +14013,8 @@
       </c>
       <c r="B880" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan, who had her hands on my head, was
-making a sleeping sound that almost sounded like a
-laugh.</t>
+          <t>Rurichiyo-chan, who was cradling my head, was making
+soft, laugh-like breaths in her sleep.</t>
         </is>
       </c>
       <c r="C880" t="n">
@@ -14028,8 +14045,8 @@
       </c>
       <c r="B882" s="1" t="inlineStr">
         <is>
-          <t>Being held like this, with my head trapped, is kind
-of wonderful, but I can’t do anything like this.</t>
+          <t>Having my head cradled like this is wonderful, but I
+can’t do anything in this position.</t>
         </is>
       </c>
       <c r="C882" t="n">
@@ -14044,8 +14061,8 @@
       </c>
       <c r="B883" s="1" t="inlineStr">
         <is>
-          <t>For now, I'll free myself from Rurichiyo-chan's arm
-and straighten the futon for her.</t>
+          <t>For now, I'll slip my head free from Rurichiyo-chan's
+arms and straighten the futon for her.</t>
         </is>
       </c>
       <c r="C883" t="n">
@@ -14075,7 +14092,7 @@
       </c>
       <c r="B885" s="1" t="inlineStr">
         <is>
-          <t>「Nn... nnn~...！」</t>
+          <t>"Mmm... mmm~...!"</t>
         </is>
       </c>
       <c r="C885" t="n">
@@ -14120,8 +14137,8 @@
       </c>
       <c r="B888" s="1" t="inlineStr">
         <is>
-          <t>When I tried to grab her arm and pull away, she
-instead grabbed my head more tightly.</t>
+          <t>When I tried to grab Rurichiyo-chan's arm to pull it
+away, she instead tightened her hold on my head.</t>
         </is>
       </c>
       <c r="C888" t="n">
@@ -14136,8 +14153,8 @@
       </c>
       <c r="B889" s="1" t="inlineStr">
         <is>
-          <t>And because she hugged me so hard, my face ended up
-pressed against her chest.</t>
+          <t>Rurichiyo-chan hugged me so tightly that my face
+ended up pressed against her chest.</t>
         </is>
       </c>
       <c r="C889" t="n">
@@ -14182,8 +14199,9 @@
       </c>
       <c r="B892" s="1" t="inlineStr">
         <is>
-          <t>I couldn't help getting happy, and I ended up rubbing
-my face all over Rurichiyo-chan's chest.</t>
+          <t>I couldn't help but feel happy, and I ended up
+pressing and rubbing my face against Rurichiyo-chan's
+breasts.</t>
         </is>
       </c>
       <c r="C892" t="n">
@@ -14213,7 +14231,7 @@
       </c>
       <c r="B894" s="1" t="inlineStr">
         <is>
-          <t>「Nn... nnn~...」</t>
+          <t>「Mmm... mmm~...」</t>
         </is>
       </c>
       <c r="C894" t="n">
@@ -14228,7 +14246,7 @@
       </c>
       <c r="B895" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan let out a small, flustered sigh.</t>
+          <t>Rurichiyo-chan let out a sulky sigh.</t>
         </is>
       </c>
       <c r="C895" t="n">
@@ -14243,8 +14261,8 @@
       </c>
       <c r="B896" s="1" t="inlineStr">
         <is>
-          <t>She’s feeling the stimulation on her chest so
-sensitively.</t>
+          <t>Rurichiyo-chan's breasts are reacting very
+sensitively to the stimulation.</t>
         </is>
       </c>
       <c r="C896" t="n">
@@ -14274,7 +14292,7 @@
       </c>
       <c r="B898" s="1" t="inlineStr">
         <is>
-          <t>Keep grinding it...</t>
+          <t>Go on, keep rubbing it...</t>
         </is>
       </c>
       <c r="C898" t="n">
@@ -14304,7 +14322,7 @@
       </c>
       <c r="B900" s="1" t="inlineStr">
         <is>
-          <t>「Mmm—... m, ufufu...！」</t>
+          <t>Mmm... nn, tee-hee...!</t>
         </is>
       </c>
       <c r="C900" t="n">
@@ -14319,7 +14337,7 @@
       </c>
       <c r="B901" s="1" t="inlineStr">
         <is>
-          <t>Ah, she's laughing...</t>
+          <t>Ah, Rurichiyo-chan is giggling...</t>
         </is>
       </c>
       <c r="C901" t="n">
@@ -14365,7 +14383,7 @@
       </c>
       <c r="B904" s="1" t="inlineStr">
         <is>
-          <t>「Suu~... suu~...！」</t>
+          <t>「Suu... suu...!」</t>
         </is>
       </c>
       <c r="C904" t="n">
@@ -14380,8 +14398,8 @@
       </c>
       <c r="B905" s="1" t="inlineStr">
         <is>
-          <t>When I take deep breaths, I can smell Rurichiyo-chan
-all around me.</t>
+          <t>When I take a deep breath, I can fully inhale
+Rurichiyo-chan's scent.</t>
         </is>
       </c>
       <c r="C905" t="n">
@@ -14396,7 +14414,7 @@
       </c>
       <c r="B906" s="1" t="inlineStr">
         <is>
-          <t>Haa... somehow this is so calming...</t>
+          <t>Haah... I somehow feel so calm...</t>
         </is>
       </c>
       <c r="C906" t="n">
@@ -14412,7 +14430,7 @@
       <c r="B907" s="1" t="inlineStr">
         <is>
           <t>Taking advantage of Rurichiyo-chan being half-asleep,
-I couldn't help but snuggle up and be clingy.</t>
+I couldn't help but snuggle up to her.</t>
         </is>
       </c>
       <c r="C907" t="n">
@@ -14427,8 +14445,8 @@
       </c>
       <c r="B908" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan has enough warmth to embrace you like
-that.</t>
+          <t>Rurichiyo-chan has the kind of embracing warmth that
+makes me do that.</t>
         </is>
       </c>
       <c r="C908" t="n">
@@ -14443,8 +14461,8 @@
       </c>
       <c r="B909" s="1" t="inlineStr">
         <is>
-          <t>And even if it did happen, Rurichiyo wouldn’t be
-angry.</t>
+          <t>Besides, even if she did wake up, Rurichiyo-chan
+wouldn't be angry.</t>
         </is>
       </c>
       <c r="C909" t="n">
@@ -14505,8 +14523,8 @@
       </c>
       <c r="B913" s="1" t="inlineStr">
         <is>
-          <t>Maybe she felt what I was feeling, because she called
-me a good boy while stroking my head…</t>
+          <t>Maybe she sensed how I felt; she patted my head while
+saying, "Good boy"...</t>
         </is>
       </c>
       <c r="C913" t="n">
@@ -14521,8 +14539,8 @@
       </c>
       <c r="B914" s="1" t="inlineStr">
         <is>
-          <t>Haha… Rurichiyo-chan really has a rather pleased,
-half-asleep way about her.</t>
+          <t>Haha... Rurichiyo-chan seems rather pleased even
+while half-asleep.</t>
         </is>
       </c>
       <c r="C914" t="n">
@@ -14537,8 +14555,7 @@
       </c>
       <c r="B915" s="1" t="inlineStr">
         <is>
-          <t>Since it's a good chance, I'll give it another good
-rub.</t>
+          <t>Might as well give it another rub.</t>
         </is>
       </c>
       <c r="C915" t="n">
@@ -14568,7 +14585,7 @@
       </c>
       <c r="B917" s="1" t="inlineStr">
         <is>
-          <t>「Mmm... you're such a spoiled baby, aren't you~...」</t>
+          <t>Mmm... you’re such a spoiled little thing~...</t>
         </is>
       </c>
       <c r="C917" t="n">
@@ -14599,8 +14616,8 @@
       </c>
       <c r="B919" s="1" t="inlineStr">
         <is>
-          <t>The more I press my face into her chest, the gentler
-her voice becomes.</t>
+          <t>The more I nuzzle my face into Rurichiyo-chan's
+chest, the more tenderness fills her voice.</t>
         </is>
       </c>
       <c r="C919" t="n">
@@ -14645,7 +14662,7 @@
       </c>
       <c r="B922" s="1" t="inlineStr">
         <is>
-          <t>「Nngh~...! Huh... ufufu!」</t>
+          <t>Mmm~... phew... hee hee...!</t>
         </is>
       </c>
       <c r="C922" t="n">
@@ -14660,8 +14677,8 @@
       </c>
       <c r="B923" s="1" t="inlineStr">
         <is>
-          <t>Leaning against her chest like that, Rurichiyo-chan
-just gets even more pleased.</t>
+          <t>As I snuggle up to her chest, Rurichiyo-chan becomes
+even more pleased.</t>
         </is>
       </c>
       <c r="C923" t="n">
@@ -14676,8 +14693,8 @@
       </c>
       <c r="B924" s="1" t="inlineStr">
         <is>
-          <t>My actions synced up with the way you soothe a baby,
-so I guess I probably started enjoying it.</t>
+          <t>My movements synced with the dream of soothing a
+baby, so I guess I started enjoying it.</t>
         </is>
       </c>
       <c r="C924" t="n">
@@ -14692,8 +14709,8 @@
       </c>
       <c r="B925" s="1" t="inlineStr">
         <is>
-          <t>…Even so, being spoiled by a girl really does make me
-feel so peaceful.</t>
+          <t>Still, being able to act spoiled toward a girl is so
+calming.</t>
         </is>
       </c>
       <c r="C925" t="n">
@@ -14708,7 +14725,7 @@
       </c>
       <c r="B926" s="1" t="inlineStr">
         <is>
-          <t>Ahh... I think I'm about to lose it...</t>
+          <t>Ah... I feel like I'm going to melt...</t>
         </is>
       </c>
       <c r="C926" t="n">
@@ -14755,7 +14772,7 @@
       </c>
       <c r="B929" s="1" t="inlineStr">
         <is>
-          <t>「Mmm~？ What happened~…？」</t>
+          <t>「Mmm~? What's the matter~...?」</t>
         </is>
       </c>
       <c r="C929" t="n">
@@ -14770,8 +14787,8 @@
       </c>
       <c r="B930" s="1" t="inlineStr">
         <is>
-          <t>When I stop being clingy, Rurichiyo-chan gets
-suspicious too.</t>
+          <t>When I stop being clingy, Rurichiyo-chan looks
+puzzled too.</t>
         </is>
       </c>
       <c r="C930" t="n">
@@ -14786,7 +14803,7 @@
       </c>
       <c r="B931" s="1" t="inlineStr">
         <is>
-          <t>I guess she's feeling something, after all...</t>
+          <t>I guess she's feeling something after all...</t>
         </is>
       </c>
       <c r="C931" t="n">
@@ -14816,7 +14833,7 @@
       </c>
       <c r="B933" s="1" t="inlineStr">
         <is>
-          <t>「So, uh... I'll give you my boobies~」</t>
+          <t>S-so... I'll breastfeed you~</t>
         </is>
       </c>
       <c r="C933" t="n">
@@ -14846,7 +14863,7 @@
       </c>
       <c r="B935" s="1" t="inlineStr">
         <is>
-          <t>「Huh............？」</t>
+          <t>「Huh...?」</t>
         </is>
       </c>
       <c r="C935" t="n">
@@ -14861,7 +14878,7 @@
       </c>
       <c r="B936" s="1" t="inlineStr">
         <is>
-          <t>rustle rustle...</t>
+          <t>rustle, rustle...</t>
         </is>
       </c>
       <c r="C936" t="n">
@@ -14892,9 +14909,9 @@
       </c>
       <c r="B938" s="1" t="inlineStr">
         <is>
-          <t>I pretty much knew what kind of dream you were
-having, but to go this far — what a child so full of
-maternal instinct...！</t>
+          <t>I pretty much knew what kind of dream Rurichiyo-chan
+was having, but to go this far—she's so overflowing
+with maternal instinct...!</t>
         </is>
       </c>
       <c r="C938" t="n">
@@ -14925,8 +14942,8 @@
       </c>
       <c r="B940" s="1" t="inlineStr">
         <is>
-          <t>On the other hand, my lower half ends up getting
-bigger from the excitement...</t>
+          <t>On the other hand, my lower half grows larger with
+anticipation...</t>
         </is>
       </c>
       <c r="C940" t="n">
@@ -14941,8 +14958,8 @@
       </c>
       <c r="B941" s="1" t="inlineStr">
         <is>
-          <t>Meanwhile, Rurichiyo-chan gropes at the buttons
-herself, gradually exposing her soft breasts.</t>
+          <t>Meanwhile, Rurichiyo-chan fumbles with the buttons
+herself, gradually baring her soft breasts.</t>
         </is>
       </c>
       <c r="C941" t="n">
@@ -14957,7 +14974,7 @@
       </c>
       <c r="B942" s="1" t="inlineStr">
         <is>
-          <t>……And finally, the front of the pajamas came open.</t>
+          <t>……And finally, the front of her pajamas came undone.</t>
         </is>
       </c>
       <c r="C942" t="n">
@@ -14987,7 +15004,7 @@
       </c>
       <c r="B944" s="1" t="inlineStr">
         <is>
-          <t>「Here you go~... it's boobie-ies~」</t>
+          <t>「Here you go~... it's boobies~」</t>
         </is>
       </c>
       <c r="C944" t="n">
@@ -15002,8 +15019,8 @@
       </c>
       <c r="B945" s="1" t="inlineStr">
         <is>
-          <t>If, literally, she opened her pajamas intending to
-give me her boobs... is that okay？</t>
+          <t>If, literally, she unbuttoned her pajamas intending
+to nurse me... would that be okay?</t>
         </is>
       </c>
       <c r="C945" t="n">
@@ -15033,7 +15050,7 @@
       </c>
       <c r="B947" s="1" t="inlineStr">
         <is>
-          <t>It should be fine！</t>
+          <t>Is this really okay?!</t>
         </is>
       </c>
       <c r="C947" t="n">
@@ -15048,8 +15065,8 @@
       </c>
       <c r="B948" s="1" t="inlineStr">
         <is>
-          <t>At the very least, Rurichiyo-chan is dreaming a
-gentle dream with pure feelings.</t>
+          <t>At the very least, Rurichiyo-chan is having a gentle,
+innocent dream.</t>
         </is>
       </c>
       <c r="C948" t="n">
@@ -15079,8 +15096,8 @@
       </c>
       <c r="B950" s="1" t="inlineStr">
         <is>
-          <t>「Mmm~？ What's wrong...？\nLet's drink lots of boobies,
-okay~...」</t>
+          <t>Mmm~? What's the matter~...? Let's drink lots of
+breast milk, okay~...</t>
         </is>
       </c>
       <c r="C950" t="n">
@@ -15095,8 +15112,8 @@
       </c>
       <c r="B951" s="1" t="inlineStr">
         <is>
-          <t>Above all, even if it was just a dream,
-Rurichiyo-chan was determined to do it.</t>
+          <t>Above all, even if it's just a dream, Rurichiyo-chan
+really intends it.</t>
         </is>
       </c>
       <c r="C951" t="n">
@@ -15141,7 +15158,7 @@
       </c>
       <c r="B954" s="1" t="inlineStr">
         <is>
-          <t>「……………………n, hamu！」</t>
+          <t>「……………………Mmm—munch！」</t>
         </is>
       </c>
       <c r="C954" t="n">
@@ -15156,8 +15173,8 @@
       </c>
       <c r="B955" s="1" t="inlineStr">
         <is>
-          <t>I press my lips to the cherry-pink little nub on her
-tiny breast.</t>
+          <t>I press my lips to the cherry-pink nub of her tiny
+breast.</t>
         </is>
       </c>
       <c r="C955" t="n">
@@ -15187,7 +15204,7 @@
       </c>
       <c r="B957" s="1" t="inlineStr">
         <is>
-          <t>「Nfu！ I did a good job~...」</t>
+          <t>「Nfu! Good job~...」</t>
         </is>
       </c>
       <c r="C957" t="n">
@@ -15218,7 +15235,8 @@
       </c>
       <c r="B959" s="1" t="inlineStr">
         <is>
-          <t>W-what is this… this situation is just too happy…！</t>
+          <t>W-what is this...? This situation is just too
+blissful...!</t>
         </is>
       </c>
       <c r="C959" t="n">
@@ -15248,8 +15266,8 @@
       </c>
       <c r="B961" s="1" t="inlineStr">
         <is>
-          <t>I'm the kind of guy who, even while getting scared of
-being happy, ends up enjoying it.</t>
+          <t>Even though I'm intimidated by this happiness, I find
+myself enjoying it.</t>
         </is>
       </c>
       <c r="C961" t="n">
@@ -15279,7 +15297,7 @@
       </c>
       <c r="B963" s="1" t="inlineStr">
         <is>
-          <t>「C’mon... let’s drink a whole lot more, okay~...」</t>
+          <t>Now... let's drink even more milk, okay~...</t>
         </is>
       </c>
       <c r="C963" t="n">
@@ -15310,9 +15328,9 @@
       </c>
       <c r="B965" s="1" t="inlineStr">
         <is>
-          <t>Well, she's half-asleep, so that's why, but even so I
-can't just ignore this sudden burst of motherly
-instinct！</t>
+          <t>Well, Rurichiyo-chan is half-asleep, but even so I
+can't just leave this display of maternal instinct
+alone!</t>
         </is>
       </c>
       <c r="C965" t="n">
@@ -15342,7 +15360,7 @@
       </c>
       <c r="B967" s="1" t="inlineStr">
         <is>
-          <t>「Nnkh, nnk...！」</t>
+          <t>「Nngh, nngh...！」</t>
         </is>
       </c>
       <c r="C967" t="n">
@@ -15372,7 +15390,7 @@
       </c>
       <c r="B969" s="1" t="inlineStr">
         <is>
-          <t>「Nn... nnn~... Good girl, good girl」</t>
+          <t>Mmm... mmm~... Good job, good job</t>
         </is>
       </c>
       <c r="C969" t="n">
@@ -15387,8 +15405,8 @@
       </c>
       <c r="B970" s="1" t="inlineStr">
         <is>
-          <t>Pretending to be a baby and making "nkunku" noises,
-and then, to my surprise, I got praised...！</t>
+          <t>When I pretended to be a baby and went 'n-kun-ku', I
+was unexpectedly praised...!</t>
         </is>
       </c>
       <c r="C970" t="n">
@@ -15433,7 +15451,7 @@
       </c>
       <c r="B973" s="1" t="inlineStr">
         <is>
-          <t>Might as well lick it too...！</t>
+          <t>I'll even lick it...!</t>
         </is>
       </c>
       <c r="C973" t="n">
@@ -15463,7 +15481,7 @@
       </c>
       <c r="B975" s="1" t="inlineStr">
         <is>
-          <t>「Nngh, lero lero lero lero...」</t>
+          <t>「Nngh, rero rero rero rero...」</t>
         </is>
       </c>
       <c r="C975" t="n">
@@ -15508,8 +15526,9 @@
       </c>
       <c r="B978" s="1" t="inlineStr">
         <is>
-          <t>I stuck my tongue out and licked that little nub, and
-got a sweet, obedient little reaction back.</t>
+          <t>I stuck out my tongue and licked the little nub of
+her nipple, and she gave a sweet, genuine little
+reaction.</t>
         </is>
       </c>
       <c r="C978" t="n">
@@ -15599,7 +15618,7 @@
       </c>
       <c r="B984" s="1" t="inlineStr">
         <is>
-          <t>「Nnnh…？ Huh, fuu, nnnh…！」</t>
+          <t>"Nnnh…? Fuu, nnnh…!"</t>
         </is>
       </c>
       <c r="C984" t="n">
@@ -15630,8 +15649,7 @@
       </c>
       <c r="B986" s="1" t="inlineStr">
         <is>
-          <t>...Oh—could it be you're feeling it?/getting turned
-on?</t>
+          <t>...Oh—could it be you're getting turned on?</t>
         </is>
       </c>
       <c r="C986" t="n">
@@ -15646,10 +15664,10 @@
       </c>
       <c r="B987" s="1" t="inlineStr">
         <is>
-          <t>In the dream I was acting like I was soothing a baby,
-so I played along like that too, but when I think
-about it properly, there's no way I wouldn't feel
-anything if my nipple was being sucked... right?</t>
+          <t>Since it felt like I was soothing a baby in the
+dream, I played along, but when I really think about
+it, there's no way she'd feel nothing if her nipple
+were being sucked... right?</t>
         </is>
       </c>
       <c r="C987" t="n">
@@ -15664,7 +15682,8 @@
       </c>
       <c r="B988" s="1" t="inlineStr">
         <is>
-          <t>Even half-asleep, my body might react and wake up？</t>
+          <t>Even if she's half-asleep, her body might react and
+wake her up.</t>
         </is>
       </c>
       <c r="C988" t="n">
@@ -15709,7 +15728,7 @@
       </c>
       <c r="B991" s="1" t="inlineStr">
         <is>
-          <t>「Nn？　...nnn！」</t>
+          <t>「Nn? ...nnu!」</t>
         </is>
       </c>
       <c r="C991" t="n">
@@ -15739,7 +15758,7 @@
       </c>
       <c r="B993" s="1" t="inlineStr">
         <is>
-          <t>「Nmpf...！」</t>
+          <t>「Mmph...!」</t>
         </is>
       </c>
       <c r="C993" t="n">
@@ -15800,7 +15819,7 @@
       </c>
       <c r="B997" s="1" t="inlineStr">
         <is>
-          <t>「Fah... more, that's better~...？」</t>
+          <t>「Mmm... more, that's better~...?」</t>
         </is>
       </c>
       <c r="C997" t="n">
@@ -15906,7 +15925,7 @@
       </c>
       <c r="B1004" s="1" t="inlineStr">
         <is>
-          <t>「Fuuuuu... nnh, nnhhh...」</t>
+          <t>「Fuuuu... nnu, nnuu...」</t>
         </is>
       </c>
       <c r="C1004" t="n">
@@ -15937,8 +15956,9 @@
       </c>
       <c r="B1006" s="1" t="inlineStr">
         <is>
-          <t>I thought she might wake up... but she seems to be
-sleeping much more carefree than I expected.</t>
+          <t>I thought she might wake up... but Rurichiyo-chan
+seems to be sleeping much more carefree than I
+expected.</t>
         </is>
       </c>
       <c r="C1006" t="n">
@@ -15953,8 +15973,7 @@
       </c>
       <c r="B1007" s="1" t="inlineStr">
         <is>
-          <t>Still, her body is honest about things, one way or
-another...</t>
+          <t>But my body was honest, after all...</t>
         </is>
       </c>
       <c r="C1007" t="n">
@@ -15984,7 +16003,7 @@
       </c>
       <c r="B1009" s="1" t="inlineStr">
         <is>
-          <t>「Faaa... un... uu...」</t>
+          <t>「Faaah... un... uuh...」</t>
         </is>
       </c>
       <c r="C1009" t="n">
@@ -15999,8 +16018,8 @@
       </c>
       <c r="B1010" s="1" t="inlineStr">
         <is>
-          <t>I stuck my tongue out again and was moved by the feel
-of it.</t>
+          <t>I stuck my tongue out again and was struck by how it
+felt.</t>
         </is>
       </c>
       <c r="C1010" t="n">
@@ -16015,8 +16034,8 @@
       </c>
       <c r="B1011" s="1" t="inlineStr">
         <is>
-          <t>The little nub swelled round and felt all stiff and
-prickly...</t>
+          <t>Her little nub puffed up, firm and slightly rough to
+the touch.</t>
         </is>
       </c>
       <c r="C1011" t="n">
@@ -16031,7 +16050,7 @@
       </c>
       <c r="B1012" s="1" t="inlineStr">
         <is>
-          <t>Her nipple's gone erect even as she lies there.</t>
+          <t>Even while she's sleeping, her nipple is erect.</t>
         </is>
       </c>
       <c r="C1012" t="n">
@@ -16061,7 +16080,7 @@
       </c>
       <c r="B1014" s="1" t="inlineStr">
         <is>
-          <t>「Nn... there, there... nn, nn...」</t>
+          <t>「Mmm... there, there... nnh, nnh...」</t>
         </is>
       </c>
       <c r="C1014" t="n">
@@ -16076,9 +16095,9 @@
       </c>
       <c r="B1015" s="1" t="inlineStr">
         <is>
-          <t>And with her natural maternal side in full swing, she
-was feeling it with her nipple while also giving my
-head little there-there pats.</t>
+          <t>And with her innate maternal instincts in full force,
+she was feeling it through her nipple while gently
+patting my head.</t>
         </is>
       </c>
       <c r="C1015" t="n">
@@ -16093,7 +16112,7 @@
       </c>
       <c r="B1016" s="1" t="inlineStr">
         <is>
-          <t>Ah... damn, Rurichiyo-chan is just too cute...！</t>
+          <t>Ah... Rurichiyo-chan is just too cute...!</t>
         </is>
       </c>
       <c r="C1016" t="n">
@@ -16123,7 +16142,7 @@
       </c>
       <c r="B1018" s="1" t="inlineStr">
         <is>
-          <t>「Amm... chu... chu...」</t>
+          <t>「Mmm... smooch... smooch...」</t>
         </is>
       </c>
       <c r="C1018" t="n">
@@ -16153,7 +16172,7 @@
       </c>
       <c r="B1020" s="1" t="inlineStr">
         <is>
-          <t>「Hah... haa...！ Fuwaaah...！」</t>
+          <t>「Hah... haa...! Ahhhh...!」</t>
         </is>
       </c>
       <c r="C1020" t="n">
@@ -16168,8 +16187,8 @@
       </c>
       <c r="B1021" s="1" t="inlineStr">
         <is>
-          <t>Unable to help myself, I latched onto her nipple, and
-Rurichiyo-chan's breath immediately burst out.</t>
+          <t>Unable to help myself, I sucked on her nipple, and
+Rurichiyo-chan immediately let out a gasp.</t>
         </is>
       </c>
       <c r="C1021" t="n">
@@ -16214,7 +16233,7 @@
       </c>
       <c r="B1024" s="1" t="inlineStr">
         <is>
-          <t>「Mmmchu！ Churu, chuku！」</t>
+          <t>「Smooch! Slurp, chuk!」</t>
         </is>
       </c>
       <c r="C1024" t="n">
@@ -16244,7 +16263,7 @@
       </c>
       <c r="B1026" s="1" t="inlineStr">
         <is>
-          <t>「Nnnh！ Faah, haaah...！ Hau, uuh...！」</t>
+          <t>Nnnh... Faaah, haaah...! Hau, uuh...!</t>
         </is>
       </c>
       <c r="C1026" t="n">
@@ -16274,7 +16293,7 @@
       </c>
       <c r="B1028" s="1" t="inlineStr">
         <is>
-          <t>「Ha, hau...n! N'ah...ah! Haa...!」</t>
+          <t>「Ha, hau... nn! N'ah... ah! Haa...!」</t>
         </is>
       </c>
       <c r="C1028" t="n">
@@ -16289,8 +16308,8 @@
       </c>
       <c r="B1029" s="1" t="inlineStr">
         <is>
-          <t>Licking, nibbling, and sucking that little
-cherry‑blossom‑pink nub….</t>
+          <t>Licking, nibbling on, and sucking that little
+cherry-pink nub...</t>
         </is>
       </c>
       <c r="C1029" t="n">
@@ -16305,8 +16324,8 @@
       </c>
       <c r="B1030" s="1" t="inlineStr">
         <is>
-          <t>With a single movement of my tongue-tip,
-Rurichiyo-chan's breath changes.</t>
+          <t>With a single flick of the tip of my tongue,
+Rurichiyo-chan's breathing changes.</t>
         </is>
       </c>
       <c r="C1030" t="n">
@@ -16321,7 +16340,7 @@
       </c>
       <c r="B1031" s="1" t="inlineStr">
         <is>
-          <t>I’m making Rurichiyo-chan feel it…….</t>
+          <t>I'm making Rurichiyo-chan feel it…….</t>
         </is>
       </c>
       <c r="C1031" t="n">
@@ -16336,8 +16355,8 @@
       </c>
       <c r="B1032" s="1" t="inlineStr">
         <is>
-          <t>When that feeling is real, she gets happier than she
-thought she would.</t>
+          <t>When that feeling registers as real, she becomes
+happier than she expected.</t>
         </is>
       </c>
       <c r="C1032" t="n">
@@ -16367,7 +16386,7 @@
       </c>
       <c r="B1034" s="1" t="inlineStr">
         <is>
-          <t>「Nnnu... ah！ Aah！ Nfuuuu！」</t>
+          <t>Nnnh... Ah! Aah! Nfuuuu!</t>
         </is>
       </c>
       <c r="C1034" t="n">
@@ -16382,8 +16401,8 @@
       </c>
       <c r="B1035" s="1" t="inlineStr">
         <is>
-          <t>Every time Rurichiyo-chan let out a sensual little
-sleeping breath, I grew even more dreamy.</t>
+          <t>Every time Rurichiyo-chan exhaled a sultry breath in
+her sleep, I drifted further into a dreamlike state.</t>
         </is>
       </c>
       <c r="C1035" t="n">
@@ -16428,7 +16447,8 @@
       </c>
       <c r="B1038" s="1" t="inlineStr">
         <is>
-          <t>Even if my head was all dreamy, my penis was hard.</t>
+          <t>Even though my head felt dreamlike, my penis was
+hard.</t>
         </is>
       </c>
       <c r="C1038" t="n">
@@ -16443,9 +16463,9 @@
       </c>
       <c r="B1039" s="1" t="inlineStr">
         <is>
-          <t>I got so wrapped up in the baby play I forgot, but I
-felt my lower half getting hot from around the moment
-I saw her chest.</t>
+          <t>I was so absorbed in the baby play I'd forgotten, but
+I could feel my lower half growing aroused from the
+moment I saw her chest.</t>
         </is>
       </c>
       <c r="C1039" t="n">
@@ -16475,7 +16495,7 @@
       </c>
       <c r="B1041" s="1" t="inlineStr">
         <is>
-          <t>「Nn... fuu, nn... nuuu...！」</t>
+          <t>「Mmm... huff, mm... nuu—！」</t>
         </is>
       </c>
       <c r="C1041" t="n">
@@ -16490,9 +16510,9 @@
       </c>
       <c r="B1042" s="1" t="inlineStr">
         <is>
-          <t>Noticing the pulse in my lower half, and then hearing
-Rurichiyo-chan’s sultry little sounds on top of that,
-was unbearable...</t>
+          <t>I noticed the throbbing in my lower half, and hearing
+Rurichiyo-chan's sultry voice on top of that was
+unbearable.</t>
         </is>
       </c>
       <c r="C1042" t="n">
@@ -16538,8 +16558,8 @@
       </c>
       <c r="B1045" s="1" t="inlineStr">
         <is>
-          <t>「Aah... nfa...！ Sucking my boobs so much... good
-girl, dechu~... nfufu！」</t>
+          <t>「Aah... nfa...! You're sucking my breasts so much...
+such a good boy, dechu~... nfufu!」</t>
         </is>
       </c>
       <c r="C1045" t="n">
@@ -16601,7 +16621,7 @@
       </c>
       <c r="B1049" s="1" t="inlineStr">
         <is>
-          <t>「...uuh, uuhh~~~！」</t>
+          <t>「…u-uh, u-uhhh—!」</t>
         </is>
       </c>
       <c r="C1049" t="n">
@@ -16648,7 +16668,7 @@
       </c>
       <c r="B1052" s="1" t="inlineStr">
         <is>
-          <t>「Nn！ Nnngh~~！ Hah, haaa...！」</t>
+          <t>Nn! Nnngh~~! Fah, faaa...!</t>
         </is>
       </c>
       <c r="C1052" t="n">
@@ -16663,9 +16683,8 @@
       </c>
       <c r="B1053" s="1" t="inlineStr">
         <is>
-          <t>However, it's also true that I ended up feeling
-something while dreaming about Rurichiyo-chan giving
-me her breasts….</t>
+          <t>However, it's also true that I couldn't help getting
+aroused while dreaming of Rurichiyo-chan nursing...</t>
         </is>
       </c>
       <c r="C1053" t="n">
@@ -16680,7 +16699,7 @@
       </c>
       <c r="B1054" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan... you're so pure, yet so lewd...！</t>
+          <t>Rurichiyo-chan... so pure, yet so erotic...!</t>
         </is>
       </c>
       <c r="C1054" t="n">
@@ -16710,7 +16729,7 @@
       </c>
       <c r="B1056" s="1" t="inlineStr">
         <is>
-          <t>「...Ugh...」</t>
+          <t>「…u-uh…」</t>
         </is>
       </c>
       <c r="C1056" t="n">
@@ -16771,7 +16790,7 @@
       </c>
       <c r="B1060" s="1" t="inlineStr">
         <is>
-          <t>「Ugh...！ Fuhhh... nn, nngh...！」</t>
+          <t>「Uhh...! fuhhh... nn, nngh...!」</t>
         </is>
       </c>
       <c r="C1060" t="n">
@@ -16786,9 +16805,9 @@
       </c>
       <c r="B1061" s="1" t="inlineStr">
         <is>
-          <t>Ruri, who'd been having her breasts licked
-continuously, also seemed to have gotten pretty
-sensitive.</t>
+          <t>Ruri-chan, whose breasts had been licked
+continuously, also seemed to have become considerably
+more sensitive.</t>
         </is>
       </c>
       <c r="C1061" t="n">
@@ -16803,8 +16822,8 @@
       </c>
       <c r="B1062" s="1" t="inlineStr">
         <is>
-          <t>Even when I wasn't consciously sucking her breasts,
-light gasps kept coming out.</t>
+          <t>Even when I wasn't consciously sucking
+Rurichiyo-chan's breasts, she kept making soft moans.</t>
         </is>
       </c>
       <c r="C1062" t="n">
@@ -16880,8 +16899,8 @@
       </c>
       <c r="B1067" s="1" t="inlineStr">
         <is>
-          <t>If I can just stop the swollen penis from rubbing,
-that alone should make a bit of a difference….</t>
+          <t>If I can just prevent my swollen penis from rubbing,
+that alone should help a little…</t>
         </is>
       </c>
       <c r="C1067" t="n">
@@ -16927,7 +16946,7 @@
       <c r="B1070" s="1" t="inlineStr">
         <is>
           <t>The moment I put my hand into my pants and touched my
-penis, I instantly regretted it terribly.</t>
+penis, I immediately regretted it.</t>
         </is>
       </c>
       <c r="C1070" t="n">
@@ -16942,8 +16961,8 @@
       </c>
       <c r="B1071" s="1" t="inlineStr">
         <is>
-          <t>I only touched it a little… but an incredible bolt of
-pleasure shot through my penis！</t>
+          <t>I had only touched it a little... but an overwhelming
+jolt of pleasure ran through my penis!</t>
         </is>
       </c>
       <c r="C1071" t="n">
@@ -16973,7 +16992,7 @@
       </c>
       <c r="B1073" s="1" t="inlineStr">
         <is>
-          <t>Kuuuh… it feels like I’m about to come… guuuh！</t>
+          <t>Kuuuh... I'm about to cum... guuuh!</t>
         </is>
       </c>
       <c r="C1073" t="n">
@@ -17003,7 +17022,7 @@
       </c>
       <c r="B1075" s="1" t="inlineStr">
         <is>
-          <t>「Nn！　Ahh！　Fuh！　Aaah---！」</t>
+          <t>「Nn! Aah! Fah! Aaah...!」</t>
         </is>
       </c>
       <c r="C1075" t="n">
@@ -17018,9 +17037,9 @@
       </c>
       <c r="B1076" s="1" t="inlineStr">
         <is>
-          <t>I clenched my lips to hold back ejaculation, and
-Rurichiyo-chan, her nipples pressed, let out a
-heartrending cry as if overcome.</t>
+          <t>I pressed my lips together to hold back ejaculation,
+and Rurichiyo-chan, her nipples being pressed, let
+out a cry as if she were overcome.</t>
         </is>
       </c>
       <c r="C1076" t="n">
@@ -17035,8 +17054,8 @@
       </c>
       <c r="B1077" s="1" t="inlineStr">
         <is>
-          <t>At the same time, the last thread of my tension
-snapped….</t>
+          <t>At the same time, the last thread of my composure
+snapped...</t>
         </is>
       </c>
       <c r="C1077" t="n">
@@ -17051,7 +17070,7 @@
       </c>
       <c r="B1078" s="1" t="inlineStr">
         <is>
-          <t>Byu！　Byubyu！　Byuku！　Byuku！</t>
+          <t>Spurt! Spurt-spurt! Spurt! Spurt!</t>
         </is>
       </c>
       <c r="C1078" t="n">
@@ -17081,8 +17100,8 @@
       </c>
       <c r="B1080" s="1" t="inlineStr">
         <is>
-          <t>…Reacting to Rurichiyo-chan's lustful voice, I too
-was overwhelmed.</t>
+          <t>…Reacting to Rurichiyo-chan's sultry voice, I too was
+overcome.</t>
         </is>
       </c>
       <c r="C1080" t="n">
@@ -17097,8 +17116,8 @@
       </c>
       <c r="B1081" s="1" t="inlineStr">
         <is>
-          <t>I hadn’t noticed, but had I been getting gradually
-more aroused？</t>
+          <t>Had I been getting gradually more aroused without
+realizing it?</t>
         </is>
       </c>
       <c r="C1081" t="n">
@@ -17159,7 +17178,7 @@
       </c>
       <c r="B1085" s="1" t="inlineStr">
         <is>
-          <t>「Huu… huuu… …alright, alright…」</t>
+          <t>「Huff... huff... ...Okay, okay...」</t>
         </is>
       </c>
       <c r="C1085" t="n">
@@ -17205,8 +17224,8 @@
       </c>
       <c r="B1088" s="1" t="inlineStr">
         <is>
-          <t>Feeling saved, I lifted my face and stared at
-Rurichiyo-chan's face.</t>
+          <t>I looked up, feeling relieved, and gazed at
+Rurichiyo-chan.</t>
         </is>
       </c>
       <c r="C1088" t="n">
@@ -17296,7 +17315,7 @@
       </c>
       <c r="B1094" s="1" t="inlineStr">
         <is>
-          <t>Awake…？</t>
+          <t>Are you awake...?</t>
         </is>
       </c>
       <c r="C1094" t="n">
@@ -17326,7 +17345,7 @@
       </c>
       <c r="B1096" s="1" t="inlineStr">
         <is>
-          <t>「Ruri, Rurichiyo-chan… ah… um…」</t>
+          <t>「Ruri, Chiyo-chan… ah… um…」</t>
         </is>
       </c>
       <c r="C1096" t="n">
@@ -17356,7 +17375,7 @@
       </c>
       <c r="B1098" s="1" t="inlineStr">
         <is>
-          <t>「Nfufu… fwaa…」</t>
+          <t>「Heh heh... yawn...」</t>
         </is>
       </c>
       <c r="C1098" t="n">
@@ -17371,9 +17390,8 @@
       </c>
       <c r="B1099" s="1" t="inlineStr">
         <is>
-          <t>In front of me, who was at a loss for words,
-Rurichiyo-chan smiled softly and lazily let out a
-yawn.</t>
+          <t>Before me, at a loss for words, Rurichiyo-chan smiled
+softly and let out a lazy yawn.</t>
         </is>
       </c>
       <c r="C1099" t="n">
@@ -17403,7 +17421,7 @@
       </c>
       <c r="B1101" s="1" t="inlineStr">
         <is>
-          <t>「Ruri... it felt really good...」</t>
+          <t>「Ruri... felt really good...」</t>
         </is>
       </c>
       <c r="C1101" t="n">
@@ -17494,8 +17512,7 @@
       </c>
       <c r="B1107" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan gave me a gentle smile directed at my
-dumbfounded self.</t>
+          <t>Rurichiyo-chan smiled gently at me.</t>
         </is>
       </c>
       <c r="C1107" t="n">
@@ -17525,7 +17542,7 @@
       </c>
       <c r="B1109" s="1" t="inlineStr">
         <is>
-          <t>「Ufufu... fwaa... nnu...」</t>
+          <t>「Heh heh... yawn... mmm...」</t>
         </is>
       </c>
       <c r="C1109" t="n">
@@ -17540,7 +17557,7 @@
       </c>
       <c r="B1110" s="1" t="inlineStr">
         <is>
-          <t>...Then her eyelids fell.</t>
+          <t>…And then her eyelids drooped.</t>
         </is>
       </c>
       <c r="C1110" t="n">
@@ -17570,7 +17587,7 @@
       </c>
       <c r="B1112" s="1" t="inlineStr">
         <is>
-          <t>「Suu~... nnu... suu~... nnu...」</t>
+          <t>「Inhale... mmm... inhale... mmm...」</t>
         </is>
       </c>
       <c r="C1112" t="n">
@@ -17585,8 +17602,7 @@
       </c>
       <c r="B1113" s="1" t="inlineStr">
         <is>
-          <t>...Or rather, she began to breathe peacefully in her
-sleep.</t>
+          <t>…Then she began to breathe soundly in her sleep.</t>
         </is>
       </c>
       <c r="C1113" t="n">
@@ -17601,7 +17617,7 @@
       </c>
       <c r="B1114" s="1" t="inlineStr">
         <is>
-          <t>Huh？ Maybe she was half-asleep the whole time？</t>
+          <t>Huh? Maybe she was half-asleep until the very end?</t>
         </is>
       </c>
       <c r="C1114" t="n">
@@ -17631,7 +17647,7 @@
       </c>
       <c r="B1116" s="1" t="inlineStr">
         <is>
-          <t>「Suu~... nnu... suu~... nnu...」</t>
+          <t>「Inhale... mmm... inhale... mmm...」</t>
         </is>
       </c>
       <c r="C1116" t="n">
@@ -17662,8 +17678,9 @@
       </c>
       <c r="B1118" s="1" t="inlineStr">
         <is>
-          <t>She'd been half in a dream from the start... I hoped
-she'd been half-asleep the whole time till the end...</t>
+          <t>Rurichiyo-chan had been in a dreamlike state from the
+start... I want to believe she was half-asleep the
+whole time until the end...</t>
         </is>
       </c>
       <c r="C1118" t="n">
@@ -17726,7 +17743,7 @@
       </c>
       <c r="B1122" s="1" t="inlineStr">
         <is>
-          <t>「Suu~... nnu... suu~... nnu...」</t>
+          <t>「Inhale... mmm... inhale... mmm...」</t>
         </is>
       </c>
       <c r="C1122" t="n">
@@ -17741,8 +17758,7 @@
       </c>
       <c r="B1123" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan kept breathing the same peaceful sleep
-breaths.</t>
+          <t>Rurichiyo-chan continued to breathe peacefully.</t>
         </is>
       </c>
       <c r="C1123" t="n">
@@ -17757,7 +17773,7 @@
       </c>
       <c r="B1124" s="1" t="inlineStr">
         <is>
-          <t>Yeah, she's definitely out cold...</t>
+          <t>Yeah, Rurichiyo-chan's definitely fast asleep...</t>
         </is>
       </c>
       <c r="C1124" t="n">
@@ -17803,7 +17819,7 @@
       </c>
       <c r="B1127" s="1" t="inlineStr">
         <is>
-          <t>...Still, Rurichiyo-chan was so kind...</t>
+          <t>...Still, Rurichiyo-chan was kind...</t>
         </is>
       </c>
       <c r="C1127" t="n">
@@ -17818,8 +17834,8 @@
       </c>
       <c r="B1128" s="1" t="inlineStr">
         <is>
-          <t>She's always sweet, but when she's half-asleep she's
-even more gentle...</t>
+          <t>Rurichiyo-chan's usually like that, but when she was
+half-asleep she seemed even gentler...</t>
         </is>
       </c>
       <c r="C1128" t="n">
@@ -17834,7 +17850,7 @@
       </c>
       <c r="B1129" s="1" t="inlineStr">
         <is>
-          <t>I've never been petted like that before... hmm.</t>
+          <t>I've never been patted like that before... hmm.</t>
         </is>
       </c>
       <c r="C1129" t="n">
@@ -17849,7 +17865,7 @@
       </c>
       <c r="B1130" s="1" t="inlineStr">
         <is>
-          <t>Being petted is a wonderful thing...！</t>
+          <t>Being patted is a wonderful thing...!</t>
         </is>
       </c>
       <c r="C1130" t="n">
@@ -17880,7 +17896,7 @@
       </c>
       <c r="B1132" s="1" t="inlineStr">
         <is>
-          <t>...I'll go to Nono-chan's place！</t>
+          <t>...I'll go to Nono-chan's place!</t>
         </is>
       </c>
       <c r="C1132" t="n">
@@ -17895,8 +17911,8 @@
       </c>
       <c r="B1133" s="1" t="inlineStr">
         <is>
-          <t>I still don't know Nono-chan very well either, so I
-think it's a good chance to get closer to her.</t>
+          <t>I don't really know Nono-chan well yet, so I think
+this is a good opportunity to get to know her better.</t>
         </is>
       </c>
       <c r="C1133" t="n">
@@ -17911,8 +17927,8 @@
       </c>
       <c r="B1134" s="1" t="inlineStr">
         <is>
-          <t>It's also her first night on this island, so she must
-be feeling a bit uneasy.</t>
+          <t>It's also Nono-chan's first night on this island, so
+she must be feeling a bit uneasy.</t>
         </is>
       </c>
       <c r="C1134" t="n">
@@ -17927,9 +17943,8 @@
       </c>
       <c r="B1135" s="1" t="inlineStr">
         <is>
-          <t>Even if people call her 'teacher', she's still so
-little, so I have to be the one to look out for
-her...！</t>
+          <t>Even if you call her 'Sensei', she's still so small,
+so I have to be the one to look out for her...!</t>
         </is>
       </c>
       <c r="C1135" t="n">
@@ -17959,7 +17974,7 @@
       </c>
       <c r="B1137" s="1" t="inlineStr">
         <is>
-          <t>...I tiptoe down the hallway at night.</t>
+          <t>...I tiptoed down the hallway at night.</t>
         </is>
       </c>
       <c r="C1137" t="n">
@@ -17974,10 +17989,10 @@
       </c>
       <c r="B1138" s="1" t="inlineStr">
         <is>
-          <t>I'm not doing anything wrong, so I could walk in
-confidently, but thinking about going to a girl's
-room this late at night brings along a certain kind
-of nervousness.</t>
+          <t>I'm not doing anything wrong, so I should be able to
+walk confidently, but when I think about going to a
+girl's room this late at night, a certain kind of
+nervousness lingers.</t>
         </is>
       </c>
       <c r="C1138" t="n">
@@ -17992,8 +18007,7 @@
       </c>
       <c r="B1139" s="1" t="inlineStr">
         <is>
-          <t>Besides, I don't dislike walking like this at this
-hour.</t>
+          <t>Besides, I don't mind walking like this.</t>
         </is>
       </c>
       <c r="C1139" t="n">
@@ -18008,9 +18022,9 @@
       </c>
       <c r="B1140" s="1" t="inlineStr">
         <is>
-          <t>What I'm saying now is the complete opposite of
-earlier, but it makes my heart race like I'm sneaking
-in for a night visit.</t>
+          <t>It's the exact opposite of what I said earlier, but
+it makes my heart race as if I'm going to sneak into
+someone's bed at night.</t>
         </is>
       </c>
       <c r="C1140" t="n">
@@ -18025,8 +18039,7 @@
       </c>
       <c r="B1141" s="1" t="inlineStr">
         <is>
-          <t>No... but the purpose is strictly to just sleep
-beside her.</t>
+          <t>No... but my aim is really just to sleep next to her.</t>
         </is>
       </c>
       <c r="C1141" t="n">
@@ -18056,9 +18069,9 @@
       </c>
       <c r="B1143" s="1" t="inlineStr">
         <is>
-          <t>But, but, a guy and a girl living under the same roof
-— it'd be weird if they didn't end up slipping up,
-right~?</t>
+          <t>But, but, when a guy and a girl live under the same
+roof — it would be strange if they didn't end up
+making a mistake, right~?</t>
         </is>
       </c>
       <c r="C1143" t="n">
@@ -18088,8 +18101,8 @@
       </c>
       <c r="B1145" s="1" t="inlineStr">
         <is>
-          <t>...Alright, we're about to get to Rurichiyo-chan and
-Nono-chan's room.</t>
+          <t>...Well, I'm almost at Rurichiyo-chan and Nono-chan's
+room.</t>
         </is>
       </c>
       <c r="C1145" t="n">
@@ -18165,7 +18178,7 @@
       </c>
       <c r="B1150" s="1" t="inlineStr">
         <is>
-          <t>「Foah...！？」</t>
+          <t>「Whoa...!?」</t>
         </is>
       </c>
       <c r="C1150" t="n">
@@ -18180,8 +18193,8 @@
       </c>
       <c r="B1151" s="1" t="inlineStr">
         <is>
-          <t>When I turned my head toward the voice, Nono-chan was
-standing down the hallway.</t>
+          <t>I turned my head at the sound and saw Nono-chan
+standing at the far end of the hallway.</t>
         </is>
       </c>
       <c r="C1151" t="n">
@@ -18211,7 +18224,7 @@
       </c>
       <c r="B1153" s="1" t="inlineStr">
         <is>
-          <t>Animal pajamas are so cute...！</t>
+          <t>Those animal pajamas are so cute...!</t>
         </is>
       </c>
       <c r="C1153" t="n">
@@ -18241,7 +18254,7 @@
       </c>
       <c r="B1155" s="1" t="inlineStr">
         <is>
-          <t>「What are you doing... at this time？」</t>
+          <t>What are you doing here at this hour...?</t>
         </is>
       </c>
       <c r="C1155" t="n">
@@ -18256,8 +18269,7 @@
       </c>
       <c r="B1156" s="1" t="inlineStr">
         <is>
-          <t>A reasonable question, but kind of obvious on
-purpose, huh.</t>
+          <t>It's a fair question, but it's a bit contrived.</t>
         </is>
       </c>
       <c r="C1156" t="n">
@@ -18287,8 +18299,8 @@
       </c>
       <c r="B1158" s="1" t="inlineStr">
         <is>
-          <t>「Ah, no, it's about what happened during Sugoroku—I
-came to sleep next to you...！」</t>
+          <t>「Ah—no, it's about that thing from when we played
+Sugoroku. I came to sleep next to you...!」</t>
         </is>
       </c>
       <c r="C1158" t="n">
@@ -18303,8 +18315,9 @@
       </c>
       <c r="B1159" s="1" t="inlineStr">
         <is>
-          <t>I had gotten worked up on the way here, so I said it
-in a very upbeat way, though trying not to shout.</t>
+          <t>I had gotten excited on the way here, so I said it in
+a very cheerful tone while trying not to raise my
+voice.</t>
         </is>
       </c>
       <c r="C1159" t="n">
@@ -18319,7 +18332,7 @@
       </c>
       <c r="B1160" s="1" t="inlineStr">
         <is>
-          <t>Nono</t>
+          <t>Nono-chan</t>
         </is>
       </c>
       <c r="C1160" t="n">
@@ -18334,7 +18347,7 @@
       </c>
       <c r="B1161" s="1" t="inlineStr">
         <is>
-          <t>「So！ So-so, to sleep...！？」</t>
+          <t>"S-S-So... t-to sleep next to me...!?"</t>
         </is>
       </c>
       <c r="C1161" t="n">
@@ -18364,8 +18377,8 @@
       </c>
       <c r="B1163" s="1" t="inlineStr">
         <is>
-          <t>I was certain. Nono was the one who wrote 'sleep
-beside me'.</t>
+          <t>I was certain that Nono-chan was the one who wrote
+'sleep next to me'.</t>
         </is>
       </c>
       <c r="C1163" t="n">
@@ -18395,7 +18408,7 @@
       </c>
       <c r="B1165" s="1" t="inlineStr">
         <is>
-          <t>「T-to Rurichiyo-chan... you mean...？」</t>
+          <t>「T-to Rurichiyo-chan...?」</t>
         </is>
       </c>
       <c r="C1165" t="n">
@@ -18455,7 +18468,7 @@
       </c>
       <c r="B1169" s="1" t="inlineStr">
         <is>
-          <t>「Eh... Eeh~！？」</t>
+          <t>「Eh... Eeeh~!?」</t>
         </is>
       </c>
       <c r="C1169" t="n">
@@ -18486,8 +18499,9 @@
       </c>
       <c r="B1171" s="1" t="inlineStr">
         <is>
-          <t>She blushed and tried to cover it up, but she'd
-obviously expected it, so it came out naturally.</t>
+          <t>She blushed and tried to play it off, but she had
+expected it too, so that reaction probably came
+naturally.</t>
         </is>
       </c>
       <c r="C1171" t="n">
@@ -18502,8 +18516,7 @@
       </c>
       <c r="B1172" s="1" t="inlineStr">
         <is>
-          <t>...Alright, this calls for a straightforward
-approach.</t>
+          <t>...Alright, let's go straight for it.</t>
         </is>
       </c>
       <c r="C1172" t="n">
@@ -18549,7 +18562,7 @@
       </c>
       <c r="B1175" s="1" t="inlineStr">
         <is>
-          <t>Nono</t>
+          <t>Nono-chan</t>
         </is>
       </c>
       <c r="C1175" t="n">
@@ -18564,7 +18577,7 @@
       </c>
       <c r="B1176" s="1" t="inlineStr">
         <is>
-          <t>「Eh！？ Wh-what are you talking about...？」</t>
+          <t>「Eh!? W-what are you talking about...?」</t>
         </is>
       </c>
       <c r="C1176" t="n">
@@ -18625,7 +18638,7 @@
       </c>
       <c r="B1180" s="1" t="inlineStr">
         <is>
-          <t>「Hwaa！？ I-I-I'm just... I couldn't sleep, that's all」</t>
+          <t>Wah!? I-I'm just... I couldn't sleep.</t>
         </is>
       </c>
       <c r="C1180" t="n">
@@ -18670,8 +18683,8 @@
       </c>
       <c r="B1183" s="1" t="inlineStr">
         <is>
-          <t>「Yeah. It's understandable since the environment
-changed, right?」</t>
+          <t>「Yeah. It can't be helped — the environment changed,
+after all, right?」</t>
         </is>
       </c>
       <c r="C1183" t="n">
@@ -18716,8 +18729,8 @@
       </c>
       <c r="B1186" s="1" t="inlineStr">
         <is>
-          <t>When I hit her directly with plain words and then
-backed off a bit, Nono-chan was at a loss for words.</t>
+          <t>After I said it bluntly and then stepped back a bit,
+Nono-chan was at a loss for words.</t>
         </is>
       </c>
       <c r="C1186" t="n">
@@ -18732,7 +18745,7 @@
       </c>
       <c r="B1187" s="1" t="inlineStr">
         <is>
-          <t>In other words, that's exactly right...！</t>
+          <t>So I was right...!</t>
         </is>
       </c>
       <c r="C1187" t="n">
@@ -18763,8 +18776,8 @@
       </c>
       <c r="B1189" s="1" t="inlineStr">
         <is>
-          <t>I get it. If I go out of my way to flaunt that I
-know, she might end up hating me.</t>
+          <t>I understand. If I go out of my way to make a show of
+knowing, Nono-chan will probably end up disliking me.</t>
         </is>
       </c>
       <c r="C1189" t="n">
@@ -18779,7 +18792,7 @@
       </c>
       <c r="B1190" s="1" t="inlineStr">
         <is>
-          <t>Then, this is a waiting move...</t>
+          <t>In that case, the best move is to wait.</t>
         </is>
       </c>
       <c r="C1190" t="n">
@@ -18839,7 +18852,7 @@
       </c>
       <c r="B1194" s="1" t="inlineStr">
         <is>
-          <t>But I deliberately pretended to stay quiet and watch.</t>
+          <t>But I, too, deliberately remained silent and watched.</t>
         </is>
       </c>
       <c r="C1194" t="n">
@@ -18854,9 +18867,8 @@
       </c>
       <c r="B1195" s="1" t="inlineStr">
         <is>
-          <t>...And then, unable to stand the silence any longer,
-Nono-chan finally began to make a low, whimpering
-sound.</t>
+          <t>...And then, unable to bear the silence any longer,
+Nono-chan finally began to let out a low groan.</t>
         </is>
       </c>
       <c r="C1195" t="n">
@@ -18871,7 +18883,7 @@
       </c>
       <c r="B1196" s="1" t="inlineStr">
         <is>
-          <t>Nono</t>
+          <t>Nono-chan</t>
         </is>
       </c>
       <c r="C1196" t="n">
@@ -18886,7 +18898,7 @@
       </c>
       <c r="B1197" s="1" t="inlineStr">
         <is>
-          <t>「U- uh... ugh... actually, I have a favor to ask.」</t>
+          <t>「U- uuu... ugh... actually, I have a favor to ask.」</t>
         </is>
       </c>
       <c r="C1197" t="n">
@@ -18931,8 +18943,8 @@
       </c>
       <c r="B1200" s="1" t="inlineStr">
         <is>
-          <t>I acted like I was starting from a completely blank
-state as I spoke.</t>
+          <t>I made a point of speaking as if I were starting from
+a completely blank slate.</t>
         </is>
       </c>
       <c r="C1200" t="n">
@@ -18978,9 +18990,9 @@
       </c>
       <c r="B1203" s="1" t="inlineStr">
         <is>
-          <t>「Um... could you sleep beside me... I mean, before
-going to sleep, do something like what Mom always
-used to do...」</t>
+          <t>Um... could you sleep beside me...? I mean, before I
+go to sleep, I was wondering if you could do what Mom
+always did for me...</t>
         </is>
       </c>
       <c r="C1203" t="n">
@@ -19011,8 +19023,8 @@
       </c>
       <c r="B1205" s="1" t="inlineStr">
         <is>
-          <t>Her wording was a bit roundabout, but I understood
-what she wanted.</t>
+          <t>Her phrasing was a bit roundabout, but I understood
+what she wanted me to do.</t>
         </is>
       </c>
       <c r="C1205" t="n">
@@ -19042,7 +19054,7 @@
       </c>
       <c r="B1207" s="1" t="inlineStr">
         <is>
-          <t>「If I'm all right, I'll help.」</t>
+          <t>Understood. If you'd like me, I'll help.</t>
         </is>
       </c>
       <c r="C1207" t="n">
@@ -19072,7 +19084,7 @@
       </c>
       <c r="B1209" s="1" t="inlineStr">
         <is>
-          <t>「Ah... yes！」</t>
+          <t>「Ah... y-yes!」</t>
         </is>
       </c>
       <c r="C1209" t="n">
@@ -19103,8 +19115,8 @@
       </c>
       <c r="B1211" s="1" t="inlineStr">
         <is>
-          <t>I'm probably a bit less nervous now, so... is it okay
-if I let loose like I usually do?</t>
+          <t>I'm probably a bit less nervous now, so... would it
+be okay if I relaxed and acted like I usually do?</t>
         </is>
       </c>
       <c r="C1211" t="n">
@@ -19164,7 +19176,7 @@
       </c>
       <c r="B1215" s="1" t="inlineStr">
         <is>
-          <t>「Ah... not here, it's a bit...」</t>
+          <t>Ah... not here... that's a little...</t>
         </is>
       </c>
       <c r="C1215" t="n">
@@ -19209,7 +19221,7 @@
       </c>
       <c r="B1218" s="1" t="inlineStr">
         <is>
-          <t>Nono</t>
+          <t>Nono-chan</t>
         </is>
       </c>
       <c r="C1218" t="n">
@@ -19224,7 +19236,7 @@
       </c>
       <c r="B1219" s="1" t="inlineStr">
         <is>
-          <t>「Ah... n-no... that, um, is a bit...」</t>
+          <t>「Ah... n-no... that's a bit... too...」</t>
         </is>
       </c>
       <c r="C1219" t="n">
@@ -19254,8 +19266,8 @@
       </c>
       <c r="B1221" s="1" t="inlineStr">
         <is>
-          <t>Is it embarrassing to be in the same room as
-Rurichiyo-chan？</t>
+          <t>Would it be embarrassing to do that in the same room
+as Rurichiyo-chan?</t>
         </is>
       </c>
       <c r="C1221" t="n">
@@ -19270,7 +19282,7 @@
       </c>
       <c r="B1222" s="1" t="inlineStr">
         <is>
-          <t>U-uhmm... that might, maybe, possibly be the case...</t>
+          <t>U-uh... that just might happen...</t>
         </is>
       </c>
       <c r="C1222" t="n">
@@ -19300,7 +19312,7 @@
       </c>
       <c r="B1224" s="1" t="inlineStr">
         <is>
-          <t>「So, wanna come to my room？」</t>
+          <t>「So, do you want to come to my room?」</t>
         </is>
       </c>
       <c r="C1224" t="n">
@@ -19360,7 +19372,7 @@
       </c>
       <c r="B1228" s="1" t="inlineStr">
         <is>
-          <t>「Y-yes……」</t>
+          <t>「y-yes...」</t>
         </is>
       </c>
       <c r="C1228" t="n">
@@ -19390,7 +19402,7 @@
       </c>
       <c r="B1230" s="1" t="inlineStr">
         <is>
-          <t>Maybe nothing would happen after all…….</t>
+          <t>Maybe it won't happen after all...</t>
         </is>
       </c>
       <c r="C1230" t="n">
@@ -19496,7 +19508,7 @@
       </c>
       <c r="B1237" s="1" t="inlineStr">
         <is>
-          <t>「Ah... ah, nngh... n~...」</t>
+          <t>「Ah... nn... n~...」</t>
         </is>
       </c>
       <c r="C1237" t="n">
@@ -19542,8 +19554,8 @@
       </c>
       <c r="B1240" s="1" t="inlineStr">
         <is>
-          <t>By the way, my room used to be a closet, but it's
-also the highest room, so it has a great view.</t>
+          <t>By the way, my room was originally a closet, but it's
+also the highest room, so it has a nice view.</t>
         </is>
       </c>
       <c r="C1240" t="n">
@@ -19558,8 +19570,7 @@
       </c>
       <c r="B1241" s="1" t="inlineStr">
         <is>
-          <t>Kids who come to my room for the first time always
-latch onto that.</t>
+          <t>First-time visitors to my room always zero in on it.</t>
         </is>
       </c>
       <c r="C1241" t="n">
@@ -19574,8 +19585,8 @@
       </c>
       <c r="B1242" s="1" t="inlineStr">
         <is>
-          <t>That usually gets the conversation going, but
-unfortunately that advantage doesn't help at night.</t>
+          <t>That would usually get the conversation going, but
+unfortunately that advantage isn't there at night.</t>
         </is>
       </c>
       <c r="C1242" t="n">
@@ -19621,8 +19632,8 @@
       </c>
       <c r="B1245" s="1" t="inlineStr">
         <is>
-          <t>「So then, what did Mom do for you before she went to
-bed？」</t>
+          <t>So... what did Mama do for you before she went to
+bed?</t>
         </is>
       </c>
       <c r="C1245" t="n">
@@ -19652,8 +19663,8 @@
       </c>
       <c r="B1247" s="1" t="inlineStr">
         <is>
-          <t>「Ah, yes... um, well... so... she would... do it like
-this... ugh...」</t>
+          <t>"Ah, y-yes... um, well... she would... do it like
+this... ugh..."</t>
         </is>
       </c>
       <c r="C1247" t="n">
@@ -19715,8 +19726,8 @@
       </c>
       <c r="B1251" s="1" t="inlineStr">
         <is>
-          <t>「...If it's hard to explain, why don't you just show
-me... I'll try to imitate it.」</t>
+          <t>"If it's hard to explain, why don't you just try
+doing it... I'll imitate you."</t>
         </is>
       </c>
       <c r="C1251" t="n">
@@ -19731,7 +19742,8 @@
       </c>
       <c r="B1252" s="1" t="inlineStr">
         <is>
-          <t>I suggest it indirectly, but in a restrained tone.</t>
+          <t>I try prompting her subtly, keeping my tone
+restrained.</t>
         </is>
       </c>
       <c r="C1252" t="n">
@@ -19761,7 +19773,7 @@
       </c>
       <c r="B1254" s="1" t="inlineStr">
         <is>
-          <t>「Ah...！ Yes！ ...Then... please, do it that way...」</t>
+          <t>"Ah...! Yes...! Then... please do it like that..."</t>
         </is>
       </c>
       <c r="C1254" t="n">
@@ -19776,8 +19788,8 @@
       </c>
       <c r="B1255" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan seemed startled for a moment, but she kept
-getting more and more downbeat.</t>
+          <t>Nono-chan seemed startled for a moment, but she grew
+increasingly subdued.</t>
         </is>
       </c>
       <c r="C1255" t="n">
@@ -19792,7 +19804,7 @@
       </c>
       <c r="B1256" s="1" t="inlineStr">
         <is>
-          <t>Did she say it and now can't back out？</t>
+          <t>Maybe she said it and now she can't back out?</t>
         </is>
       </c>
       <c r="C1256" t="n">
@@ -19807,7 +19819,7 @@
       </c>
       <c r="B1257" s="1" t="inlineStr">
         <is>
-          <t>Nono</t>
+          <t>Nono-chan</t>
         </is>
       </c>
       <c r="C1257" t="n">
@@ -19853,7 +19865,7 @@
       </c>
       <c r="B1260" s="1" t="inlineStr">
         <is>
-          <t>「Yeah, sure. What is it？」</t>
+          <t>「Yeah? What is it?」</t>
         </is>
       </c>
       <c r="C1260" t="n">
@@ -19930,8 +19942,8 @@
       </c>
       <c r="B1265" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan, thinking it over as she spoke, threaded
-together clear words.</t>
+          <t>Although she had to think it over, Nono-chan formed
+her words clearly.</t>
         </is>
       </c>
       <c r="C1265" t="n">
@@ -19946,8 +19958,8 @@
       </c>
       <c r="B1266" s="1" t="inlineStr">
         <is>
-          <t>I don't know what she's going to do, but maybe it's
-not as big a deal as I expected.</t>
+          <t>I don't know what she's going to do, but it might not
+be such a big deal after all.</t>
         </is>
       </c>
       <c r="C1266" t="n">
@@ -20022,7 +20034,7 @@
       </c>
       <c r="B1271" s="1" t="inlineStr">
         <is>
-          <t>...Now she wants it kept secret, huh.</t>
+          <t>So this time it's 'keep it a secret,' huh.</t>
         </is>
       </c>
       <c r="C1271" t="n">
@@ -20082,7 +20094,7 @@
       </c>
       <c r="B1275" s="1" t="inlineStr">
         <is>
-          <t>After a short pause, Nono-chan psychs herself up.</t>
+          <t>After a brief pause, Nono-chan psyched herself up.</t>
         </is>
       </c>
       <c r="C1275" t="n">
@@ -20128,8 +20140,8 @@
       </c>
       <c r="B1278" s="1" t="inlineStr">
         <is>
-          <t>Then, with that same resolve, she suddenly pulled
-back.</t>
+          <t>Just when I thought so, Nono-chan pulled back, her
+resolve still intact.</t>
         </is>
       </c>
       <c r="C1278" t="n">
@@ -20159,7 +20171,7 @@
       </c>
       <c r="B1280" s="1" t="inlineStr">
         <is>
-          <t>「Now, this time for real... here I go...」</t>
+          <t>「Alright... this time I'm really going...」</t>
         </is>
       </c>
       <c r="C1280" t="n">
@@ -20189,7 +20201,7 @@
       </c>
       <c r="B1282" s="1" t="inlineStr">
         <is>
-          <t>「Okay.」</t>
+          <t>「Yeah.」</t>
         </is>
       </c>
       <c r="C1282" t="n">
@@ -20219,7 +20231,7 @@
       </c>
       <c r="B1284" s="1" t="inlineStr">
         <is>
-          <t>「Answer me seriously！」</t>
+          <t>「Please answer me seriously!」</t>
         </is>
       </c>
       <c r="C1284" t="n">
@@ -20249,7 +20261,7 @@
       </c>
       <c r="B1286" s="1" t="inlineStr">
         <is>
-          <t>And she had a more serious look than usual.</t>
+          <t>She also looked unusually serious.</t>
         </is>
       </c>
       <c r="C1286" t="n">
@@ -20264,7 +20276,7 @@
       </c>
       <c r="B1287" s="1" t="inlineStr">
         <is>
-          <t>My breathing's gotten rougher — what's going on？</t>
+          <t>My breath's getting ragged too; what's going on?</t>
         </is>
       </c>
       <c r="C1287" t="n">
@@ -20370,7 +20382,7 @@
       </c>
       <c r="B1294" s="1" t="inlineStr">
         <is>
-          <t>「………!？!」</t>
+          <t>「...!?」</t>
         </is>
       </c>
       <c r="C1294" t="n">
@@ -20385,7 +20397,7 @@
       </c>
       <c r="B1295" s="1" t="inlineStr">
         <is>
-          <t>It was so sudden that I was taken aback.</t>
+          <t>I was also taken aback by how sudden it was.</t>
         </is>
       </c>
       <c r="C1295" t="n">
@@ -20415,7 +20427,7 @@
       </c>
       <c r="B1297" s="1" t="inlineStr">
         <is>
-          <t>She patted my head gently.</t>
+          <t>Nono-chan gently patted my head.</t>
         </is>
       </c>
       <c r="C1297" t="n">
@@ -20430,8 +20442,8 @@
       </c>
       <c r="B1298" s="1" t="inlineStr">
         <is>
-          <t>Then, she drew her cheek close and rubbed cheek to
-cheek.</t>
+          <t>Then, Nono-chan leaned in and rubbed her cheek
+against mine.</t>
         </is>
       </c>
       <c r="C1298" t="n">
@@ -20446,7 +20458,7 @@
       </c>
       <c r="B1299" s="1" t="inlineStr">
         <is>
-          <t>She did this on both sides.</t>
+          <t>Nono-chan did the same on both sides.</t>
         </is>
       </c>
       <c r="C1299" t="n">
@@ -20461,7 +20473,7 @@
       </c>
       <c r="B1300" s="1" t="inlineStr">
         <is>
-          <t>And then I was hugged tight.</t>
+          <t>Then Nono-chan hugged me tightly.</t>
         </is>
       </c>
       <c r="C1300" t="n">
@@ -20476,7 +20488,7 @@
       </c>
       <c r="B1301" s="1" t="inlineStr">
         <is>
-          <t>Then she turned her face to mine and pressed her
+          <t>Then Nono-chan turned to face me and pressed her
 forehead against mine.</t>
         </is>
       </c>
@@ -20492,7 +20504,7 @@
       </c>
       <c r="B1302" s="1" t="inlineStr">
         <is>
-          <t>My heart was pounding so close like that...</t>
+          <t>Being so close, my heart started racing...</t>
         </is>
       </c>
       <c r="C1302" t="n">
@@ -20522,7 +20534,7 @@
       </c>
       <c r="B1304" s="1" t="inlineStr">
         <is>
-          <t>「...chu」</t>
+          <t>「...*smooch*」</t>
         </is>
       </c>
       <c r="C1304" t="n">
@@ -20537,7 +20549,7 @@
       </c>
       <c r="B1305" s="1" t="inlineStr">
         <is>
-          <t>A little mouth-to-mouth kiss...</t>
+          <t>*Smooch* — a quick kiss on the mouth...</t>
         </is>
       </c>
       <c r="C1305" t="n">
@@ -20552,7 +20564,7 @@
       </c>
       <c r="B1306" s="1" t="inlineStr">
         <is>
-          <t>...A kiss！？</t>
+          <t>...A kiss!?</t>
         </is>
       </c>
       <c r="C1306" t="n">
@@ -20582,7 +20594,7 @@
       </c>
       <c r="B1308" s="1" t="inlineStr">
         <is>
-          <t>「No, Nono-chan...」</t>
+          <t>「N-Nono-chan...」</t>
         </is>
       </c>
       <c r="C1308" t="n">
@@ -20612,7 +20624,7 @@
       </c>
       <c r="B1310" s="1" t="inlineStr">
         <is>
-          <t>「...Did you remember it！？」</t>
+          <t>「...Did you remember?!」</t>
         </is>
       </c>
       <c r="C1310" t="n">
@@ -20673,7 +20685,7 @@
       </c>
       <c r="B1314" s="1" t="inlineStr">
         <is>
-          <t>So this is what Nono-chan's mom used to do.</t>
+          <t>Th-this is what Nono-chan's mama used to do.</t>
         </is>
       </c>
       <c r="C1314" t="n">
@@ -20719,7 +20731,7 @@
       </c>
       <c r="B1317" s="1" t="inlineStr">
         <is>
-          <t>「...You can't sleep without doing this？」</t>
+          <t>"…You can't sleep unless I do this?"</t>
         </is>
       </c>
       <c r="C1317" t="n">
@@ -20734,7 +20746,7 @@
       </c>
       <c r="B1318" s="1" t="inlineStr">
         <is>
-          <t>I couldn't help but feel the more frightened one.</t>
+          <t>Before I knew it, I was the one who got scared.</t>
         </is>
       </c>
       <c r="C1318" t="n">
@@ -20749,8 +20761,8 @@
       </c>
       <c r="B1319" s="1" t="inlineStr">
         <is>
-          <t>Then, as if to match me, Nono-chan sank down and
-became quiet.</t>
+          <t>Then, as if mirroring me, Nono-chan also went quiet
+and looked dejected.</t>
         </is>
       </c>
       <c r="C1319" t="n">
@@ -20780,8 +20792,8 @@
       </c>
       <c r="B1321" s="1" t="inlineStr">
         <is>
-          <t>「Ah, that is… um… I don’t really know, but I just
-can’t sleep…」</t>
+          <t>「Ah... um... I'm not sure, but I just can't fall
+asleep...」</t>
         </is>
       </c>
       <c r="C1321" t="n">
@@ -20811,8 +20823,8 @@
       </c>
       <c r="B1323" s="1" t="inlineStr">
         <is>
-          <t>「Like Janitor-sensei said, I think part of it is that
-the environment changed...」</t>
+          <t>「As Janitor-sensei said, I think it's partly because
+the environment has changed...」</t>
         </is>
       </c>
       <c r="C1323" t="n">
@@ -20842,8 +20854,8 @@
       </c>
       <c r="B1325" s="1" t="inlineStr">
         <is>
-          <t>「B-but. If you do the same thing you always do for
-me, I think I can sleep！」</t>
+          <t>「B-but... if you do for me what you always do, I
+think I can sleep!」</t>
         </is>
       </c>
       <c r="C1325" t="n">
@@ -20858,8 +20870,8 @@
       </c>
       <c r="B1326" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan told me in a troubled voice, speaking
-haltingly.</t>
+          <t>Nono-chan spoke to me haltingly, with a troubled
+expression.</t>
         </is>
       </c>
       <c r="C1326" t="n">
@@ -20921,7 +20933,7 @@
       </c>
       <c r="B1330" s="1" t="inlineStr">
         <is>
-          <t>「…Well then, shall we try it？」</t>
+          <t>「…Well then, shall we try it?」</t>
         </is>
       </c>
       <c r="C1330" t="n">
@@ -20951,7 +20963,7 @@
       </c>
       <c r="B1332" s="1" t="inlineStr">
         <is>
-          <t>「Trying isn’t good enough！ Do it seriously！」</t>
+          <t>Don't just 'try' it! Please do it seriously!</t>
         </is>
       </c>
       <c r="C1332" t="n">
@@ -20981,7 +20993,7 @@
       </c>
       <c r="B1334" s="1" t="inlineStr">
         <is>
-          <t>「Yes…！　Sorry.」</t>
+          <t>「Y-yes...! I'm sorry.」</t>
         </is>
       </c>
       <c r="C1334" t="n">
@@ -21044,7 +21056,7 @@
       </c>
       <c r="B1338" s="1" t="inlineStr">
         <is>
-          <t>…If I’m a guy, I have to respond properly too！</t>
+          <t>...If I'm a guy, I have to do my part properly too!</t>
         </is>
       </c>
       <c r="C1338" t="n">
@@ -21135,8 +21147,8 @@
       </c>
       <c r="B1344" s="1" t="inlineStr">
         <is>
-          <t>…If she gets that hyped up, she might not be able to
-sleep either.</t>
+          <t>…If she gets that worked up, she might not be able to
+sleep.</t>
         </is>
       </c>
       <c r="C1344" t="n">
@@ -21151,7 +21163,7 @@
       </c>
       <c r="B1345" s="1" t="inlineStr">
         <is>
-          <t>But we had to try.</t>
+          <t>But I had no choice but to try.</t>
         </is>
       </c>
       <c r="C1345" t="n">
@@ -21166,8 +21178,8 @@
       </c>
       <c r="B1346" s="1" t="inlineStr">
         <is>
-          <t>I drew Nono-chan close and moved while remembering
-what she’d done for me earlier.</t>
+          <t>I pulled Nono-chan closer and, remembering what she'd
+just done for me, acted.</t>
         </is>
       </c>
       <c r="C1346" t="n">
@@ -21197,7 +21209,7 @@
       </c>
       <c r="B1348" s="1" t="inlineStr">
         <is>
-          <t>Then next, I rubbed cheek to cheek.</t>
+          <t>Then I rubbed my cheek against hers.</t>
         </is>
       </c>
       <c r="C1348" t="n">
@@ -21227,7 +21239,7 @@
       </c>
       <c r="B1350" s="1" t="inlineStr">
         <is>
-          <t>「Nng, mmm…」</t>
+          <t>「Nn... Nn...」</t>
         </is>
       </c>
       <c r="C1350" t="n">
@@ -21257,8 +21269,8 @@
       </c>
       <c r="B1352" s="1" t="inlineStr">
         <is>
-          <t>To ease her nerves, I gently hug her stiff little
-frame... ah, so soft and warm...</t>
+          <t>I give her a gentle squeeze to ease her tension...
+ah, so soft and warm...</t>
         </is>
       </c>
       <c r="C1352" t="n">
@@ -21273,8 +21285,8 @@
       </c>
       <c r="B1353" s="1" t="inlineStr">
         <is>
-          <t>No, no... I suppress that beguiling warmth with
-reason, and bump my forehead to hers head-on.</t>
+          <t>No, no... I hold back that enticing warmth with
+reason, then lightly bump my forehead against hers.</t>
         </is>
       </c>
       <c r="C1353" t="n">
@@ -21304,7 +21316,7 @@
       </c>
       <c r="B1355" s="1" t="inlineStr">
         <is>
-          <t>「Ah........」</t>
+          <t>「Ah…」</t>
         </is>
       </c>
       <c r="C1355" t="n">
@@ -21319,7 +21331,8 @@
       </c>
       <c r="B1356" s="1" t="inlineStr">
         <is>
-          <t>And then, a sleepy smooch, chu, chuchu... chu...！</t>
+          <t>And then, a good-night smooch — chu, chu-chu...
+chu...!</t>
         </is>
       </c>
       <c r="C1356" t="n">
@@ -21379,7 +21392,7 @@
       </c>
       <c r="B1360" s="1" t="inlineStr">
         <is>
-          <t>「Fuaah...！」</t>
+          <t>「Fwah…！」</t>
         </is>
       </c>
       <c r="C1360" t="n">
@@ -21394,7 +21407,7 @@
       </c>
       <c r="B1361" s="1" t="inlineStr">
         <is>
-          <t>When the last kiss ends, Nono-chan sucks in a breath.</t>
+          <t>As the last kiss ended, Nono-chan gasped.</t>
         </is>
       </c>
       <c r="C1361" t="n">
@@ -21409,7 +21422,7 @@
       </c>
       <c r="B1362" s="1" t="inlineStr">
         <is>
-          <t>And then........</t>
+          <t>And then...</t>
         </is>
       </c>
       <c r="C1362" t="n">
@@ -21439,7 +21452,7 @@
       </c>
       <c r="B1364" s="1" t="inlineStr">
         <is>
-          <t>「Suu........ suu........ suu...」</t>
+          <t>「Soft, steady breaths...」</t>
         </is>
       </c>
       <c r="C1364" t="n">
@@ -21454,8 +21467,8 @@
       </c>
       <c r="B1365" s="1" t="inlineStr">
         <is>
-          <t>Just as I think she's going to collapse into me, she
-starts letting out healthy, sleepy breaths.</t>
+          <t>Just when I think she's going to slump against me,
+she begins to breathe softly and steadily.</t>
         </is>
       </c>
       <c r="C1365" t="n">
@@ -21516,7 +21529,7 @@
       </c>
       <c r="B1369" s="1" t="inlineStr">
         <is>
-          <t>...Amazing. As if by magic, she just conks out.</t>
+          <t>...Amazing. She fell asleep as if by magic.</t>
         </is>
       </c>
       <c r="C1369" t="n">
@@ -21561,7 +21574,7 @@
       </c>
       <c r="B1372" s="1" t="inlineStr">
         <is>
-          <t>「Suu........ suu........ suu...」</t>
+          <t>「Soft, steady breaths...」</t>
         </is>
       </c>
       <c r="C1372" t="n">
@@ -21576,7 +21589,7 @@
       </c>
       <c r="B1373" s="1" t="inlineStr">
         <is>
-          <t>For now, I lay Nono-chan down on the bed.</t>
+          <t>For now, I laid Nono-chan down on the bed.</t>
         </is>
       </c>
       <c r="C1373" t="n">
@@ -21591,8 +21604,8 @@
       </c>
       <c r="B1374" s="1" t="inlineStr">
         <is>
-          <t>I have a lot on my mind, but I'm relieved I at least
-got her to sleep.</t>
+          <t>There's a lot on my mind, but I'm relieved I managed
+to get Nono-chan to sleep.</t>
         </is>
       </c>
       <c r="C1374" t="n">
@@ -21607,7 +21620,7 @@
       </c>
       <c r="B1375" s="1" t="inlineStr">
         <is>
-          <t>So, what should I do now？</t>
+          <t>So, what should I do now?</t>
         </is>
       </c>
       <c r="C1375" t="n">
@@ -21638,9 +21651,9 @@
       </c>
       <c r="B1377" s="1" t="inlineStr">
         <is>
-          <t>It would be more practical to leave her here, but
-everyone would find out that the person I went to
-sleep beside was Nono-chan.</t>
+          <t>It would make more sense to let her sleep here, but
+everyone would find out that I went to bed with
+Nono-chan.</t>
         </is>
       </c>
       <c r="C1377" t="n">
@@ -21655,8 +21668,9 @@
       </c>
       <c r="B1378" s="1" t="inlineStr">
         <is>
-          <t>I don't care, and I'm sure the others wouldn't mind
-that much, but Nono-chan herself would.</t>
+          <t>I wouldn't care, and I'm sure the others wouldn't
+mind that much either, but Nono-chan herself probably
+would.</t>
         </is>
       </c>
       <c r="C1378" t="n">
@@ -21671,8 +21685,8 @@
       </c>
       <c r="B1379" s="1" t="inlineStr">
         <is>
-          <t>She takes pride in her title as a teacher, so she
-dislikes being seen as small.</t>
+          <t>Nono-chan takes pride in the title of "teacher," so
+she resists being treated like a child.</t>
         </is>
       </c>
       <c r="C1379" t="n">
@@ -21687,9 +21701,10 @@
       </c>
       <c r="B1380" s="1" t="inlineStr">
         <is>
-          <t>And yet needing someone to sleep next to her would
-make her look like a little kid, and she wouldn't
-want everyone to know that.</t>
+          <t>Even so, the fact that Nono-chan can't sleep unless
+someone sleeps beside her would make her seem like a
+little kid, and she wouldn't want everyone to find
+out.</t>
         </is>
       </c>
       <c r="C1380" t="n">
@@ -21720,9 +21735,9 @@
       </c>
       <c r="B1382" s="1" t="inlineStr">
         <is>
-          <t>Anyway, tonight the mission was basically to carry
-Nono-chan to her room, lay her on the bed, and that
-would be mission clear.</t>
+          <t>Anyway, for tonight, the plan was basically to carry
+Nono-chan to her room, put her to bed, and that would
+be mission accomplished.</t>
         </is>
       </c>
       <c r="C1382" t="n">
@@ -21752,7 +21767,7 @@
       </c>
       <c r="B1384" s="1" t="inlineStr">
         <is>
-          <t>「Suu… suu… suu…」</t>
+          <t>「Soft, steady breaths...」</t>
         </is>
       </c>
       <c r="C1384" t="n">
@@ -21767,7 +21782,7 @@
       </c>
       <c r="B1385" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan kept breathing in a steady, regular rhythm.</t>
+          <t>Nono-chan continued to breathe steadily.</t>
         </is>
       </c>
       <c r="C1385" t="n">
@@ -21782,8 +21797,8 @@
       </c>
       <c r="B1386" s="1" t="inlineStr">
         <is>
-          <t>She’d said once she fell asleep she was hard to wake,
-and yeah, her sleep really looks deep.</t>
+          <t>She’d said that once she fell asleep she was hard to
+wake, and indeed, she seems to be in a deep sleep.</t>
         </is>
       </c>
       <c r="C1386" t="n">
@@ -21814,7 +21829,7 @@
       </c>
       <c r="B1388" s="1" t="inlineStr">
         <is>
-          <t>……………Is she really not going to wake up？</t>
+          <t>…I wonder if she really won't wake up?</t>
         </is>
       </c>
       <c r="C1388" t="n">
@@ -21860,7 +21875,7 @@
       </c>
       <c r="B1391" s="1" t="inlineStr">
         <is>
-          <t>「…Eih.」</t>
+          <t>「…There!」</t>
         </is>
       </c>
       <c r="C1391" t="n">
@@ -21890,7 +21905,7 @@
       </c>
       <c r="B1393" s="1" t="inlineStr">
         <is>
-          <t>「Suu… suu…」</t>
+          <t>「Soft, steady breaths...」</t>
         </is>
       </c>
       <c r="C1393" t="n">
@@ -21920,7 +21935,7 @@
       </c>
       <c r="B1395" s="1" t="inlineStr">
         <is>
-          <t>「…Eiy, eiy.」</t>
+          <t>「…There! There!」</t>
         </is>
       </c>
       <c r="C1395" t="n">
@@ -21950,7 +21965,7 @@
       </c>
       <c r="B1397" s="1" t="inlineStr">
         <is>
-          <t>「Suu… suu… suu…」</t>
+          <t>「Soft, steady breaths...」</t>
         </is>
       </c>
       <c r="C1397" t="n">
@@ -21965,8 +21980,9 @@
       </c>
       <c r="B1398" s="1" t="inlineStr">
         <is>
-          <t>I prodded a few times, but there was no sign she’d
-wake up and her breathing didn’t even falter.</t>
+          <t>I poked/squished her cheek a few times, but there was
+no sign she'd wake up and her breathing didn't even
+change.</t>
         </is>
       </c>
       <c r="C1398" t="n">
@@ -21996,7 +22012,7 @@
       </c>
       <c r="B1400" s="1" t="inlineStr">
         <is>
-          <t>I see… she’s sleeping that deeply…</t>
+          <t>I see... she's sleeping so soundly...</t>
         </is>
       </c>
       <c r="C1400" t="n">
@@ -22011,7 +22027,7 @@
       </c>
       <c r="B1401" s="1" t="inlineStr">
         <is>
-          <t>Right now she wouldn’t notice whatever I did.</t>
+          <t>Right now, Nono-chan wouldn't notice anything I did.</t>
         </is>
       </c>
       <c r="C1401" t="n">
@@ -22056,7 +22072,7 @@
       </c>
       <c r="B1404" s="1" t="inlineStr">
         <is>
-          <t>…Is that really… the case…？</t>
+          <t>…I see... I wonder if that's so...?</t>
         </is>
       </c>
       <c r="C1404" t="n">
@@ -22071,9 +22087,9 @@
       </c>
       <c r="B1405" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan is a genius. Maybe because she’s a genius
-there are things a simple person like me can’t
-measure.</t>
+          <t>Nono-chan is a genius. But because she’s a genius,
+there may be things an ordinary person like me can’t
+fathom.</t>
         </is>
       </c>
       <c r="C1405" t="n">
@@ -22088,8 +22104,7 @@
       </c>
       <c r="B1406" s="1" t="inlineStr">
         <is>
-          <t>In other words, she might absolutely not wake
-up……maybe.</t>
+          <t>In other words... Nono-chan might not wake up at all.</t>
         </is>
       </c>
       <c r="C1406" t="n">
@@ -22104,7 +22119,7 @@
       </c>
       <c r="B1407" s="1" t="inlineStr">
         <is>
-          <t>Muu… desire swirls in my head.</t>
+          <t>Mmm... desires are swirling in my head.</t>
         </is>
       </c>
       <c r="C1407" t="n">
@@ -22119,8 +22134,8 @@
       </c>
       <c r="B1408" s="1" t="inlineStr">
         <is>
-          <t>It’s wrong to mess with a sleeping girl, but would it
-be forgivable to give her another kiss…？</t>
+          <t>It's wrong to play a prank on a sleeping girl, but
+would one more Kiss really be unforgivable...?</t>
         </is>
       </c>
       <c r="C1408" t="n">
@@ -22212,7 +22227,7 @@
       </c>
       <c r="B1414" s="1" t="inlineStr">
         <is>
-          <t>「Suu… suu… suu…」</t>
+          <t>「Soft, steady breaths...」</t>
         </is>
       </c>
       <c r="C1414" t="n">
@@ -22227,7 +22242,7 @@
       </c>
       <c r="B1415" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan's sleeping breaths are the same as ever.</t>
+          <t>Nono-chan's breathing was as steady as ever.</t>
         </is>
       </c>
       <c r="C1415" t="n">
@@ -22242,7 +22257,7 @@
       </c>
       <c r="B1416" s="1" t="inlineStr">
         <is>
-          <t>With such steady breathing, she definitely won't wake
+          <t>With such steady breathing, she’s unlikely to wake
 up.</t>
         </is>
       </c>
@@ -22274,8 +22289,8 @@
       </c>
       <c r="B1418" s="1" t="inlineStr">
         <is>
-          <t>Tensing up from that nervousness, I slowly lowered my
-face...</t>
+          <t>Though my body stiffened with nervousness, I slowly
+lowered my face...</t>
         </is>
       </c>
       <c r="C1418" t="n">
@@ -22290,7 +22305,7 @@
       </c>
       <c r="B1419" s="1" t="inlineStr">
         <is>
-          <t>...smooch.</t>
+          <t>...kiss.</t>
         </is>
       </c>
       <c r="C1419" t="n">
@@ -22320,7 +22335,7 @@
       </c>
       <c r="B1421" s="1" t="inlineStr">
         <is>
-          <t>I stole Nono-chan's lips...！</t>
+          <t>I ended up stealing a kiss from Nono-chan...!</t>
         </is>
       </c>
       <c r="C1421" t="n">
@@ -22335,8 +22350,8 @@
       </c>
       <c r="B1422" s="1" t="inlineStr">
         <is>
-          <t>No, we do a little smooch as a goodnight ritual, but
-doing it like this feels wrong.</t>
+          <t>Well, we do a 'chu' as our goodnight ritual, but
+doing it this way feels wrong.</t>
         </is>
       </c>
       <c r="C1422" t="n">
@@ -22366,7 +22381,7 @@
       </c>
       <c r="B1424" s="1" t="inlineStr">
         <is>
-          <t>Warm...pleasant...feels good...</t>
+          <t>Warm... it feels good...</t>
         </is>
       </c>
       <c r="C1424" t="n">
@@ -22396,7 +22411,7 @@
       </c>
       <c r="B1426" s="1" t="inlineStr">
         <is>
-          <t>「suu... suu...」</t>
+          <t>「Soft, steady breaths...」</t>
         </is>
       </c>
       <c r="C1426" t="n">
@@ -22411,8 +22426,8 @@
       </c>
       <c r="B1427" s="1" t="inlineStr">
         <is>
-          <t>Besides, the unchanged rhythm of her breathing
-rhythmically brushing against my lips is comforting.</t>
+          <t>Also, the steady, unchanging breaths that
+periodically brush against my lips feel pleasant.</t>
         </is>
       </c>
       <c r="C1427" t="n">
@@ -22442,7 +22457,7 @@
       </c>
       <c r="B1429" s="1" t="inlineStr">
         <is>
-          <t>「n—... muu...」</t>
+          <t>「Nn... mmm...」</t>
         </is>
       </c>
       <c r="C1429" t="n">
@@ -22472,7 +22487,7 @@
       </c>
       <c r="B1431" s="1" t="inlineStr">
         <is>
-          <t>「...！ ？」</t>
+          <t>「...!?」</t>
         </is>
       </c>
       <c r="C1431" t="n">
@@ -22518,7 +22533,7 @@
       </c>
       <c r="B1434" s="1" t="inlineStr">
         <is>
-          <t>「suu... suu...」</t>
+          <t>"Soft, steady breaths..."</t>
         </is>
       </c>
       <c r="C1434" t="n">
@@ -22534,7 +22549,7 @@
       <c r="B1435" s="1" t="inlineStr">
         <is>
           <t>I panicked thinking I'd woken her, but Nono-chan's
-breath soon returned to normal.</t>
+breathing soon returned to normal.</t>
         </is>
       </c>
       <c r="C1435" t="n">
@@ -22549,8 +22564,8 @@
       </c>
       <c r="B1436" s="1" t="inlineStr">
         <is>
-          <t>Her breathing had only changed because her mouth had
-been covered, so she must still be in a deep sleep.</t>
+          <t>Her breathing only changed because her lips were
+covered, so she must still be in a deep sleep.</t>
         </is>
       </c>
       <c r="C1436" t="n">
@@ -22595,7 +22610,7 @@
       </c>
       <c r="B1439" s="1" t="inlineStr">
         <is>
-          <t>「...hm？」</t>
+          <t>「...Nn?」</t>
         </is>
       </c>
       <c r="C1439" t="n">
@@ -22610,8 +22625,8 @@
       </c>
       <c r="B1440" s="1" t="inlineStr">
         <is>
-          <t>When I reached out to pick her up in a princess
-carry, I suddenly realized something.</t>
+          <t>When I reached out to carry Nono-chan in a princess
+carry, I belatedly realized something.</t>
         </is>
       </c>
       <c r="C1440" t="n">
@@ -22626,7 +22641,7 @@
       </c>
       <c r="B1441" s="1" t="inlineStr">
         <is>
-          <t>These pajamas are front-opening.</t>
+          <t>These pajamas open in the front.</t>
         </is>
       </c>
       <c r="C1441" t="n">
@@ -22641,8 +22656,8 @@
       </c>
       <c r="B1442" s="1" t="inlineStr">
         <is>
-          <t>I had pictured a onesie, so I was surprised they
-opened in the front...</t>
+          <t>I’d pictured a kigurumi, so I was surprised that
+these pajamas open in the front...</t>
         </is>
       </c>
       <c r="C1442" t="n">
@@ -22672,7 +22687,7 @@
       </c>
       <c r="B1444" s="1" t="inlineStr">
         <is>
-          <t>click, click, click...</t>
+          <t>snap, snap, snap...</t>
         </is>
       </c>
       <c r="C1444" t="n">
@@ -22702,7 +22717,7 @@
       </c>
       <c r="B1446" s="1" t="inlineStr">
         <is>
-          <t>I-I'm not supposed to be doing something like this！</t>
+          <t>I- I shouldn't be doing this!</t>
         </is>
       </c>
       <c r="C1446" t="n">
@@ -22734,8 +22749,8 @@
       </c>
       <c r="B1448" s="1" t="inlineStr">
         <is>
-          <t>No, still, absentmindedly undoing the buttons can
-only be described as losing my mind.</t>
+          <t>No — unconsciously unbuttoning them can only mean I'm
+out of my mind.</t>
         </is>
       </c>
       <c r="C1448" t="n">
@@ -22765,7 +22780,7 @@
       </c>
       <c r="B1450" s="1" t="inlineStr">
         <is>
-          <t>「Suu... suu... suu...」</t>
+          <t>「suu... suu... suu...」</t>
         </is>
       </c>
       <c r="C1450" t="n">
@@ -22797,7 +22812,7 @@
       <c r="B1452" s="1" t="inlineStr">
         <is>
           <t>Right next to her, a guy with an erect penis was
-standing, yet she was completely undefended.</t>
+standing, yet she was completely defenseless.</t>
         </is>
       </c>
       <c r="C1452" t="n">
@@ -22812,8 +22827,8 @@
       </c>
       <c r="B1453" s="1" t="inlineStr">
         <is>
-          <t>She's making healthy sleeping breaths with her small
-breasts exposed...！</t>
+          <t>Nono-chan is breathing peacefully with her tiny
+breasts exposed...!</t>
         </is>
       </c>
       <c r="C1453" t="n">
@@ -22858,8 +22873,8 @@
       </c>
       <c r="B1456" s="1" t="inlineStr">
         <is>
-          <t>I snapped back to myself and shook my head in a
-panic.</t>
+          <t>I snapped back to my senses and frantically shook my
+head.</t>
         </is>
       </c>
       <c r="C1456" t="n">
@@ -22874,8 +22889,8 @@
       </c>
       <c r="B1457" s="1" t="inlineStr">
         <is>
-          <t>I can't allow any more mischief！ Even if someone else
-would, I won't forgive myself！</t>
+          <t>I won't allow any more mischief! Even if someone else
+would, I myself won't forgive it!</t>
         </is>
       </c>
       <c r="C1457" t="n">
@@ -22890,7 +22905,8 @@
       </c>
       <c r="B1458" s="1" t="inlineStr">
         <is>
-          <t>I won't forgive it, but maybe use it as material...？</t>
+          <t>I won't forgive it, but maybe I could at least use it
+as masturbation material...?</t>
         </is>
       </c>
       <c r="C1458" t="n">
@@ -22935,7 +22951,7 @@
       </c>
       <c r="B1461" s="1" t="inlineStr">
         <is>
-          <t>Mu, uuu... I can't hold back...！</t>
+          <t>Mmm... I can't hold back...!</t>
         </is>
       </c>
       <c r="C1461" t="n">
@@ -22950,8 +22966,8 @@
       </c>
       <c r="B1462" s="1" t="inlineStr">
         <is>
-          <t>Giving in to the impulse, I went all the way and
-pulled my pants down.</t>
+          <t>I gave in to the impulse and boldly pulled my pants
+down.</t>
         </is>
       </c>
       <c r="C1462" t="n">
@@ -22966,7 +22982,7 @@
       </c>
       <c r="B1463" s="1" t="inlineStr">
         <is>
-          <t>Sure enough, there it was: a painfully hard penis...</t>
+          <t>Sure enough, there it was: my rock-hard penis...</t>
         </is>
       </c>
       <c r="C1463" t="n">
@@ -22981,7 +22997,7 @@
       </c>
       <c r="B1464" s="1" t="inlineStr">
         <is>
-          <t>I was even more surprised when I gripped it.</t>
+          <t>When I grabbed them, I was even more surprised.</t>
         </is>
       </c>
       <c r="C1464" t="n">
@@ -23072,7 +23088,7 @@
       </c>
       <c r="B1470" s="1" t="inlineStr">
         <is>
-          <t>「Suu... suu... suu...」</t>
+          <t>「suu... suu... suu...」</t>
         </is>
       </c>
       <c r="C1470" t="n">
@@ -23103,8 +23119,7 @@
       </c>
       <c r="B1472" s="1" t="inlineStr">
         <is>
-          <t>Doing something like masturbating right in front of
-her felt horribly wrong.</t>
+          <t>Masturbating in front of her felt terribly wrong.</t>
         </is>
       </c>
       <c r="C1472" t="n">
@@ -23119,8 +23134,8 @@
       </c>
       <c r="B1473" s="1" t="inlineStr">
         <is>
-          <t>What made it worse was these pajamas that came off so
-easily.</t>
+          <t>To make matters worse, these pajamas were so easy to
+take off.</t>
         </is>
       </c>
       <c r="C1473" t="n">
@@ -23135,8 +23150,9 @@
       </c>
       <c r="B1474" s="1" t="inlineStr">
         <is>
-          <t>I could strip Nono-chan naked anytime... suppressing
-that temptation only made me more aroused.</t>
+          <t>I could undress Nono-chan whenever I wanted... but
+trying to suppress that temptation only made me even
+more aroused.</t>
         </is>
       </c>
       <c r="C1474" t="n">
@@ -23166,8 +23182,7 @@
       </c>
       <c r="B1476" s="1" t="inlineStr">
         <is>
-          <t>I wanted, at this point, to just strip her
-completely！</t>
+          <t>I might as well just strip Nono-chan completely!</t>
         </is>
       </c>
       <c r="C1476" t="n">
@@ -23197,8 +23212,8 @@
       </c>
       <c r="B1478" s="1" t="inlineStr">
         <is>
-          <t>I want to make that tiny hand hold my rock-hard,
-swollen penis…！</t>
+          <t>I want that tiny hand to grasp my rock-hard, swollen
+penis…！</t>
         </is>
       </c>
       <c r="C1478" t="n">
@@ -23260,7 +23275,7 @@
       </c>
       <c r="B1482" s="1" t="inlineStr">
         <is>
-          <t>「Suu…… suu…… nnn…」</t>
+          <t>「suu... suu... nnu...」</t>
         </is>
       </c>
       <c r="C1482" t="n">
@@ -23275,7 +23290,7 @@
       </c>
       <c r="B1483" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan's breath in sleep falters faintly.</t>
+          <t>Nono-chan's breathing in her sleep falters faintly.</t>
         </is>
       </c>
       <c r="C1483" t="n">
@@ -23290,8 +23305,8 @@
       </c>
       <c r="B1484" s="1" t="inlineStr">
         <is>
-          <t>It's probably just a coincidence, but it makes my
-heart skip a beat.</t>
+          <t>It's probably just a coincidence, but I can't help
+but feel my heart skip a beat.</t>
         </is>
       </c>
       <c r="C1484" t="n">
@@ -23306,8 +23321,9 @@
       </c>
       <c r="B1485" s="1" t="inlineStr">
         <is>
-          <t>The reason my heart skips is because I've got sinful
-feelings myself, and that's what amps me up…！</t>
+          <t>The reason my heart skips a beat is that I myself
+have guilty feelings — and it's precisely because of
+that that my arousal intensifies…!</t>
         </is>
       </c>
       <c r="C1485" t="n">
@@ -23322,8 +23338,7 @@
       </c>
       <c r="B1486" s="1" t="inlineStr">
         <is>
-          <t>This sense of transgression is unbearable in the best
-way.</t>
+          <t>I find this sense of transgression irresistible.</t>
         </is>
       </c>
       <c r="C1486" t="n">
@@ -23353,7 +23368,7 @@
       </c>
       <c r="B1488" s="1" t="inlineStr">
         <is>
-          <t>「Ah… ah… aguuh！？」</t>
+          <t>「Ah... ah... aagh!?」</t>
         </is>
       </c>
       <c r="C1488" t="n">
@@ -23368,8 +23383,9 @@
       </c>
       <c r="B1489" s="1" t="inlineStr">
         <is>
-          <t>Watching Nono-chan, I hit my peak, and in an instant
-the feeling of coming hit me and I panicked.</t>
+          <t>As I watched Nono-chan, I reached my climax, and in
+an instant I felt the sensation of ejaculating and
+panicked.</t>
         </is>
       </c>
       <c r="C1489" t="n">
@@ -23415,7 +23431,7 @@
       </c>
       <c r="B1492" s="1" t="inlineStr">
         <is>
-          <t>「Suu…… suu……」</t>
+          <t>「suu... suu...」</t>
         </is>
       </c>
       <c r="C1492" t="n">
@@ -23430,8 +23446,8 @@
       </c>
       <c r="B1493" s="1" t="inlineStr">
         <is>
-          <t>In front of me is Nono-chan's sleeping face and her
-loosened, soft skin.</t>
+          <t>In front of me were Nono-chan's sleeping face and her
+bare, soft skin.</t>
         </is>
       </c>
       <c r="C1493" t="n">
@@ -23446,7 +23462,7 @@
       </c>
       <c r="B1494" s="1" t="inlineStr">
         <is>
-          <t>Seeing that, my throat makes a sound.</t>
+          <t>Seeing that, a sound escaped my throat.</t>
         </is>
       </c>
       <c r="C1494" t="n">
@@ -23521,7 +23537,7 @@
       </c>
       <c r="B1499" s="1" t="inlineStr">
         <is>
-          <t>「Suu…… nnn… suu……」</t>
+          <t>「suu... nnu... suu...」</t>
         </is>
       </c>
       <c r="C1499" t="n">
@@ -23536,8 +23552,8 @@
       </c>
       <c r="B1500" s="1" t="inlineStr">
         <is>
-          <t>Watching Nono-chan's innocent sleeping breaths, I
-stroke my penis faster.</t>
+          <t>Watching Nono-chan as she breathed innocently in her
+sleep, I began stroking my penis.</t>
         </is>
       </c>
       <c r="C1500" t="n">
@@ -23552,8 +23568,9 @@
       </c>
       <c r="B1501" s="1" t="inlineStr">
         <is>
-          <t>Then the orgasm I had held back rushes back in an
-instant and takes over my lower half.</t>
+          <t>Then the ejaculatory sensation I'd been holding back
+suddenly returned and seized control of my lower
+body.</t>
         </is>
       </c>
       <c r="C1501" t="n">
@@ -23583,7 +23600,7 @@
       </c>
       <c r="B1503" s="1" t="inlineStr">
         <is>
-          <t>「Ah… no, I can't… I'm sorry, Nono-chan！」</t>
+          <t>「Ah... I can't anymore... I'm sorry, Nono-chan!」</t>
         </is>
       </c>
       <c r="C1503" t="n">
@@ -23598,7 +23615,7 @@
       </c>
       <c r="B1504" s="1" t="inlineStr">
         <is>
-          <t>Pew pew！ Splurt！ Splurt！ Splurt！</t>
+          <t>Spurt! Spurt! Spurt! Splurt!</t>
         </is>
       </c>
       <c r="C1504" t="n">
@@ -23628,7 +23645,7 @@
       </c>
       <c r="B1506" s="1" t="inlineStr">
         <is>
-          <t>「Uah… ah…」</t>
+          <t>「Uwah… ah…」</t>
         </is>
       </c>
       <c r="C1506" t="n">
@@ -23660,8 +23677,9 @@
       </c>
       <c r="B1508" s="1" t="inlineStr">
         <is>
-          <t>The semen that shot out as if it had exploded is
-splattered from Nono-chan’s cheek down to her chest.</t>
+          <t>The semen, expelled in what was almost an accidental
+discharge, splattered across Nono-chan’s cheek and
+onto her chest.</t>
         </is>
       </c>
       <c r="C1508" t="n">
@@ -23708,7 +23726,7 @@
       </c>
       <c r="B1511" s="1" t="inlineStr">
         <is>
-          <t>「Suu... suu...」</t>
+          <t>「suu... suu...」</t>
         </is>
       </c>
       <c r="C1511" t="n">
@@ -23754,7 +23772,7 @@
       </c>
       <c r="B1514" s="1" t="inlineStr">
         <is>
-          <t>Sorry, Nono-chan… I'll wipe you properly, okay?</t>
+          <t>I'm sorry, Nono-chan... I'll clean you up properly.</t>
         </is>
       </c>
       <c r="C1514" t="n">
@@ -23769,7 +23787,7 @@
       </c>
       <c r="B1515" s="1" t="inlineStr">
         <is>
-          <t>I quickly cleaned up my thing and then prepared some
+          <t>I quickly cleaned up my penis and prepared some
 tissues and a wet towel warmed to body temperature.</t>
         </is>
       </c>
@@ -23815,7 +23833,7 @@
       </c>
       <c r="B1518" s="1" t="inlineStr">
         <is>
-          <t>First, wipe off the semen with a tissue.</t>
+          <t>First, I'll wipe the semen off with a tissue.</t>
         </is>
       </c>
       <c r="C1518" t="n">
@@ -23830,8 +23848,8 @@
       </c>
       <c r="B1519" s="1" t="inlineStr">
         <is>
-          <t>I wrap my palm in a slightly larger wad of tissues
-and wipe the semen off her cheek.</t>
+          <t>I wrap my palm in a slightly thicker wad of tissue
+and wipe the semen from Nono-chan's cheek.</t>
         </is>
       </c>
       <c r="C1519" t="n">
@@ -23861,7 +23879,7 @@
       </c>
       <c r="B1521" s="1" t="inlineStr">
         <is>
-          <t>「suu…………suu…n'—！」</t>
+          <t>「suu…………suu……nnh……！」</t>
         </is>
       </c>
       <c r="C1521" t="n">
@@ -23892,7 +23910,7 @@
       </c>
       <c r="B1523" s="1" t="inlineStr">
         <is>
-          <t>But she still shows no sign of waking yet.</t>
+          <t>But she still shows no sign of waking.</t>
         </is>
       </c>
       <c r="C1523" t="n">
@@ -23907,7 +23925,7 @@
       </c>
       <c r="B1524" s="1" t="inlineStr">
         <is>
-          <t>Alright, this time it's her chest….</t>
+          <t>Alright, now for her chest...</t>
         </is>
       </c>
       <c r="C1524" t="n">
@@ -23922,7 +23940,7 @@
       </c>
       <c r="B1525" s="1" t="inlineStr">
         <is>
-          <t>I'll just touch it a little… sorry.</t>
+          <t>I'm going to touch it just a little... sorry.</t>
         </is>
       </c>
       <c r="C1525" t="n">
@@ -23937,8 +23955,8 @@
       </c>
       <c r="B1526" s="1" t="inlineStr">
         <is>
-          <t>As if to hide my own apologetic feelings, I apologize
-and gently press a tissue to Nono-chan's chest.</t>
+          <t>As if to hide my own guilty feelings, I apologized
+and gently pressed a tissue to Nono-chan's chest.</t>
         </is>
       </c>
       <c r="C1526" t="n">
@@ -23983,8 +24001,8 @@
       </c>
       <c r="B1529" s="1" t="inlineStr">
         <is>
-          <t>…Through the tissue, I can feel the smoothness of her
-chest.</t>
+          <t>…Through the tissue, I can feel the gentle curve of
+Nono-chan's chest.</t>
         </is>
       </c>
       <c r="C1529" t="n">
@@ -23999,8 +24017,8 @@
       </c>
       <c r="B1530" s="1" t="inlineStr">
         <is>
-          <t>Ah... she's small, but she's still a girl, after
-all...</t>
+          <t>Ah... they're small, but Nono-chan is still a girl,
+after all...</t>
         </is>
       </c>
       <c r="C1530" t="n">
@@ -24045,7 +24063,7 @@
       </c>
       <c r="B1533" s="1" t="inlineStr">
         <is>
-          <t>「Suu... suu... suu...」</t>
+          <t>「suu... suu... suu...」</t>
         </is>
       </c>
       <c r="C1533" t="n">
@@ -24060,8 +24078,8 @@
       </c>
       <c r="B1534" s="1" t="inlineStr">
         <is>
-          <t>As expected, she must sense being touched, because
-Nono-chan's sleeping breaths pick up slightly.</t>
+          <t>Perhaps sensing that she's being touched, Nono-chan's
+breathing in her sleep quickened slightly.</t>
         </is>
       </c>
       <c r="C1534" t="n">
@@ -24076,8 +24094,8 @@
       </c>
       <c r="B1535" s="1" t="inlineStr">
         <is>
-          <t>I've heard she doesn't wake up easily, but I should
-get this over with quickly...</t>
+          <t>I've heard she doesn't wake up easily, so I'd better
+finish quickly...</t>
         </is>
       </c>
       <c r="C1535" t="n">
@@ -24092,7 +24110,7 @@
       </c>
       <c r="B1536" s="1" t="inlineStr">
         <is>
-          <t>Even so, slowly, slowly….</t>
+          <t>Even so, slowly, slowly...</t>
         </is>
       </c>
       <c r="C1536" t="n">
@@ -24122,7 +24140,7 @@
       </c>
       <c r="B1538" s="1" t="inlineStr">
         <is>
-          <t>「……！」</t>
+          <t>「……っ！」</t>
         </is>
       </c>
       <c r="C1538" t="n">
@@ -24137,8 +24155,8 @@
       </c>
       <c r="B1539" s="1" t="inlineStr">
         <is>
-          <t>Maybe because I was flustered and careless, I
-absentmindedly rubbed her nipple through the tissue.</t>
+          <t>Maybe I'd gotten flustered and careless, and I ended
+up rubbing Nono-chan's nipple through the tissue.</t>
         </is>
       </c>
       <c r="C1539" t="n">
@@ -24153,7 +24171,7 @@
       </c>
       <c r="B1540" s="1" t="inlineStr">
         <is>
-          <t>Nono</t>
+          <t>Nono-chan</t>
         </is>
       </c>
       <c r="C1540" t="n">
@@ -24168,7 +24186,7 @@
       </c>
       <c r="B1541" s="1" t="inlineStr">
         <is>
-          <t>「Suu... suu... nngh, huu...？」</t>
+          <t>suu... suu... nn... fuu...?</t>
         </is>
       </c>
       <c r="C1541" t="n">
@@ -24183,8 +24201,8 @@
       </c>
       <c r="B1542" s="1" t="inlineStr">
         <is>
-          <t>Maybe feeling something off at that spot, her
-sleeping breaths grow uneven.</t>
+          <t>Perhaps sensing discomfort at her nipple, her
+breathing in sleep becomes uneven.</t>
         </is>
       </c>
       <c r="C1542" t="n">
@@ -24214,7 +24232,7 @@
       </c>
       <c r="B1544" s="1" t="inlineStr">
         <is>
-          <t>…For now, the semen has been wiped off.</t>
+          <t>For now, I've wiped the semen off.</t>
         </is>
       </c>
       <c r="C1544" t="n">
@@ -24245,7 +24263,7 @@
       </c>
       <c r="B1546" s="1" t="inlineStr">
         <is>
-          <t>First, the cheek...</t>
+          <t>I'll start with Nono-chan's cheek...</t>
         </is>
       </c>
       <c r="C1546" t="n">
@@ -24260,7 +24278,7 @@
       </c>
       <c r="B1547" s="1" t="inlineStr">
         <is>
-          <t>Nono</t>
+          <t>Nono-chan</t>
         </is>
       </c>
       <c r="C1547" t="n">
@@ -24275,7 +24293,7 @@
       </c>
       <c r="B1548" s="1" t="inlineStr">
         <is>
-          <t>「suu... nng, nnh... suu... nnh...」</t>
+          <t>「suu... n'... n'u... suu... n'u...」</t>
         </is>
       </c>
       <c r="C1548" t="n">
@@ -24290,8 +24308,8 @@
       </c>
       <c r="B1549" s="1" t="inlineStr">
         <is>
-          <t>Maybe reacting to the cold, wet towel, she finally
-started letting out groans.</t>
+          <t>Perhaps reacting to the cool touch of the damp towel,
+Nono-chan began to let out groans.</t>
         </is>
       </c>
       <c r="C1549" t="n">
@@ -24306,7 +24324,7 @@
       </c>
       <c r="B1550" s="1" t="inlineStr">
         <is>
-          <t>N-No way... she won't wake up, right？</t>
+          <t>N-No way... she won't wake up, right?</t>
         </is>
       </c>
       <c r="C1550" t="n">
@@ -24321,8 +24339,8 @@
       </c>
       <c r="B1551" s="1" t="inlineStr">
         <is>
-          <t>I want to believe she won't wake up, but I just don't
-know.</t>
+          <t>I want to believe she won't wake up, but I can't be
+sure.</t>
         </is>
       </c>
       <c r="C1551" t="n">
@@ -24337,7 +24355,7 @@
       </c>
       <c r="B1552" s="1" t="inlineStr">
         <is>
-          <t>And I have to wipe your chest again...</t>
+          <t>I also have to wipe Nono-chan's chest...</t>
         </is>
       </c>
       <c r="C1552" t="n">
@@ -24352,9 +24370,9 @@
       </c>
       <c r="B1553" s="1" t="inlineStr">
         <is>
-          <t>But if I think about it the other way, if I wipe her
-chest and button up her pajamas I can at least feel
-safe for now.</t>
+          <t>But on the other hand, if I wipe Nono-chan's chest
+and button up her pajamas, I can at least feel a
+little safer for now.</t>
         </is>
       </c>
       <c r="C1553" t="n">
@@ -24384,7 +24402,7 @@
       </c>
       <c r="B1555" s="1" t="inlineStr">
         <is>
-          <t>Nono</t>
+          <t>Nono-chan</t>
         </is>
       </c>
       <c r="C1555" t="n">
@@ -24399,7 +24417,7 @@
       </c>
       <c r="B1556" s="1" t="inlineStr">
         <is>
-          <t>「Nn... suu... nnu... nn...！」</t>
+          <t>Nn... suh... nnh... nn...!</t>
         </is>
       </c>
       <c r="C1556" t="n">
@@ -24414,8 +24432,8 @@
       </c>
       <c r="B1557" s="1" t="inlineStr">
         <is>
-          <t>When the towel touched her chest, her sleeping
-breaths grew even more ragged.</t>
+          <t>When the towel touched Nono-chan's chest, her
+breathing grew even more ragged.</t>
         </is>
       </c>
       <c r="C1557" t="n">
@@ -24430,7 +24448,7 @@
       </c>
       <c r="B1558" s="1" t="inlineStr">
         <is>
-          <t>Your chest is so sensitive…</t>
+          <t>Nono-chan's chest is so sensitive…</t>
         </is>
       </c>
       <c r="C1558" t="n">
@@ -24460,8 +24478,8 @@
       </c>
       <c r="B1560" s="1" t="inlineStr">
         <is>
-          <t>Feeling the slight rise and fall of her chest, I was
-moved again.</t>
+          <t>Feeling the slight rise and fall of Nono-chan's
+chest, I was moved again.</t>
         </is>
       </c>
       <c r="C1560" t="n">
@@ -24476,7 +24494,7 @@
       </c>
       <c r="B1561" s="1" t="inlineStr">
         <is>
-          <t>Nono</t>
+          <t>Nono-chan</t>
         </is>
       </c>
       <c r="C1561" t="n">
@@ -24491,7 +24509,7 @@
       </c>
       <c r="B1562" s="1" t="inlineStr">
         <is>
-          <t>「Nngh…！ Nnh… huh, nnngh…」</t>
+          <t>「Nn...! Nn... fuh, nnngh...」</t>
         </is>
       </c>
       <c r="C1562" t="n">
@@ -24538,8 +24556,8 @@
       </c>
       <c r="B1565" s="1" t="inlineStr">
         <is>
-          <t>I wiped away the semen stains and buttoned up the
-front of her pajamas.</t>
+          <t>I wiped away the traces of semen and buttoned up the
+front of Nono-chan's pajamas.</t>
         </is>
       </c>
       <c r="C1565" t="n">
@@ -24554,7 +24572,7 @@
       </c>
       <c r="B1566" s="1" t="inlineStr">
         <is>
-          <t>That’s back to the way it was.</t>
+          <t>There — it's back to normal.</t>
         </is>
       </c>
       <c r="C1566" t="n">
@@ -24615,7 +24633,8 @@
       </c>
       <c r="B1570" s="1" t="inlineStr">
         <is>
-          <t>Using a sleeping girl as material... that's wrong.</t>
+          <t>Using a sleeping girl as material for masturbation is
+wrong.</t>
         </is>
       </c>
       <c r="C1570" t="n">
@@ -24630,7 +24649,7 @@
       </c>
       <c r="B1571" s="1" t="inlineStr">
         <is>
-          <t>Reflect on this... me！</t>
+          <t>I need to reflect on this...!</t>
         </is>
       </c>
       <c r="C1571" t="n">
@@ -24645,7 +24664,7 @@
       </c>
       <c r="B1572" s="1" t="inlineStr">
         <is>
-          <t>Nono</t>
+          <t>Nono-chan</t>
         </is>
       </c>
       <c r="C1572" t="n">
@@ -24691,8 +24710,8 @@
       </c>
       <c r="B1575" s="1" t="inlineStr">
         <is>
-          <t>Her breathing had gotten messy before, but in the end
-she didn't wake up.</t>
+          <t>Nono-chan's breathing had grown ragged at times, but
+in the end she never woke up.</t>
         </is>
       </c>
       <c r="C1575" t="n">
@@ -24768,8 +24787,8 @@
       </c>
       <c r="B1580" s="1" t="inlineStr">
         <is>
-          <t>Come to think of it, even if she's a deep sleeper,
-she looks awfully quiet when she sleeps.</t>
+          <t>Now that I think about it, even though Nono-chan is a
+deep sleeper, she's sleeping awfully quietly.</t>
         </is>
       </c>
       <c r="C1580" t="n">
@@ -24784,8 +24803,8 @@
       </c>
       <c r="B1581" s="1" t="inlineStr">
         <is>
-          <t>That's probably because it was the first day she came
-to this island and she was nervous.</t>
+          <t>She was probably nervous because it was her first day
+on the island.</t>
         </is>
       </c>
       <c r="C1581" t="n">
@@ -24815,8 +24834,8 @@
       </c>
       <c r="B1583" s="1" t="inlineStr">
         <is>
-          <t>Maybe she's mentally worn out, so she might be
-sleeping more soundly than usual.</t>
+          <t>Nono-chan might be sleeping more soundly than usual
+because she's mentally tired.</t>
         </is>
       </c>
       <c r="C1583" t="n">
@@ -24831,7 +24850,7 @@
       </c>
       <c r="B1584" s="1" t="inlineStr">
         <is>
-          <t>And yet... ah, and yet...！</t>
+          <t>And yet... ah, and yet...!</t>
         </is>
       </c>
       <c r="C1584" t="n">
@@ -24846,8 +24865,8 @@
       </c>
       <c r="B1585" s="1" t="inlineStr">
         <is>
-          <t>I felt embarrassed about my actions all over again,
-but now isn't the time to just be regretting them.</t>
+          <t>I felt ashamed of my actions all over again, but now
+isn't the time to just be regretting them.</t>
         </is>
       </c>
       <c r="C1585" t="n">
@@ -24862,7 +24881,7 @@
       </c>
       <c r="B1586" s="1" t="inlineStr">
         <is>
-          <t>I have a mission to deliver Nono-chan to her room.</t>
+          <t>My mission is to escort Nono-chan to her room.</t>
         </is>
       </c>
       <c r="C1586" t="n">
@@ -24877,10 +24896,10 @@
       </c>
       <c r="B1587" s="1" t="inlineStr">
         <is>
-          <t>If the goal is for her to relax, it'd still be better
-if she slept here, but if that happens she'll
-probably feel awkward afterward, Nono-chan would try
-to be considerate.</t>
+          <t>If the goal is to let Nono-chan rest, it would still
+be better for her to sleep here, but if she wakes up
+she'll probably feel self-conscious and try to be
+considerate.</t>
         </is>
       </c>
       <c r="C1587" t="n">
@@ -24895,7 +24914,8 @@
       </c>
       <c r="B1588" s="1" t="inlineStr">
         <is>
-          <t>And I can't let myself run wild any further...！</t>
+          <t>And I can't let myself get carried away any
+further...!</t>
         </is>
       </c>
       <c r="C1588" t="n">
@@ -24910,7 +24930,8 @@
       </c>
       <c r="B1589" s="1" t="inlineStr">
         <is>
-          <t>I made up my mind and decided to take Nono-chan home.</t>
+          <t>I made up my mind and decided to escort Nono-chan to
+her room.</t>
         </is>
       </c>
       <c r="C1589" t="n">
